--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6403,7 +6403,7 @@
         <v>128203131</v>
       </c>
       <c r="B51" t="n">
-        <v>105404</v>
+        <v>105405</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128203088</v>
       </c>
       <c r="B52" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>128203259</v>
       </c>
       <c r="B53" t="n">
-        <v>110352</v>
+        <v>110353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6729,54 +6729,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203096</v>
+        <v>128203256</v>
       </c>
       <c r="B54" t="n">
-        <v>98446</v>
+        <v>109296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736474</v>
+        <v>736176</v>
       </c>
       <c r="R54" t="n">
-        <v>6411596</v>
+        <v>6411455</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6809,11 +6800,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6848,7 +6834,7 @@
         <v>128203241</v>
       </c>
       <c r="B55" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6952,10 +6938,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203179</v>
+        <v>128203195</v>
       </c>
       <c r="B56" t="n">
-        <v>99509</v>
+        <v>98377</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,37 +6949,46 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736300</v>
+        <v>736314</v>
       </c>
       <c r="R56" t="n">
-        <v>6411481</v>
+        <v>6411572</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7025,6 +7020,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7054,10 +7054,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203100</v>
+        <v>128203096</v>
       </c>
       <c r="B57" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736361</v>
+        <v>736474</v>
       </c>
       <c r="R57" t="n">
-        <v>6411697</v>
+        <v>6411596</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7134,6 +7134,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7165,10 +7170,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203195</v>
+        <v>128203100</v>
       </c>
       <c r="B58" t="n">
-        <v>98376</v>
+        <v>98447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7176,26 +7181,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7209,13 +7214,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736314</v>
+        <v>736361</v>
       </c>
       <c r="R58" t="n">
-        <v>6411572</v>
+        <v>6411697</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7247,11 +7252,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7281,27 +7281,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203256</v>
+        <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>109295</v>
+        <v>99510</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736176</v>
+        <v>736300</v>
       </c>
       <c r="R59" t="n">
-        <v>6411455</v>
+        <v>6411481</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,27 +7383,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203237</v>
+        <v>128203220</v>
       </c>
       <c r="B60" t="n">
-        <v>110352</v>
+        <v>109296</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7411,20 +7411,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R60" t="n">
-        <v>6411500</v>
+        <v>6411551</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7458,7 +7467,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Överallt!</t>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7490,42 +7499,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203233</v>
+        <v>128203144</v>
       </c>
       <c r="B61" t="n">
-        <v>98453</v>
+        <v>109296</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7534,13 +7543,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736276</v>
+        <v>736246</v>
       </c>
       <c r="R61" t="n">
-        <v>6411531</v>
+        <v>6411634</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7572,6 +7581,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7583,7 +7597,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7708,10 +7722,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203186</v>
+        <v>128203233</v>
       </c>
       <c r="B63" t="n">
-        <v>98490</v>
+        <v>98454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7719,26 +7733,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219862</v>
+        <v>219799</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7752,10 +7766,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736331</v>
+        <v>736276</v>
       </c>
       <c r="R63" t="n">
-        <v>6411530</v>
+        <v>6411531</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7801,7 +7815,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7819,27 +7833,27 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203220</v>
+        <v>128203237</v>
       </c>
       <c r="B64" t="n">
-        <v>109295</v>
+        <v>110353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7847,29 +7861,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R64" t="n">
-        <v>6411551</v>
+        <v>6411500</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7903,7 +7908,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7935,42 +7940,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203144</v>
+        <v>128203186</v>
       </c>
       <c r="B65" t="n">
-        <v>109295</v>
+        <v>98491</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7979,13 +7984,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736246</v>
+        <v>736331</v>
       </c>
       <c r="R65" t="n">
-        <v>6411634</v>
+        <v>6411530</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8015,11 +8020,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8051,45 +8051,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128203243</v>
+        <v>128203089</v>
       </c>
       <c r="B66" t="n">
-        <v>109295</v>
+        <v>98447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>736237</v>
+        <v>736488</v>
       </c>
       <c r="R66" t="n">
-        <v>6411472</v>
+        <v>6411510</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8135,7 +8144,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8153,54 +8162,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128203089</v>
+        <v>128203243</v>
       </c>
       <c r="B67" t="n">
-        <v>98446</v>
+        <v>109296</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>736488</v>
+        <v>736237</v>
       </c>
       <c r="R67" t="n">
-        <v>6411510</v>
+        <v>6411472</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203104</v>
+        <v>128203239</v>
       </c>
       <c r="B68" t="n">
-        <v>105404</v>
+        <v>109296</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8275,16 +8275,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8299,13 +8299,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736325</v>
+        <v>736283</v>
       </c>
       <c r="R68" t="n">
-        <v>6411730</v>
+        <v>6411500</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Spridd. Flera i blom.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8371,57 +8371,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203209</v>
+        <v>128203095</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>109296</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736295</v>
+        <v>736474</v>
       </c>
       <c r="R69" t="n">
-        <v>6411567</v>
+        <v>6411596</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8453,6 +8444,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8464,7 +8460,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8482,48 +8478,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203239</v>
+        <v>128203209</v>
       </c>
       <c r="B70" t="n">
-        <v>109295</v>
+        <v>98471</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R70" t="n">
-        <v>6411500</v>
+        <v>6411567</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8555,11 +8560,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203095</v>
+        <v>128203104</v>
       </c>
       <c r="B71" t="n">
-        <v>109295</v>
+        <v>105405</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,16 +8600,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8624,13 +8624,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736474</v>
+        <v>736325</v>
       </c>
       <c r="R71" t="n">
-        <v>6411596</v>
+        <v>6411730</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8699,7 +8699,7 @@
         <v>128203181</v>
       </c>
       <c r="B72" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8803,57 +8803,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128203182</v>
+        <v>128203166</v>
       </c>
       <c r="B73" t="n">
-        <v>98446</v>
+        <v>109296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736350</v>
+        <v>736275</v>
       </c>
       <c r="R73" t="n">
-        <v>6411491</v>
+        <v>6411455</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8883,11 +8874,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8919,48 +8905,57 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203166</v>
+        <v>128203182</v>
       </c>
       <c r="B74" t="n">
-        <v>109295</v>
+        <v>98447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>736275</v>
+        <v>736350</v>
       </c>
       <c r="R74" t="n">
-        <v>6411455</v>
+        <v>6411491</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8990,6 +8985,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9024,7 +9024,7 @@
         <v>128203187</v>
       </c>
       <c r="B75" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203023</v>
+        <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>57669</v>
+        <v>98475</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,31 +9143,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>742</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9176,13 +9176,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736365</v>
+        <v>736184</v>
       </c>
       <c r="R76" t="n">
-        <v>6411573</v>
+        <v>6411805</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9214,6 +9214,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9225,7 +9230,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9243,45 +9248,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203199</v>
+        <v>128203023</v>
       </c>
       <c r="B77" t="n">
-        <v>98453</v>
+        <v>57669</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219799</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736314</v>
+        <v>736365</v>
       </c>
       <c r="R77" t="n">
-        <v>6411572</v>
+        <v>6411573</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9316,11 +9330,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9332,7 +9341,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9353,7 +9362,7 @@
         <v>128203189</v>
       </c>
       <c r="B78" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9455,7 +9464,7 @@
         <v>128203185</v>
       </c>
       <c r="B79" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9562,7 +9571,7 @@
         <v>128203099</v>
       </c>
       <c r="B80" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9670,10 +9679,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203086</v>
+        <v>128203199</v>
       </c>
       <c r="B81" t="n">
-        <v>98446</v>
+        <v>98454</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9681,16 +9690,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9698,29 +9707,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736450</v>
+        <v>736314</v>
       </c>
       <c r="R81" t="n">
-        <v>6411486</v>
+        <v>6411572</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9752,6 +9752,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9763,7 +9768,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9781,10 +9786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203221</v>
+        <v>128203086</v>
       </c>
       <c r="B82" t="n">
-        <v>98470</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,26 +9797,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9825,13 +9830,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736272</v>
+        <v>736450</v>
       </c>
       <c r="R82" t="n">
-        <v>6411546</v>
+        <v>6411486</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9874,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9892,37 +9897,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203114</v>
+        <v>128203221</v>
       </c>
       <c r="B83" t="n">
-        <v>98474</v>
+        <v>98471</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>742</v>
+        <v>219811</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9936,10 +9941,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736184</v>
+        <v>736272</v>
       </c>
       <c r="R83" t="n">
-        <v>6411805</v>
+        <v>6411546</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9974,11 +9979,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10008,37 +10008,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203249</v>
+        <v>128203192</v>
       </c>
       <c r="B84" t="n">
-        <v>98446</v>
+        <v>105405</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736192</v>
+        <v>736339</v>
       </c>
       <c r="R84" t="n">
-        <v>6411467</v>
+        <v>6411571</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10090,6 +10090,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10101,7 +10106,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10122,7 +10127,7 @@
         <v>128203132</v>
       </c>
       <c r="B85" t="n">
-        <v>107353</v>
+        <v>107354</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10230,10 +10235,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203162</v>
+        <v>128203249</v>
       </c>
       <c r="B86" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10260,7 +10265,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10274,13 +10279,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736250</v>
+        <v>736192</v>
       </c>
       <c r="R86" t="n">
-        <v>6411464</v>
+        <v>6411467</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10341,37 +10346,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203192</v>
+        <v>128203162</v>
       </c>
       <c r="B87" t="n">
-        <v>105404</v>
+        <v>98447</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10385,13 +10390,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736339</v>
+        <v>736250</v>
       </c>
       <c r="R87" t="n">
-        <v>6411571</v>
+        <v>6411464</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10423,11 +10428,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10460,7 +10460,7 @@
         <v>128203111</v>
       </c>
       <c r="B88" t="n">
-        <v>98399</v>
+        <v>98400</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10573,10 +10573,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128205915</v>
+        <v>128203211</v>
       </c>
       <c r="B89" t="n">
-        <v>57669</v>
+        <v>99144</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10584,46 +10584,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>222322</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736315</v>
+        <v>736301</v>
       </c>
       <c r="R89" t="n">
-        <v>6411597</v>
+        <v>6411564</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10666,7 +10657,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10684,10 +10675,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203225</v>
+        <v>128203165</v>
       </c>
       <c r="B90" t="n">
-        <v>98470</v>
+        <v>98447</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10695,26 +10686,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10728,13 +10719,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736263</v>
+        <v>736260</v>
       </c>
       <c r="R90" t="n">
-        <v>6411533</v>
+        <v>6411450</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10777,7 +10768,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,10 +10786,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203197</v>
+        <v>128203081</v>
       </c>
       <c r="B91" t="n">
-        <v>98470</v>
+        <v>98447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,37 +10797,46 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736314</v>
+        <v>736347</v>
       </c>
       <c r="R91" t="n">
-        <v>6411572</v>
+        <v>6411466</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10868,11 +10868,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10884,7 +10879,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10902,48 +10897,57 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203211</v>
+        <v>128203225</v>
       </c>
       <c r="B92" t="n">
-        <v>99143</v>
+        <v>98471</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736301</v>
+        <v>736263</v>
       </c>
       <c r="R92" t="n">
-        <v>6411564</v>
+        <v>6411533</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10986,7 +10990,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11004,32 +11008,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203180</v>
+        <v>128203197</v>
       </c>
       <c r="B93" t="n">
-        <v>105404</v>
+        <v>98471</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11039,13 +11043,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736300</v>
+        <v>736314</v>
       </c>
       <c r="R93" t="n">
-        <v>6411481</v>
+        <v>6411572</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11079,7 +11083,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11093,7 +11097,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11111,42 +11115,42 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203165</v>
+        <v>128205915</v>
       </c>
       <c r="B94" t="n">
-        <v>98446</v>
+        <v>57669</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11155,13 +11159,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736260</v>
+        <v>736315</v>
       </c>
       <c r="R94" t="n">
-        <v>6411450</v>
+        <v>6411597</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11222,54 +11226,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203156</v>
+        <v>128203180</v>
       </c>
       <c r="B95" t="n">
-        <v>98386</v>
+        <v>105405</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>223591</v>
+        <v>221137</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736221</v>
+        <v>736300</v>
       </c>
       <c r="R95" t="n">
-        <v>6411593</v>
+        <v>6411481</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11304,6 +11299,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11333,10 +11333,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203081</v>
+        <v>128203156</v>
       </c>
       <c r="B96" t="n">
-        <v>98446</v>
+        <v>98387</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11344,26 +11344,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11377,10 +11377,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736347</v>
+        <v>736221</v>
       </c>
       <c r="R96" t="n">
-        <v>6411466</v>
+        <v>6411593</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11447,7 +11447,7 @@
         <v>128203087</v>
       </c>
       <c r="B97" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>128203246</v>
       </c>
       <c r="B98" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11653,32 +11653,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203106</v>
+        <v>128203080</v>
       </c>
       <c r="B99" t="n">
-        <v>98470</v>
+        <v>109296</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736305</v>
+        <v>736347</v>
       </c>
       <c r="R99" t="n">
-        <v>6411739</v>
+        <v>6411466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11726,11 +11726,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -11742,7 +11737,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11760,10 +11755,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203167</v>
+        <v>128203106</v>
       </c>
       <c r="B100" t="n">
-        <v>98446</v>
+        <v>98471</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11771,43 +11766,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736275</v>
+        <v>736305</v>
       </c>
       <c r="R100" t="n">
-        <v>6411455</v>
+        <v>6411739</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11842,6 +11828,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11853,7 +11844,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11871,45 +11862,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203080</v>
+        <v>128203167</v>
       </c>
       <c r="B101" t="n">
-        <v>109295</v>
+        <v>98447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736347</v>
+        <v>736275</v>
       </c>
       <c r="R101" t="n">
-        <v>6411466</v>
+        <v>6411455</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
         <v>128203154</v>
       </c>
       <c r="B102" t="n">
-        <v>98376</v>
+        <v>98377</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>128203126</v>
       </c>
       <c r="B103" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>128203129</v>
       </c>
       <c r="B104" t="n">
-        <v>105404</v>
+        <v>105405</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12297,57 +12297,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203207</v>
+        <v>128203242</v>
       </c>
       <c r="B105" t="n">
-        <v>98470</v>
+        <v>109296</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736300</v>
+        <v>736237</v>
       </c>
       <c r="R105" t="n">
-        <v>6411576</v>
+        <v>6411484</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12379,6 +12370,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12390,7 +12386,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12408,48 +12404,57 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203242</v>
+        <v>128203207</v>
       </c>
       <c r="B106" t="n">
-        <v>109295</v>
+        <v>98471</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736237</v>
+        <v>736300</v>
       </c>
       <c r="R106" t="n">
-        <v>6411484</v>
+        <v>6411576</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12481,11 +12486,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12515,32 +12515,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203107</v>
+        <v>128203177</v>
       </c>
       <c r="B107" t="n">
-        <v>105404</v>
+        <v>98454</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221137</v>
+        <v>219799</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12550,10 +12550,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736305</v>
+        <v>736300</v>
       </c>
       <c r="R107" t="n">
-        <v>6411739</v>
+        <v>6411481</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12622,48 +12622,57 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203255</v>
+        <v>128203234</v>
       </c>
       <c r="B108" t="n">
-        <v>109295</v>
+        <v>98447</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736200</v>
+        <v>736279</v>
       </c>
       <c r="R108" t="n">
-        <v>6411456</v>
+        <v>6411517</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12724,32 +12733,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203177</v>
+        <v>128203255</v>
       </c>
       <c r="B109" t="n">
-        <v>98453</v>
+        <v>109296</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12759,10 +12768,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736300</v>
+        <v>736200</v>
       </c>
       <c r="R109" t="n">
-        <v>6411481</v>
+        <v>6411456</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12797,11 +12806,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12813,7 +12817,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12831,57 +12835,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203234</v>
+        <v>128203107</v>
       </c>
       <c r="B110" t="n">
-        <v>98446</v>
+        <v>105405</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736279</v>
+        <v>736305</v>
       </c>
       <c r="R110" t="n">
-        <v>6411517</v>
+        <v>6411739</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12913,6 +12908,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12942,54 +12942,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128203160</v>
+        <v>128203161</v>
       </c>
       <c r="B111" t="n">
-        <v>98446</v>
+        <v>109296</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>736240</v>
+        <v>736250</v>
       </c>
       <c r="R111" t="n">
-        <v>6411466</v>
+        <v>6411464</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13053,10 +13044,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128203161</v>
+        <v>128203236</v>
       </c>
       <c r="B112" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13088,13 +13079,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>736250</v>
+        <v>736279</v>
       </c>
       <c r="R112" t="n">
-        <v>6411464</v>
+        <v>6411517</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13124,6 +13115,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13155,48 +13151,57 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128203236</v>
+        <v>128203160</v>
       </c>
       <c r="B113" t="n">
-        <v>109295</v>
+        <v>98447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>736279</v>
+        <v>736240</v>
       </c>
       <c r="R113" t="n">
-        <v>6411517</v>
+        <v>6411466</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13226,11 +13231,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13265,7 +13265,7 @@
         <v>128203138</v>
       </c>
       <c r="B114" t="n">
-        <v>98453</v>
+        <v>98454</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>128203094</v>
       </c>
       <c r="B115" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13484,10 +13484,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128203247</v>
+        <v>128203134</v>
       </c>
       <c r="B116" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13512,17 +13512,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>736192</v>
+        <v>736242</v>
       </c>
       <c r="R116" t="n">
-        <v>6411467</v>
+        <v>6411713</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -13568,7 +13577,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13586,57 +13595,48 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128203215</v>
+        <v>128203247</v>
       </c>
       <c r="B117" t="n">
-        <v>98453</v>
+        <v>109296</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>736301</v>
+        <v>736192</v>
       </c>
       <c r="R117" t="n">
-        <v>6411564</v>
+        <v>6411467</v>
       </c>
       <c r="S117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13697,42 +13697,42 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128203134</v>
+        <v>128203215</v>
       </c>
       <c r="B118" t="n">
-        <v>109295</v>
+        <v>98454</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13741,13 +13741,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>736242</v>
+        <v>736301</v>
       </c>
       <c r="R118" t="n">
-        <v>6411713</v>
+        <v>6411564</v>
       </c>
       <c r="S118" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13811,7 +13811,7 @@
         <v>128203101</v>
       </c>
       <c r="B119" t="n">
-        <v>98376</v>
+        <v>98377</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>128203159</v>
       </c>
       <c r="B120" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14026,57 +14026,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128203213</v>
+        <v>128203230</v>
       </c>
       <c r="B121" t="n">
-        <v>98470</v>
+        <v>109296</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>736301</v>
+        <v>736270</v>
       </c>
       <c r="R121" t="n">
-        <v>6411564</v>
+        <v>6411530</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14108,6 +14099,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14119,7 +14115,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14137,48 +14133,57 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128203230</v>
+        <v>128203213</v>
       </c>
       <c r="B122" t="n">
-        <v>109295</v>
+        <v>98471</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>736270</v>
+        <v>736301</v>
       </c>
       <c r="R122" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14210,11 +14215,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14247,7 +14247,7 @@
         <v>128203151</v>
       </c>
       <c r="B123" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14351,57 +14351,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203216</v>
+        <v>128203091</v>
       </c>
       <c r="B124" t="n">
-        <v>98446</v>
+        <v>109296</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736297</v>
+        <v>736520</v>
       </c>
       <c r="R124" t="n">
-        <v>6411559</v>
+        <v>6411544</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14431,11 +14422,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14467,10 +14453,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203092</v>
+        <v>128203190</v>
       </c>
       <c r="B125" t="n">
-        <v>98446</v>
+        <v>98447</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14497,7 +14483,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14511,13 +14497,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R125" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14578,10 +14564,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203235</v>
+        <v>128203216</v>
       </c>
       <c r="B126" t="n">
-        <v>110352</v>
+        <v>98447</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14589,34 +14575,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736279</v>
+        <v>736297</v>
       </c>
       <c r="R126" t="n">
-        <v>6411517</v>
+        <v>6411559</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14649,6 +14644,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14680,35 +14680,44 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203091</v>
+        <v>128203092</v>
       </c>
       <c r="B127" t="n">
-        <v>109295</v>
+        <v>98447</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -14782,10 +14791,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203190</v>
+        <v>128203235</v>
       </c>
       <c r="B128" t="n">
-        <v>98446</v>
+        <v>110353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14793,43 +14802,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736335</v>
+        <v>736279</v>
       </c>
       <c r="R128" t="n">
-        <v>6411533</v>
+        <v>6411517</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203112</v>
+        <v>128203093</v>
       </c>
       <c r="B129" t="n">
-        <v>98453</v>
+        <v>109296</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736184</v>
+        <v>736498</v>
       </c>
       <c r="R129" t="n">
-        <v>6411805</v>
+        <v>6411566</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,11 +14966,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14982,7 +14977,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15000,10 +14995,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203113</v>
+        <v>128203112</v>
       </c>
       <c r="B130" t="n">
-        <v>98470</v>
+        <v>98454</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15011,21 +15006,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15107,10 +15102,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203252</v>
+        <v>128203113</v>
       </c>
       <c r="B131" t="n">
-        <v>98490</v>
+        <v>98471</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15118,46 +15113,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219862</v>
+        <v>219811</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>736193</v>
+        <v>736184</v>
       </c>
       <c r="R131" t="n">
-        <v>6411456</v>
+        <v>6411805</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15189,6 +15175,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15200,7 +15191,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15218,10 +15209,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203178</v>
+        <v>128203252</v>
       </c>
       <c r="B132" t="n">
-        <v>97995</v>
+        <v>98491</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15229,37 +15220,46 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221930</v>
+        <v>219862</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736300</v>
+        <v>736193</v>
       </c>
       <c r="R132" t="n">
-        <v>6411481</v>
+        <v>6411456</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15291,11 +15291,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15307,7 +15302,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15325,32 +15320,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203093</v>
+        <v>128203178</v>
       </c>
       <c r="B133" t="n">
-        <v>109295</v>
+        <v>97996</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>221930</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15360,10 +15355,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736498</v>
+        <v>736300</v>
       </c>
       <c r="R133" t="n">
-        <v>6411566</v>
+        <v>6411481</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15398,6 +15393,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15430,7 +15430,7 @@
         <v>128203083</v>
       </c>
       <c r="B134" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>128203164</v>
       </c>
       <c r="B135" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>128203228</v>
       </c>
       <c r="B136" t="n">
-        <v>98453</v>
+        <v>98454</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>128203127</v>
       </c>
       <c r="B137" t="n">
-        <v>98453</v>
+        <v>98454</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>128203139</v>
       </c>
       <c r="B138" t="n">
-        <v>98472</v>
+        <v>98473</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15964,54 +15964,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203084</v>
+        <v>128203085</v>
       </c>
       <c r="B139" t="n">
-        <v>98446</v>
+        <v>109296</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736442</v>
+        <v>736450</v>
       </c>
       <c r="R139" t="n">
-        <v>6411479</v>
+        <v>6411486</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16075,10 +16066,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203223</v>
+        <v>128203084</v>
       </c>
       <c r="B140" t="n">
-        <v>98376</v>
+        <v>98447</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16086,26 +16077,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16119,13 +16110,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736272</v>
+        <v>736442</v>
       </c>
       <c r="R140" t="n">
-        <v>6411536</v>
+        <v>6411479</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16168,7 +16159,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16186,10 +16177,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203231</v>
+        <v>128203223</v>
       </c>
       <c r="B141" t="n">
-        <v>98446</v>
+        <v>98377</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16197,26 +16188,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16230,10 +16221,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736270</v>
+        <v>736272</v>
       </c>
       <c r="R141" t="n">
-        <v>6411530</v>
+        <v>6411536</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16279,7 +16270,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16297,48 +16288,57 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203085</v>
+        <v>128203231</v>
       </c>
       <c r="B142" t="n">
-        <v>109295</v>
+        <v>98447</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736450</v>
+        <v>736270</v>
       </c>
       <c r="R142" t="n">
-        <v>6411486</v>
+        <v>6411530</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>128203240</v>
       </c>
       <c r="B143" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,27 +6400,27 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203131</v>
+        <v>128203259</v>
       </c>
       <c r="B51" t="n">
-        <v>105405</v>
+        <v>110354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221137</v>
+        <v>219677</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6428,29 +6428,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736256</v>
+        <v>736176</v>
       </c>
       <c r="R51" t="n">
-        <v>6411743</v>
+        <v>6411455</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6482,6 +6473,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6493,7 +6489,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Våtmark mellan strandvallar.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6514,7 +6510,7 @@
         <v>128203088</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6622,27 +6618,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128203259</v>
+        <v>128203131</v>
       </c>
       <c r="B53" t="n">
-        <v>110353</v>
+        <v>105406</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219677</v>
+        <v>221137</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6650,20 +6646,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736176</v>
+        <v>736256</v>
       </c>
       <c r="R53" t="n">
-        <v>6411455</v>
+        <v>6411743</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6695,11 +6700,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Våtmark mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
         <v>128203256</v>
       </c>
       <c r="B54" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>128203241</v>
       </c>
       <c r="B55" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>128203195</v>
       </c>
       <c r="B56" t="n">
-        <v>98377</v>
+        <v>98378</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>128203096</v>
       </c>
       <c r="B57" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>128203100</v>
       </c>
       <c r="B58" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>99510</v>
+        <v>99511</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203220</v>
+        <v>128203021</v>
       </c>
       <c r="B60" t="n">
-        <v>109296</v>
+        <v>57669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,31 +7394,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7427,10 +7423,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736295</v>
+        <v>736197</v>
       </c>
       <c r="R60" t="n">
-        <v>6411551</v>
+        <v>6411554</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7463,11 +7459,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7499,27 +7490,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203144</v>
+        <v>128203237</v>
       </c>
       <c r="B61" t="n">
-        <v>109296</v>
+        <v>110354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7527,26 +7518,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736246</v>
+        <v>736283</v>
       </c>
       <c r="R61" t="n">
-        <v>6411634</v>
+        <v>6411500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7583,7 +7565,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7615,38 +7597,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203021</v>
+        <v>128203186</v>
       </c>
       <c r="B62" t="n">
-        <v>57669</v>
+        <v>98492</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7655,10 +7641,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736197</v>
+        <v>736331</v>
       </c>
       <c r="R62" t="n">
-        <v>6411554</v>
+        <v>6411530</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7722,42 +7708,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203233</v>
+        <v>128203220</v>
       </c>
       <c r="B63" t="n">
-        <v>98454</v>
+        <v>109297</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7766,10 +7752,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736276</v>
+        <v>736295</v>
       </c>
       <c r="R63" t="n">
-        <v>6411531</v>
+        <v>6411551</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7804,6 +7790,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7815,7 +7806,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7833,27 +7824,27 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203237</v>
+        <v>128203144</v>
       </c>
       <c r="B64" t="n">
-        <v>110353</v>
+        <v>109297</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7861,17 +7852,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736283</v>
+        <v>736246</v>
       </c>
       <c r="R64" t="n">
-        <v>6411500</v>
+        <v>6411634</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Överallt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7940,10 +7940,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203186</v>
+        <v>128203233</v>
       </c>
       <c r="B65" t="n">
-        <v>98491</v>
+        <v>98455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7951,26 +7951,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219862</v>
+        <v>219799</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736331</v>
+        <v>736276</v>
       </c>
       <c r="R65" t="n">
-        <v>6411530</v>
+        <v>6411531</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
         <v>128203089</v>
       </c>
       <c r="B66" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>128203243</v>
       </c>
       <c r="B67" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8264,48 +8264,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203239</v>
+        <v>128203209</v>
       </c>
       <c r="B68" t="n">
-        <v>109296</v>
+        <v>98472</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R68" t="n">
-        <v>6411500</v>
+        <v>6411567</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8337,11 +8346,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8353,7 +8357,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8371,10 +8375,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203095</v>
+        <v>128203104</v>
       </c>
       <c r="B69" t="n">
-        <v>109296</v>
+        <v>105406</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,16 +8386,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8406,13 +8410,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736474</v>
+        <v>736325</v>
       </c>
       <c r="R69" t="n">
-        <v>6411596</v>
+        <v>6411730</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8446,7 +8450,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8460,7 +8464,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8478,57 +8482,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203209</v>
+        <v>128203239</v>
       </c>
       <c r="B70" t="n">
-        <v>98471</v>
+        <v>109297</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R70" t="n">
-        <v>6411567</v>
+        <v>6411500</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8560,6 +8555,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203104</v>
+        <v>128203095</v>
       </c>
       <c r="B71" t="n">
-        <v>105405</v>
+        <v>109297</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,16 +8600,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8624,13 +8624,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736325</v>
+        <v>736474</v>
       </c>
       <c r="R71" t="n">
-        <v>6411730</v>
+        <v>6411596</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Spridd. Flera i blom.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8696,35 +8696,44 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128203181</v>
+        <v>128203182</v>
       </c>
       <c r="B72" t="n">
-        <v>109296</v>
+        <v>98448</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8771,7 +8780,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8806,7 +8815,7 @@
         <v>128203166</v>
       </c>
       <c r="B73" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8905,10 +8914,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203182</v>
+        <v>128203187</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8935,7 +8944,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8949,10 +8958,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>736350</v>
+        <v>736331</v>
       </c>
       <c r="R74" t="n">
-        <v>6411491</v>
+        <v>6411530</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8985,11 +8994,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9021,54 +9025,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128203187</v>
+        <v>128203181</v>
       </c>
       <c r="B75" t="n">
-        <v>98447</v>
+        <v>109297</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736331</v>
+        <v>736350</v>
       </c>
       <c r="R75" t="n">
-        <v>6411530</v>
+        <v>6411491</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9101,6 +9096,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9132,57 +9132,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203114</v>
+        <v>128203199</v>
       </c>
       <c r="B76" t="n">
-        <v>98475</v>
+        <v>98455</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>742</v>
+        <v>219799</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736184</v>
+        <v>736314</v>
       </c>
       <c r="R76" t="n">
-        <v>6411805</v>
+        <v>6411572</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9216,7 +9207,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9230,7 +9221,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9248,42 +9239,42 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203023</v>
+        <v>128203086</v>
       </c>
       <c r="B77" t="n">
-        <v>57669</v>
+        <v>98448</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9292,13 +9283,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736365</v>
+        <v>736450</v>
       </c>
       <c r="R77" t="n">
-        <v>6411573</v>
+        <v>6411486</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9359,45 +9350,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203189</v>
+        <v>128203221</v>
       </c>
       <c r="B78" t="n">
-        <v>109296</v>
+        <v>98472</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736335</v>
+        <v>736272</v>
       </c>
       <c r="R78" t="n">
-        <v>6411533</v>
+        <v>6411546</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9461,10 +9461,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203185</v>
+        <v>128203189</v>
       </c>
       <c r="B79" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736331</v>
+        <v>736335</v>
       </c>
       <c r="R79" t="n">
-        <v>6411530</v>
+        <v>6411533</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9532,11 +9532,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9568,10 +9563,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203099</v>
+        <v>128203185</v>
       </c>
       <c r="B80" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9596,29 +9591,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736361</v>
+        <v>736331</v>
       </c>
       <c r="R80" t="n">
-        <v>6411697</v>
+        <v>6411530</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9648,6 +9634,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9679,48 +9670,57 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203199</v>
+        <v>128203099</v>
       </c>
       <c r="B81" t="n">
-        <v>98454</v>
+        <v>109297</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736314</v>
+        <v>736361</v>
       </c>
       <c r="R81" t="n">
-        <v>6411572</v>
+        <v>6411697</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9752,11 +9752,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9768,7 +9763,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9786,37 +9781,37 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203086</v>
+        <v>128203114</v>
       </c>
       <c r="B82" t="n">
-        <v>98447</v>
+        <v>98476</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219798</v>
+        <v>742</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9830,13 +9825,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736450</v>
+        <v>736184</v>
       </c>
       <c r="R82" t="n">
-        <v>6411486</v>
+        <v>6411805</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9868,6 +9863,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,32 +9897,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203221</v>
+        <v>128203023</v>
       </c>
       <c r="B83" t="n">
-        <v>98471</v>
+        <v>57669</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219811</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9930,9 +9930,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736272</v>
+        <v>736365</v>
       </c>
       <c r="R83" t="n">
-        <v>6411546</v>
+        <v>6411573</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10008,37 +10008,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203192</v>
+        <v>128203249</v>
       </c>
       <c r="B84" t="n">
-        <v>105405</v>
+        <v>98448</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736339</v>
+        <v>736192</v>
       </c>
       <c r="R84" t="n">
-        <v>6411571</v>
+        <v>6411467</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10090,11 +10090,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10106,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10127,7 +10122,7 @@
         <v>128203132</v>
       </c>
       <c r="B85" t="n">
-        <v>107354</v>
+        <v>107355</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10235,10 +10230,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203249</v>
+        <v>128203162</v>
       </c>
       <c r="B86" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10265,7 +10260,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10279,13 +10274,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736192</v>
+        <v>736250</v>
       </c>
       <c r="R86" t="n">
-        <v>6411467</v>
+        <v>6411464</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10346,10 +10341,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203162</v>
+        <v>128203111</v>
       </c>
       <c r="B87" t="n">
-        <v>98447</v>
+        <v>98401</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10357,26 +10352,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219798</v>
+        <v>219794</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10390,10 +10385,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736250</v>
+        <v>736184</v>
       </c>
       <c r="R87" t="n">
-        <v>6411464</v>
+        <v>6411805</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10428,6 +10423,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10457,32 +10457,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128203111</v>
+        <v>128203192</v>
       </c>
       <c r="B88" t="n">
-        <v>98400</v>
+        <v>105406</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219794</v>
+        <v>221137</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>736184</v>
+        <v>736339</v>
       </c>
       <c r="R88" t="n">
-        <v>6411805</v>
+        <v>6411571</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10573,10 +10573,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203211</v>
+        <v>128205915</v>
       </c>
       <c r="B89" t="n">
-        <v>99144</v>
+        <v>57669</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10584,37 +10584,46 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736301</v>
+        <v>736315</v>
       </c>
       <c r="R89" t="n">
-        <v>6411564</v>
+        <v>6411597</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10657,7 +10666,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10678,7 +10687,7 @@
         <v>128203165</v>
       </c>
       <c r="B90" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10789,7 +10798,7 @@
         <v>128203081</v>
       </c>
       <c r="B91" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10900,7 +10909,7 @@
         <v>128203225</v>
       </c>
       <c r="B92" t="n">
-        <v>98471</v>
+        <v>98472</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11011,7 +11020,7 @@
         <v>128203197</v>
       </c>
       <c r="B93" t="n">
-        <v>98471</v>
+        <v>98472</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11115,10 +11124,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128205915</v>
+        <v>128203180</v>
       </c>
       <c r="B94" t="n">
-        <v>57669</v>
+        <v>105406</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11126,46 +11135,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>221137</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736315</v>
+        <v>736300</v>
       </c>
       <c r="R94" t="n">
-        <v>6411597</v>
+        <v>6411481</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11197,6 +11197,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11208,7 +11213,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11226,45 +11231,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203180</v>
+        <v>128203156</v>
       </c>
       <c r="B95" t="n">
-        <v>105405</v>
+        <v>98388</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221137</v>
+        <v>223591</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736300</v>
+        <v>736221</v>
       </c>
       <c r="R95" t="n">
-        <v>6411481</v>
+        <v>6411593</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11299,11 +11313,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11315,7 +11324,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11333,57 +11342,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203156</v>
+        <v>128203211</v>
       </c>
       <c r="B96" t="n">
-        <v>98387</v>
+        <v>99145</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>223591</v>
+        <v>222322</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736221</v>
+        <v>736301</v>
       </c>
       <c r="R96" t="n">
-        <v>6411593</v>
+        <v>6411564</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11444,10 +11444,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203087</v>
+        <v>128203246</v>
       </c>
       <c r="B97" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11479,13 +11479,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736474</v>
+        <v>736213</v>
       </c>
       <c r="R97" t="n">
-        <v>6411506</v>
+        <v>6411456</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11515,6 +11515,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11546,32 +11551,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203246</v>
+        <v>128203106</v>
       </c>
       <c r="B98" t="n">
-        <v>109296</v>
+        <v>98472</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11581,13 +11586,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736213</v>
+        <v>736305</v>
       </c>
       <c r="R98" t="n">
-        <v>6411456</v>
+        <v>6411739</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11621,7 +11626,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11635,7 +11640,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11653,45 +11658,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203080</v>
+        <v>128203167</v>
       </c>
       <c r="B99" t="n">
-        <v>109296</v>
+        <v>98448</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736347</v>
+        <v>736275</v>
       </c>
       <c r="R99" t="n">
-        <v>6411466</v>
+        <v>6411455</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11755,32 +11769,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203106</v>
+        <v>128203087</v>
       </c>
       <c r="B100" t="n">
-        <v>98471</v>
+        <v>109297</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11790,10 +11804,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736305</v>
+        <v>736474</v>
       </c>
       <c r="R100" t="n">
-        <v>6411739</v>
+        <v>6411506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11828,11 +11842,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11844,7 +11853,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11862,54 +11871,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203167</v>
+        <v>128203080</v>
       </c>
       <c r="B101" t="n">
-        <v>98447</v>
+        <v>109297</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736275</v>
+        <v>736347</v>
       </c>
       <c r="R101" t="n">
-        <v>6411455</v>
+        <v>6411466</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11973,54 +11973,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203154</v>
+        <v>128203129</v>
       </c>
       <c r="B102" t="n">
-        <v>98377</v>
+        <v>105406</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R102" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12066,7 +12057,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12084,10 +12075,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203126</v>
+        <v>128203154</v>
       </c>
       <c r="B103" t="n">
-        <v>98471</v>
+        <v>98378</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12095,26 +12086,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219811</v>
+        <v>219788</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12128,13 +12119,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R103" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12177,7 +12168,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12195,35 +12186,44 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203129</v>
+        <v>128203126</v>
       </c>
       <c r="B104" t="n">
-        <v>105405</v>
+        <v>98472</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12297,48 +12297,57 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203242</v>
+        <v>128203207</v>
       </c>
       <c r="B105" t="n">
-        <v>109296</v>
+        <v>98472</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736237</v>
+        <v>736300</v>
       </c>
       <c r="R105" t="n">
-        <v>6411484</v>
+        <v>6411576</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12370,11 +12379,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12386,7 +12390,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12404,10 +12408,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203207</v>
+        <v>128203177</v>
       </c>
       <c r="B106" t="n">
-        <v>98471</v>
+        <v>98455</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12415,33 +12419,24 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12451,10 +12446,10 @@
         <v>736300</v>
       </c>
       <c r="R106" t="n">
-        <v>6411576</v>
+        <v>6411481</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12486,6 +12481,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12515,10 +12515,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203177</v>
+        <v>128203234</v>
       </c>
       <c r="B107" t="n">
-        <v>98454</v>
+        <v>98448</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12526,16 +12526,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12543,20 +12543,29 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736300</v>
+        <v>736279</v>
       </c>
       <c r="R107" t="n">
-        <v>6411481</v>
+        <v>6411517</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12588,11 +12597,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12604,7 +12608,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12622,57 +12626,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203234</v>
+        <v>128203242</v>
       </c>
       <c r="B108" t="n">
-        <v>98447</v>
+        <v>109297</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736279</v>
+        <v>736237</v>
       </c>
       <c r="R108" t="n">
-        <v>6411517</v>
+        <v>6411484</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12702,6 +12697,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12733,10 +12733,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203255</v>
+        <v>128203107</v>
       </c>
       <c r="B109" t="n">
-        <v>109296</v>
+        <v>105406</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12744,16 +12744,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736200</v>
+        <v>736305</v>
       </c>
       <c r="R109" t="n">
-        <v>6411456</v>
+        <v>6411739</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12806,6 +12806,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12817,7 +12822,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12835,10 +12840,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203107</v>
+        <v>128203255</v>
       </c>
       <c r="B110" t="n">
-        <v>105405</v>
+        <v>109297</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12846,16 +12851,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12870,10 +12875,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736305</v>
+        <v>736200</v>
       </c>
       <c r="R110" t="n">
-        <v>6411739</v>
+        <v>6411456</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12908,11 +12913,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12942,45 +12942,54 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128203161</v>
+        <v>128203160</v>
       </c>
       <c r="B111" t="n">
-        <v>109296</v>
+        <v>98448</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>736250</v>
+        <v>736240</v>
       </c>
       <c r="R111" t="n">
-        <v>6411464</v>
+        <v>6411466</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13044,48 +13053,57 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128203236</v>
+        <v>128203138</v>
       </c>
       <c r="B112" t="n">
-        <v>109296</v>
+        <v>98455</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>736279</v>
+        <v>736231</v>
       </c>
       <c r="R112" t="n">
-        <v>6411517</v>
+        <v>6411673</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13117,11 +13135,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13133,7 +13146,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13151,10 +13164,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128203160</v>
+        <v>128203094</v>
       </c>
       <c r="B113" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13195,10 +13208,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>736240</v>
+        <v>736498</v>
       </c>
       <c r="R113" t="n">
-        <v>6411466</v>
+        <v>6411566</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13262,57 +13275,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128203138</v>
+        <v>128203161</v>
       </c>
       <c r="B114" t="n">
-        <v>98454</v>
+        <v>109297</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>736231</v>
+        <v>736250</v>
       </c>
       <c r="R114" t="n">
-        <v>6411673</v>
+        <v>6411464</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13355,7 +13359,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13373,57 +13377,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128203094</v>
+        <v>128203236</v>
       </c>
       <c r="B115" t="n">
-        <v>98447</v>
+        <v>109297</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>736498</v>
+        <v>736279</v>
       </c>
       <c r="R115" t="n">
-        <v>6411566</v>
+        <v>6411517</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13453,6 +13448,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13487,7 +13487,7 @@
         <v>128203134</v>
       </c>
       <c r="B116" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>128203247</v>
       </c>
       <c r="B117" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>128203215</v>
       </c>
       <c r="B118" t="n">
-        <v>98454</v>
+        <v>98455</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>128203101</v>
       </c>
       <c r="B119" t="n">
-        <v>98377</v>
+        <v>98378</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>128203159</v>
       </c>
       <c r="B120" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14026,48 +14026,57 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128203230</v>
+        <v>128203213</v>
       </c>
       <c r="B121" t="n">
-        <v>109296</v>
+        <v>98472</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>736270</v>
+        <v>736301</v>
       </c>
       <c r="R121" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14099,11 +14108,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14115,7 +14119,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14133,57 +14137,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128203213</v>
+        <v>128203230</v>
       </c>
       <c r="B122" t="n">
-        <v>98471</v>
+        <v>109297</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>736301</v>
+        <v>736270</v>
       </c>
       <c r="R122" t="n">
-        <v>6411564</v>
+        <v>6411530</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14215,6 +14210,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14244,27 +14244,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128203151</v>
+        <v>128203235</v>
       </c>
       <c r="B123" t="n">
-        <v>109296</v>
+        <v>110354</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -14279,13 +14279,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>736248</v>
+        <v>736279</v>
       </c>
       <c r="R123" t="n">
-        <v>6411616</v>
+        <v>6411517</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14315,11 +14315,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14351,48 +14346,57 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203091</v>
+        <v>128203190</v>
       </c>
       <c r="B124" t="n">
-        <v>109296</v>
+        <v>98448</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R124" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14453,10 +14457,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203190</v>
+        <v>128203216</v>
       </c>
       <c r="B125" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14497,10 +14501,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736335</v>
+        <v>736297</v>
       </c>
       <c r="R125" t="n">
-        <v>6411533</v>
+        <v>6411559</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14533,6 +14537,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14564,10 +14573,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203216</v>
+        <v>128203092</v>
       </c>
       <c r="B126" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14594,7 +14603,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14608,13 +14617,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736297</v>
+        <v>736520</v>
       </c>
       <c r="R126" t="n">
-        <v>6411559</v>
+        <v>6411544</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14644,11 +14653,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14680,54 +14684,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203092</v>
+        <v>128203151</v>
       </c>
       <c r="B127" t="n">
-        <v>98447</v>
+        <v>109297</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736520</v>
+        <v>736248</v>
       </c>
       <c r="R127" t="n">
-        <v>6411544</v>
+        <v>6411616</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14760,6 +14755,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14791,27 +14791,27 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203235</v>
+        <v>128203091</v>
       </c>
       <c r="B128" t="n">
-        <v>110353</v>
+        <v>109297</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -14826,13 +14826,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736279</v>
+        <v>736520</v>
       </c>
       <c r="R128" t="n">
-        <v>6411517</v>
+        <v>6411544</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203093</v>
+        <v>128203112</v>
       </c>
       <c r="B129" t="n">
-        <v>109296</v>
+        <v>98455</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736498</v>
+        <v>736184</v>
       </c>
       <c r="R129" t="n">
-        <v>6411566</v>
+        <v>6411805</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,6 +14966,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14977,7 +14982,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -14995,10 +15000,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203112</v>
+        <v>128203113</v>
       </c>
       <c r="B130" t="n">
-        <v>98454</v>
+        <v>98472</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15006,21 +15011,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15102,10 +15107,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203113</v>
+        <v>128203252</v>
       </c>
       <c r="B131" t="n">
-        <v>98471</v>
+        <v>98492</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15113,37 +15118,46 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219811</v>
+        <v>219862</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>736184</v>
+        <v>736193</v>
       </c>
       <c r="R131" t="n">
-        <v>6411805</v>
+        <v>6411456</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15175,11 +15189,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15191,7 +15200,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15209,57 +15218,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203252</v>
+        <v>128203093</v>
       </c>
       <c r="B132" t="n">
-        <v>98491</v>
+        <v>109297</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736193</v>
+        <v>736498</v>
       </c>
       <c r="R132" t="n">
-        <v>6411456</v>
+        <v>6411566</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>128203178</v>
       </c>
       <c r="B133" t="n">
-        <v>97996</v>
+        <v>97997</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15427,48 +15427,57 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203083</v>
+        <v>128203139</v>
       </c>
       <c r="B134" t="n">
-        <v>109296</v>
+        <v>98474</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220299</v>
+        <v>741</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Wahlenb.) K. Richt.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736442</v>
+        <v>736244</v>
       </c>
       <c r="R134" t="n">
-        <v>6411479</v>
+        <v>6411666</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15529,48 +15538,57 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203164</v>
+        <v>128203228</v>
       </c>
       <c r="B135" t="n">
-        <v>109296</v>
+        <v>98455</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736260</v>
+        <v>736263</v>
       </c>
       <c r="R135" t="n">
-        <v>6411450</v>
+        <v>6411533</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15613,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15631,10 +15649,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203228</v>
+        <v>128203127</v>
       </c>
       <c r="B136" t="n">
-        <v>98454</v>
+        <v>98455</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15661,7 +15679,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15675,10 +15693,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736263</v>
+        <v>736239</v>
       </c>
       <c r="R136" t="n">
-        <v>6411533</v>
+        <v>6411738</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15724,7 +15742,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15742,57 +15760,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203127</v>
+        <v>128203083</v>
       </c>
       <c r="B137" t="n">
-        <v>98454</v>
+        <v>109297</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736239</v>
+        <v>736442</v>
       </c>
       <c r="R137" t="n">
-        <v>6411738</v>
+        <v>6411479</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15835,7 +15844,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15853,57 +15862,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203139</v>
+        <v>128203164</v>
       </c>
       <c r="B138" t="n">
-        <v>98473</v>
+        <v>109297</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>741</v>
+        <v>220299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736244</v>
+        <v>736260</v>
       </c>
       <c r="R138" t="n">
-        <v>6411666</v>
+        <v>6411450</v>
       </c>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15964,45 +15964,54 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203085</v>
+        <v>128203084</v>
       </c>
       <c r="B139" t="n">
-        <v>109296</v>
+        <v>98448</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736450</v>
+        <v>736442</v>
       </c>
       <c r="R139" t="n">
-        <v>6411486</v>
+        <v>6411479</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16066,10 +16075,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203084</v>
+        <v>128203223</v>
       </c>
       <c r="B140" t="n">
-        <v>98447</v>
+        <v>98378</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16077,26 +16086,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16110,13 +16119,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736442</v>
+        <v>736272</v>
       </c>
       <c r="R140" t="n">
-        <v>6411479</v>
+        <v>6411536</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16159,7 +16168,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16177,10 +16186,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203223</v>
+        <v>128203231</v>
       </c>
       <c r="B141" t="n">
-        <v>98377</v>
+        <v>98448</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16188,26 +16197,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16221,10 +16230,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736272</v>
+        <v>736270</v>
       </c>
       <c r="R141" t="n">
-        <v>6411536</v>
+        <v>6411530</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16270,7 +16279,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16288,57 +16297,48 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203231</v>
+        <v>128203085</v>
       </c>
       <c r="B142" t="n">
-        <v>98447</v>
+        <v>109297</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736270</v>
+        <v>736450</v>
       </c>
       <c r="R142" t="n">
-        <v>6411530</v>
+        <v>6411486</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>128203240</v>
       </c>
       <c r="B143" t="n">
-        <v>109296</v>
+        <v>109297</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,10 +6400,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203259</v>
+        <v>128203088</v>
       </c>
       <c r="B51" t="n">
-        <v>110354</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,34 +6411,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R51" t="n">
-        <v>6411455</v>
+        <v>6411506</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6471,11 +6480,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6507,10 +6511,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203088</v>
+        <v>128203259</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>110354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6518,43 +6522,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736474</v>
+        <v>736176</v>
       </c>
       <c r="R52" t="n">
-        <v>6411506</v>
+        <v>6411455</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6587,6 +6582,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6729,27 +6729,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203256</v>
+        <v>128203179</v>
       </c>
       <c r="B54" t="n">
-        <v>109297</v>
+        <v>99511</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736176</v>
+        <v>736300</v>
       </c>
       <c r="R54" t="n">
-        <v>6411455</v>
+        <v>6411481</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6831,48 +6831,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203241</v>
+        <v>128203195</v>
       </c>
       <c r="B55" t="n">
-        <v>109297</v>
+        <v>98378</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736223</v>
+        <v>736314</v>
       </c>
       <c r="R55" t="n">
-        <v>6411512</v>
+        <v>6411572</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6906,7 +6915,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6920,7 +6929,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6938,10 +6947,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203195</v>
+        <v>128203096</v>
       </c>
       <c r="B56" t="n">
-        <v>98378</v>
+        <v>98448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6949,26 +6958,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6982,13 +6991,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736314</v>
+        <v>736474</v>
       </c>
       <c r="R56" t="n">
-        <v>6411572</v>
+        <v>6411596</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7022,7 +7031,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7036,7 +7045,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7054,7 +7063,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203096</v>
+        <v>128203100</v>
       </c>
       <c r="B57" t="n">
         <v>98448</v>
@@ -7084,7 +7093,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7098,10 +7107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736474</v>
+        <v>736361</v>
       </c>
       <c r="R57" t="n">
-        <v>6411596</v>
+        <v>6411697</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7134,11 +7143,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7170,54 +7174,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203100</v>
+        <v>128203241</v>
       </c>
       <c r="B58" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736361</v>
+        <v>736223</v>
       </c>
       <c r="R58" t="n">
-        <v>6411697</v>
+        <v>6411512</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7250,6 +7245,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7281,27 +7281,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203179</v>
+        <v>128203256</v>
       </c>
       <c r="B59" t="n">
-        <v>99511</v>
+        <v>109297</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736300</v>
+        <v>736176</v>
       </c>
       <c r="R59" t="n">
-        <v>6411481</v>
+        <v>6411455</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203021</v>
+        <v>128203144</v>
       </c>
       <c r="B60" t="n">
-        <v>57669</v>
+        <v>109297</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,27 +7394,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7423,13 +7427,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736197</v>
+        <v>736246</v>
       </c>
       <c r="R60" t="n">
-        <v>6411554</v>
+        <v>6411634</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7459,6 +7463,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7490,48 +7499,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203237</v>
+        <v>128203021</v>
       </c>
       <c r="B61" t="n">
-        <v>110354</v>
+        <v>57669</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736283</v>
+        <v>736197</v>
       </c>
       <c r="R61" t="n">
-        <v>6411500</v>
+        <v>6411554</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7561,11 +7575,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7597,10 +7606,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203186</v>
+        <v>128203237</v>
       </c>
       <c r="B62" t="n">
-        <v>98492</v>
+        <v>110354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7608,46 +7617,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219862</v>
+        <v>219677</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736331</v>
+        <v>736283</v>
       </c>
       <c r="R62" t="n">
-        <v>6411530</v>
+        <v>6411500</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7677,6 +7677,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7708,42 +7713,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203220</v>
+        <v>128203233</v>
       </c>
       <c r="B63" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7752,10 +7757,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736295</v>
+        <v>736276</v>
       </c>
       <c r="R63" t="n">
-        <v>6411551</v>
+        <v>6411531</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7790,11 +7795,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7824,42 +7824,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203144</v>
+        <v>128203186</v>
       </c>
       <c r="B64" t="n">
-        <v>109297</v>
+        <v>98492</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7868,13 +7868,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736246</v>
+        <v>736331</v>
       </c>
       <c r="R64" t="n">
-        <v>6411634</v>
+        <v>6411530</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7904,11 +7904,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7940,42 +7935,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203233</v>
+        <v>128203220</v>
       </c>
       <c r="B65" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736276</v>
+        <v>736295</v>
       </c>
       <c r="R65" t="n">
-        <v>6411531</v>
+        <v>6411551</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8022,6 +8017,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8264,57 +8264,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203209</v>
+        <v>128203239</v>
       </c>
       <c r="B68" t="n">
-        <v>98472</v>
+        <v>109297</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R68" t="n">
-        <v>6411567</v>
+        <v>6411500</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8346,6 +8337,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8357,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8375,10 +8371,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203104</v>
+        <v>128203095</v>
       </c>
       <c r="B69" t="n">
-        <v>105406</v>
+        <v>109297</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8386,16 +8382,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8410,13 +8406,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736325</v>
+        <v>736474</v>
       </c>
       <c r="R69" t="n">
-        <v>6411730</v>
+        <v>6411596</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8450,7 +8446,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Spridd. Flera i blom.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8464,7 +8460,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8482,48 +8478,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203239</v>
+        <v>128203209</v>
       </c>
       <c r="B70" t="n">
-        <v>109297</v>
+        <v>98472</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R70" t="n">
-        <v>6411500</v>
+        <v>6411567</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8555,11 +8560,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203095</v>
+        <v>128203104</v>
       </c>
       <c r="B71" t="n">
-        <v>109297</v>
+        <v>105406</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,16 +8600,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8624,13 +8624,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736474</v>
+        <v>736325</v>
       </c>
       <c r="R71" t="n">
-        <v>6411596</v>
+        <v>6411730</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8696,44 +8696,35 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128203182</v>
+        <v>128203181</v>
       </c>
       <c r="B72" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8780,7 +8771,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Stig över våtmark; avsnitslat.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8914,7 +8905,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203187</v>
+        <v>128203182</v>
       </c>
       <c r="B74" t="n">
         <v>98448</v>
@@ -8944,7 +8935,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8958,10 +8949,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>736331</v>
+        <v>736350</v>
       </c>
       <c r="R74" t="n">
-        <v>6411530</v>
+        <v>6411491</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8994,6 +8985,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9025,45 +9021,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128203181</v>
+        <v>128203187</v>
       </c>
       <c r="B75" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736350</v>
+        <v>736331</v>
       </c>
       <c r="R75" t="n">
-        <v>6411491</v>
+        <v>6411530</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9096,11 +9101,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9132,32 +9132,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203199</v>
+        <v>128203185</v>
       </c>
       <c r="B76" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9167,13 +9167,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736314</v>
+        <v>736331</v>
       </c>
       <c r="R76" t="n">
-        <v>6411572</v>
+        <v>6411530</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9239,57 +9239,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203086</v>
+        <v>128203189</v>
       </c>
       <c r="B77" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736450</v>
+        <v>736335</v>
       </c>
       <c r="R77" t="n">
-        <v>6411486</v>
+        <v>6411533</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9350,10 +9341,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203221</v>
+        <v>128203199</v>
       </c>
       <c r="B78" t="n">
-        <v>98472</v>
+        <v>98455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9361,46 +9352,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736272</v>
+        <v>736314</v>
       </c>
       <c r="R78" t="n">
-        <v>6411546</v>
+        <v>6411572</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9432,6 +9414,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9443,7 +9430,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9461,7 +9448,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203189</v>
+        <v>128203099</v>
       </c>
       <c r="B79" t="n">
         <v>109297</v>
@@ -9489,20 +9476,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736335</v>
+        <v>736361</v>
       </c>
       <c r="R79" t="n">
-        <v>6411533</v>
+        <v>6411697</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9563,48 +9559,57 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203185</v>
+        <v>128203086</v>
       </c>
       <c r="B80" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736331</v>
+        <v>736450</v>
       </c>
       <c r="R80" t="n">
-        <v>6411530</v>
+        <v>6411486</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9634,11 +9639,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9670,42 +9670,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203099</v>
+        <v>128203221</v>
       </c>
       <c r="B81" t="n">
-        <v>109297</v>
+        <v>98472</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9714,13 +9714,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736361</v>
+        <v>736272</v>
       </c>
       <c r="R81" t="n">
-        <v>6411697</v>
+        <v>6411546</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9781,10 +9781,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203114</v>
+        <v>128203023</v>
       </c>
       <c r="B82" t="n">
-        <v>98476</v>
+        <v>57669</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,31 +9792,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>742</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9825,13 +9825,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736184</v>
+        <v>736365</v>
       </c>
       <c r="R82" t="n">
-        <v>6411805</v>
+        <v>6411573</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9863,11 +9863,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9879,7 +9874,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,10 +9892,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203023</v>
+        <v>128203114</v>
       </c>
       <c r="B83" t="n">
-        <v>57669</v>
+        <v>98476</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9908,31 +9903,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>742</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9936,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736365</v>
+        <v>736184</v>
       </c>
       <c r="R83" t="n">
-        <v>6411573</v>
+        <v>6411805</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9979,6 +9974,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10008,32 +10008,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203249</v>
+        <v>128203132</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>107355</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736192</v>
+        <v>736242</v>
       </c>
       <c r="R84" t="n">
-        <v>6411467</v>
+        <v>6411713</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10119,32 +10119,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203132</v>
+        <v>128203249</v>
       </c>
       <c r="B85" t="n">
-        <v>107355</v>
+        <v>98448</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10163,10 +10163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736242</v>
+        <v>736192</v>
       </c>
       <c r="R85" t="n">
-        <v>6411713</v>
+        <v>6411467</v>
       </c>
       <c r="S85" t="n">
         <v>3</v>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B89" t="n">
-        <v>57669</v>
+        <v>98448</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R89" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203165</v>
+        <v>128203081</v>
       </c>
       <c r="B90" t="n">
         <v>98448</v>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736260</v>
+        <v>736347</v>
       </c>
       <c r="R90" t="n">
-        <v>6411450</v>
+        <v>6411466</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10795,10 +10795,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203081</v>
+        <v>128203225</v>
       </c>
       <c r="B91" t="n">
-        <v>98448</v>
+        <v>98472</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,21 +10806,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10839,13 +10839,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736347</v>
+        <v>736263</v>
       </c>
       <c r="R91" t="n">
-        <v>6411466</v>
+        <v>6411533</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,7 +10906,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203225</v>
+        <v>128203197</v>
       </c>
       <c r="B92" t="n">
         <v>98472</v>
@@ -10934,29 +10934,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736263</v>
+        <v>736314</v>
       </c>
       <c r="R92" t="n">
-        <v>6411533</v>
+        <v>6411572</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10988,6 +10979,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10999,7 +10995,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11017,45 +11013,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203197</v>
+        <v>128205915</v>
       </c>
       <c r="B93" t="n">
-        <v>98472</v>
+        <v>57669</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219811</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736314</v>
+        <v>736315</v>
       </c>
       <c r="R93" t="n">
-        <v>6411572</v>
+        <v>6411597</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11090,11 +11095,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11124,45 +11124,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203180</v>
+        <v>128203156</v>
       </c>
       <c r="B94" t="n">
-        <v>105406</v>
+        <v>98388</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221137</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736300</v>
+        <v>736221</v>
       </c>
       <c r="R94" t="n">
-        <v>6411481</v>
+        <v>6411593</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11197,11 +11206,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11213,7 +11217,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11231,54 +11235,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203156</v>
+        <v>128203180</v>
       </c>
       <c r="B95" t="n">
-        <v>98388</v>
+        <v>105406</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>223591</v>
+        <v>221137</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736221</v>
+        <v>736300</v>
       </c>
       <c r="R95" t="n">
-        <v>6411593</v>
+        <v>6411481</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11313,6 +11308,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203246</v>
+        <v>128203087</v>
       </c>
       <c r="B97" t="n">
         <v>109297</v>
@@ -11479,13 +11479,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736213</v>
+        <v>736474</v>
       </c>
       <c r="R97" t="n">
-        <v>6411456</v>
+        <v>6411506</v>
       </c>
       <c r="S97" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11515,11 +11515,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11551,32 +11546,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203106</v>
+        <v>128203246</v>
       </c>
       <c r="B98" t="n">
-        <v>98472</v>
+        <v>109297</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11586,13 +11581,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736305</v>
+        <v>736213</v>
       </c>
       <c r="R98" t="n">
-        <v>6411739</v>
+        <v>6411456</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11626,7 +11621,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11640,7 +11635,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11658,54 +11653,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203167</v>
+        <v>128203080</v>
       </c>
       <c r="B99" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736275</v>
+        <v>736347</v>
       </c>
       <c r="R99" t="n">
-        <v>6411455</v>
+        <v>6411466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11769,32 +11755,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203087</v>
+        <v>128203106</v>
       </c>
       <c r="B100" t="n">
-        <v>109297</v>
+        <v>98472</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11804,10 +11790,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736474</v>
+        <v>736305</v>
       </c>
       <c r="R100" t="n">
-        <v>6411506</v>
+        <v>6411739</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11842,6 +11828,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11853,7 +11844,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11871,45 +11862,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203080</v>
+        <v>128203167</v>
       </c>
       <c r="B101" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736347</v>
+        <v>736275</v>
       </c>
       <c r="R101" t="n">
-        <v>6411466</v>
+        <v>6411455</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11973,45 +11973,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203129</v>
+        <v>128203154</v>
       </c>
       <c r="B102" t="n">
-        <v>105406</v>
+        <v>98378</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221137</v>
+        <v>219788</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R102" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12057,7 +12066,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12075,10 +12084,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203154</v>
+        <v>128203126</v>
       </c>
       <c r="B103" t="n">
-        <v>98378</v>
+        <v>98472</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12086,26 +12095,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219788</v>
+        <v>219811</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12119,13 +12128,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R103" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12168,7 +12177,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12186,44 +12195,35 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203126</v>
+        <v>128203129</v>
       </c>
       <c r="B104" t="n">
-        <v>98472</v>
+        <v>105406</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12626,10 +12626,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203242</v>
+        <v>128203107</v>
       </c>
       <c r="B108" t="n">
-        <v>109297</v>
+        <v>105406</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12637,16 +12637,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12661,10 +12661,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736237</v>
+        <v>736305</v>
       </c>
       <c r="R108" t="n">
-        <v>6411484</v>
+        <v>6411739</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12733,10 +12733,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203107</v>
+        <v>128203255</v>
       </c>
       <c r="B109" t="n">
-        <v>105406</v>
+        <v>109297</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12744,16 +12744,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736305</v>
+        <v>736200</v>
       </c>
       <c r="R109" t="n">
-        <v>6411739</v>
+        <v>6411456</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12806,11 +12806,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12822,7 +12817,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12840,7 +12835,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203255</v>
+        <v>128203242</v>
       </c>
       <c r="B110" t="n">
         <v>109297</v>
@@ -12875,10 +12870,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736200</v>
+        <v>736237</v>
       </c>
       <c r="R110" t="n">
-        <v>6411456</v>
+        <v>6411484</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12911,6 +12906,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13275,7 +13275,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128203161</v>
+        <v>128203236</v>
       </c>
       <c r="B114" t="n">
         <v>109297</v>
@@ -13310,13 +13310,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>736250</v>
+        <v>736279</v>
       </c>
       <c r="R114" t="n">
-        <v>6411464</v>
+        <v>6411517</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13346,6 +13346,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13377,7 +13382,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128203236</v>
+        <v>128203161</v>
       </c>
       <c r="B115" t="n">
         <v>109297</v>
@@ -13412,13 +13417,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>736279</v>
+        <v>736250</v>
       </c>
       <c r="R115" t="n">
-        <v>6411517</v>
+        <v>6411464</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13448,11 +13453,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13484,42 +13484,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128203134</v>
+        <v>128203215</v>
       </c>
       <c r="B116" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13528,13 +13528,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>736242</v>
+        <v>736301</v>
       </c>
       <c r="R116" t="n">
-        <v>6411713</v>
+        <v>6411564</v>
       </c>
       <c r="S116" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128203247</v>
+        <v>128203134</v>
       </c>
       <c r="B117" t="n">
         <v>109297</v>
@@ -13623,17 +13623,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>736192</v>
+        <v>736242</v>
       </c>
       <c r="R117" t="n">
-        <v>6411467</v>
+        <v>6411713</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -13679,7 +13688,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13697,57 +13706,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128203215</v>
+        <v>128203247</v>
       </c>
       <c r="B118" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>736301</v>
+        <v>736192</v>
       </c>
       <c r="R118" t="n">
-        <v>6411564</v>
+        <v>6411467</v>
       </c>
       <c r="S118" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13808,57 +13808,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128203101</v>
+        <v>128203159</v>
       </c>
       <c r="B119" t="n">
-        <v>98378</v>
+        <v>109297</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>736358</v>
+        <v>736240</v>
       </c>
       <c r="R119" t="n">
-        <v>6411725</v>
+        <v>6411466</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13890,6 +13881,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13901,7 +13897,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13919,48 +13915,57 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128203159</v>
+        <v>128203101</v>
       </c>
       <c r="B120" t="n">
-        <v>109297</v>
+        <v>98378</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>736240</v>
+        <v>736358</v>
       </c>
       <c r="R120" t="n">
-        <v>6411466</v>
+        <v>6411725</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13992,11 +13997,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14346,57 +14346,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203190</v>
+        <v>128203091</v>
       </c>
       <c r="B124" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736335</v>
+        <v>736520</v>
       </c>
       <c r="R124" t="n">
-        <v>6411533</v>
+        <v>6411544</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14457,57 +14448,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203216</v>
+        <v>128203151</v>
       </c>
       <c r="B125" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736297</v>
+        <v>736248</v>
       </c>
       <c r="R125" t="n">
-        <v>6411559</v>
+        <v>6411616</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14541,7 +14523,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Kant av våtmark.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14573,7 +14555,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203092</v>
+        <v>128203190</v>
       </c>
       <c r="B126" t="n">
         <v>98448</v>
@@ -14603,7 +14585,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14617,13 +14599,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R126" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14684,48 +14666,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203151</v>
+        <v>128203216</v>
       </c>
       <c r="B127" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736248</v>
+        <v>736297</v>
       </c>
       <c r="R127" t="n">
-        <v>6411616</v>
+        <v>6411559</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14759,7 +14750,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14791,35 +14782,44 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203091</v>
+        <v>128203092</v>
       </c>
       <c r="B128" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -15427,57 +15427,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203139</v>
+        <v>128203164</v>
       </c>
       <c r="B134" t="n">
-        <v>98474</v>
+        <v>109297</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>741</v>
+        <v>220299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736244</v>
+        <v>736260</v>
       </c>
       <c r="R134" t="n">
-        <v>6411666</v>
+        <v>6411450</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15862,48 +15853,57 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203164</v>
+        <v>128203139</v>
       </c>
       <c r="B138" t="n">
-        <v>109297</v>
+        <v>98474</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220299</v>
+        <v>741</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Wahlenb.) K. Richt.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736260</v>
+        <v>736244</v>
       </c>
       <c r="R138" t="n">
-        <v>6411450</v>
+        <v>6411666</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15964,57 +15964,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203084</v>
+        <v>128203240</v>
       </c>
       <c r="B139" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736442</v>
+        <v>736238</v>
       </c>
       <c r="R139" t="n">
-        <v>6411479</v>
+        <v>6411496</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16044,6 +16035,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16075,10 +16071,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203223</v>
+        <v>128203084</v>
       </c>
       <c r="B140" t="n">
-        <v>98378</v>
+        <v>98448</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16086,26 +16082,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16119,13 +16115,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736272</v>
+        <v>736442</v>
       </c>
       <c r="R140" t="n">
-        <v>6411536</v>
+        <v>6411479</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16168,7 +16164,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16186,10 +16182,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203231</v>
+        <v>128203223</v>
       </c>
       <c r="B141" t="n">
-        <v>98448</v>
+        <v>98378</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16197,26 +16193,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16230,10 +16226,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736270</v>
+        <v>736272</v>
       </c>
       <c r="R141" t="n">
-        <v>6411530</v>
+        <v>6411536</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16279,7 +16275,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16297,48 +16293,57 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203085</v>
+        <v>128203231</v>
       </c>
       <c r="B142" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736450</v>
+        <v>736270</v>
       </c>
       <c r="R142" t="n">
-        <v>6411486</v>
+        <v>6411530</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16399,7 +16404,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128203240</v>
+        <v>128203085</v>
       </c>
       <c r="B143" t="n">
         <v>109297</v>
@@ -16434,13 +16439,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>736238</v>
+        <v>736450</v>
       </c>
       <c r="R143" t="n">
-        <v>6411496</v>
+        <v>6411486</v>
       </c>
       <c r="S143" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16470,11 +16475,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,10 +6400,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203088</v>
+        <v>128203259</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>110354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,43 +6411,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736474</v>
+        <v>736176</v>
       </c>
       <c r="R51" t="n">
-        <v>6411506</v>
+        <v>6411455</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6480,6 +6471,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6511,27 +6507,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203259</v>
+        <v>128203131</v>
       </c>
       <c r="B52" t="n">
-        <v>110354</v>
+        <v>105406</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219677</v>
+        <v>221137</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6539,20 +6535,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736176</v>
+        <v>736256</v>
       </c>
       <c r="R52" t="n">
-        <v>6411455</v>
+        <v>6411743</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6584,11 +6589,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Våtmark mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6618,37 +6618,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128203131</v>
+        <v>128203088</v>
       </c>
       <c r="B53" t="n">
-        <v>105406</v>
+        <v>98448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6662,13 +6662,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736256</v>
+        <v>736474</v>
       </c>
       <c r="R53" t="n">
-        <v>6411743</v>
+        <v>6411506</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Våtmark mellan strandvallar.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -10008,32 +10008,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203132</v>
+        <v>128203249</v>
       </c>
       <c r="B84" t="n">
-        <v>107355</v>
+        <v>98448</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736242</v>
+        <v>736192</v>
       </c>
       <c r="R84" t="n">
-        <v>6411713</v>
+        <v>6411467</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203249</v>
+        <v>128203162</v>
       </c>
       <c r="B85" t="n">
         <v>98448</v>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10163,13 +10163,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736192</v>
+        <v>736250</v>
       </c>
       <c r="R85" t="n">
-        <v>6411467</v>
+        <v>6411464</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10230,10 +10230,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203162</v>
+        <v>128203111</v>
       </c>
       <c r="B86" t="n">
-        <v>98448</v>
+        <v>98401</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,26 +10241,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>219794</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10274,10 +10274,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736250</v>
+        <v>736184</v>
       </c>
       <c r="R86" t="n">
-        <v>6411464</v>
+        <v>6411805</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10312,6 +10312,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10323,7 +10328,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10341,37 +10346,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203111</v>
+        <v>128203132</v>
       </c>
       <c r="B87" t="n">
-        <v>98401</v>
+        <v>107355</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219794</v>
+        <v>220079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10385,13 +10390,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736184</v>
+        <v>736242</v>
       </c>
       <c r="R87" t="n">
-        <v>6411805</v>
+        <v>6411713</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10423,11 +10428,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11444,32 +11444,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203087</v>
+        <v>128203106</v>
       </c>
       <c r="B97" t="n">
-        <v>109297</v>
+        <v>98472</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736474</v>
+        <v>736305</v>
       </c>
       <c r="R97" t="n">
-        <v>6411506</v>
+        <v>6411739</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11517,6 +11517,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11528,7 +11533,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11546,48 +11551,57 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203246</v>
+        <v>128203167</v>
       </c>
       <c r="B98" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736213</v>
+        <v>736275</v>
       </c>
       <c r="R98" t="n">
-        <v>6411456</v>
+        <v>6411455</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11617,11 +11631,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11653,7 +11662,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203080</v>
+        <v>128203246</v>
       </c>
       <c r="B99" t="n">
         <v>109297</v>
@@ -11688,13 +11697,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736347</v>
+        <v>736213</v>
       </c>
       <c r="R99" t="n">
-        <v>6411466</v>
+        <v>6411456</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11724,6 +11733,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11755,32 +11769,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203106</v>
+        <v>128203087</v>
       </c>
       <c r="B100" t="n">
-        <v>98472</v>
+        <v>109297</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11790,10 +11804,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736305</v>
+        <v>736474</v>
       </c>
       <c r="R100" t="n">
-        <v>6411739</v>
+        <v>6411506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11828,11 +11842,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11844,7 +11853,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11862,54 +11871,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203167</v>
+        <v>128203080</v>
       </c>
       <c r="B101" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736275</v>
+        <v>736347</v>
       </c>
       <c r="R101" t="n">
-        <v>6411455</v>
+        <v>6411466</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,10 +6400,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203259</v>
+        <v>128203088</v>
       </c>
       <c r="B51" t="n">
-        <v>110354</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,34 +6411,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R51" t="n">
-        <v>6411455</v>
+        <v>6411506</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6471,11 +6480,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6507,27 +6511,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203131</v>
+        <v>128203259</v>
       </c>
       <c r="B52" t="n">
-        <v>105406</v>
+        <v>110354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221137</v>
+        <v>219677</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6535,29 +6539,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736256</v>
+        <v>736176</v>
       </c>
       <c r="R52" t="n">
-        <v>6411743</v>
+        <v>6411455</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6589,6 +6584,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Våtmark mellan strandvallar.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6618,37 +6618,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128203088</v>
+        <v>128203131</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>105406</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6662,13 +6662,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736474</v>
+        <v>736256</v>
       </c>
       <c r="R53" t="n">
-        <v>6411506</v>
+        <v>6411743</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Våtmark mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203144</v>
+        <v>128203021</v>
       </c>
       <c r="B60" t="n">
-        <v>109297</v>
+        <v>57669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,31 +7394,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7427,13 +7423,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736246</v>
+        <v>736197</v>
       </c>
       <c r="R60" t="n">
-        <v>6411634</v>
+        <v>6411554</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7463,11 +7459,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7499,38 +7490,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203021</v>
+        <v>128203233</v>
       </c>
       <c r="B61" t="n">
-        <v>57669</v>
+        <v>98455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>219799</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7539,10 +7534,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736197</v>
+        <v>736276</v>
       </c>
       <c r="R61" t="n">
-        <v>6411554</v>
+        <v>6411531</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7588,7 +7583,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7606,10 +7601,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203237</v>
+        <v>128203186</v>
       </c>
       <c r="B62" t="n">
-        <v>110354</v>
+        <v>98492</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,37 +7612,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219677</v>
+        <v>219862</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736283</v>
+        <v>736331</v>
       </c>
       <c r="R62" t="n">
-        <v>6411500</v>
+        <v>6411530</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7677,11 +7681,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7713,42 +7712,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203233</v>
+        <v>128203144</v>
       </c>
       <c r="B63" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7757,13 +7756,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736276</v>
+        <v>736246</v>
       </c>
       <c r="R63" t="n">
-        <v>6411531</v>
+        <v>6411634</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7795,6 +7794,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7806,7 +7810,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7824,42 +7828,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203186</v>
+        <v>128203220</v>
       </c>
       <c r="B64" t="n">
-        <v>98492</v>
+        <v>109297</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7868,10 +7872,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736331</v>
+        <v>736295</v>
       </c>
       <c r="R64" t="n">
-        <v>6411530</v>
+        <v>6411551</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7904,6 +7908,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7935,27 +7944,27 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203220</v>
+        <v>128203237</v>
       </c>
       <c r="B65" t="n">
-        <v>109297</v>
+        <v>110354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7963,29 +7972,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R65" t="n">
-        <v>6411551</v>
+        <v>6411500</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -10008,32 +10008,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203249</v>
+        <v>128203132</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>107355</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736192</v>
+        <v>736242</v>
       </c>
       <c r="R84" t="n">
-        <v>6411467</v>
+        <v>6411713</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203162</v>
+        <v>128203249</v>
       </c>
       <c r="B85" t="n">
         <v>98448</v>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10163,13 +10163,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736250</v>
+        <v>736192</v>
       </c>
       <c r="R85" t="n">
-        <v>6411464</v>
+        <v>6411467</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10230,10 +10230,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203111</v>
+        <v>128203162</v>
       </c>
       <c r="B86" t="n">
-        <v>98401</v>
+        <v>98448</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,26 +10241,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219794</v>
+        <v>219798</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10274,10 +10274,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736184</v>
+        <v>736250</v>
       </c>
       <c r="R86" t="n">
-        <v>6411805</v>
+        <v>6411464</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10312,11 +10312,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10328,7 +10323,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10346,37 +10341,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203132</v>
+        <v>128203111</v>
       </c>
       <c r="B87" t="n">
-        <v>107355</v>
+        <v>98401</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220079</v>
+        <v>219794</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10390,13 +10385,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736242</v>
+        <v>736184</v>
       </c>
       <c r="R87" t="n">
-        <v>6411713</v>
+        <v>6411805</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10428,6 +10423,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203165</v>
+        <v>128205915</v>
       </c>
       <c r="B89" t="n">
-        <v>98448</v>
+        <v>57669</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736260</v>
+        <v>736315</v>
       </c>
       <c r="R89" t="n">
-        <v>6411450</v>
+        <v>6411597</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203081</v>
+        <v>128203156</v>
       </c>
       <c r="B90" t="n">
-        <v>98448</v>
+        <v>98388</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10695,26 +10695,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736347</v>
+        <v>736221</v>
       </c>
       <c r="R90" t="n">
-        <v>6411466</v>
+        <v>6411593</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,57 +10795,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203225</v>
+        <v>128203180</v>
       </c>
       <c r="B91" t="n">
-        <v>98472</v>
+        <v>105406</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736263</v>
+        <v>736300</v>
       </c>
       <c r="R91" t="n">
-        <v>6411533</v>
+        <v>6411481</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10877,6 +10868,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10888,7 +10884,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,32 +10902,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203197</v>
+        <v>128203211</v>
       </c>
       <c r="B92" t="n">
-        <v>98472</v>
+        <v>99145</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10941,13 +10937,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736314</v>
+        <v>736301</v>
       </c>
       <c r="R92" t="n">
-        <v>6411572</v>
+        <v>6411564</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10977,11 +10973,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11013,42 +11004,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B93" t="n">
-        <v>57669</v>
+        <v>98448</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11057,13 +11048,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R93" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11124,10 +11115,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203156</v>
+        <v>128203081</v>
       </c>
       <c r="B94" t="n">
-        <v>98388</v>
+        <v>98448</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11135,26 +11126,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11168,10 +11159,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736221</v>
+        <v>736347</v>
       </c>
       <c r="R94" t="n">
-        <v>6411593</v>
+        <v>6411466</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11217,7 +11208,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11235,48 +11226,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203180</v>
+        <v>128203225</v>
       </c>
       <c r="B95" t="n">
-        <v>105406</v>
+        <v>98472</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736300</v>
+        <v>736263</v>
       </c>
       <c r="R95" t="n">
-        <v>6411481</v>
+        <v>6411533</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11308,11 +11308,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11324,7 +11319,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11342,32 +11337,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203211</v>
+        <v>128203197</v>
       </c>
       <c r="B96" t="n">
-        <v>99145</v>
+        <v>98472</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11377,13 +11372,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736301</v>
+        <v>736314</v>
       </c>
       <c r="R96" t="n">
-        <v>6411564</v>
+        <v>6411572</v>
       </c>
       <c r="S96" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11413,6 +11408,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -14346,48 +14346,57 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203091</v>
+        <v>128203190</v>
       </c>
       <c r="B124" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R124" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14448,48 +14457,57 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203151</v>
+        <v>128203216</v>
       </c>
       <c r="B125" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736248</v>
+        <v>736297</v>
       </c>
       <c r="R125" t="n">
-        <v>6411616</v>
+        <v>6411559</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14523,7 +14541,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14555,7 +14573,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203190</v>
+        <v>128203092</v>
       </c>
       <c r="B126" t="n">
         <v>98448</v>
@@ -14585,7 +14603,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14599,13 +14617,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736335</v>
+        <v>736520</v>
       </c>
       <c r="R126" t="n">
-        <v>6411533</v>
+        <v>6411544</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14666,57 +14684,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203216</v>
+        <v>128203091</v>
       </c>
       <c r="B127" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736297</v>
+        <v>736520</v>
       </c>
       <c r="R127" t="n">
-        <v>6411559</v>
+        <v>6411544</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14746,11 +14755,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14782,54 +14786,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203092</v>
+        <v>128203151</v>
       </c>
       <c r="B128" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736520</v>
+        <v>736248</v>
       </c>
       <c r="R128" t="n">
-        <v>6411544</v>
+        <v>6411616</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14862,6 +14857,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203112</v>
+        <v>128203093</v>
       </c>
       <c r="B129" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736184</v>
+        <v>736498</v>
       </c>
       <c r="R129" t="n">
-        <v>6411805</v>
+        <v>6411566</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,11 +14966,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14982,7 +14977,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15000,10 +14995,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203113</v>
+        <v>128203178</v>
       </c>
       <c r="B130" t="n">
-        <v>98472</v>
+        <v>97997</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15011,21 +15006,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219811</v>
+        <v>221930</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15035,10 +15030,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>736184</v>
+        <v>736300</v>
       </c>
       <c r="R130" t="n">
-        <v>6411805</v>
+        <v>6411481</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15075,7 +15070,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15089,7 +15084,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15107,10 +15102,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203252</v>
+        <v>128203112</v>
       </c>
       <c r="B131" t="n">
-        <v>98492</v>
+        <v>98455</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15118,46 +15113,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219862</v>
+        <v>219799</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>736193</v>
+        <v>736184</v>
       </c>
       <c r="R131" t="n">
-        <v>6411456</v>
+        <v>6411805</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15189,6 +15175,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15200,7 +15191,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15218,32 +15209,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203093</v>
+        <v>128203113</v>
       </c>
       <c r="B132" t="n">
-        <v>109297</v>
+        <v>98472</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15253,10 +15244,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736498</v>
+        <v>736184</v>
       </c>
       <c r="R132" t="n">
-        <v>6411566</v>
+        <v>6411805</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15291,6 +15282,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15302,7 +15298,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15320,10 +15316,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203178</v>
+        <v>128203252</v>
       </c>
       <c r="B133" t="n">
-        <v>97997</v>
+        <v>98492</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15331,37 +15327,46 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221930</v>
+        <v>219862</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736300</v>
+        <v>736193</v>
       </c>
       <c r="R133" t="n">
-        <v>6411481</v>
+        <v>6411456</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15393,11 +15398,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15529,57 +15529,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203228</v>
+        <v>128203083</v>
       </c>
       <c r="B135" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736263</v>
+        <v>736442</v>
       </c>
       <c r="R135" t="n">
-        <v>6411533</v>
+        <v>6411479</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15622,7 +15613,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15640,10 +15631,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203127</v>
+        <v>128203139</v>
       </c>
       <c r="B136" t="n">
-        <v>98455</v>
+        <v>98474</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15651,26 +15642,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219799</v>
+        <v>741</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15684,13 +15675,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736239</v>
+        <v>736244</v>
       </c>
       <c r="R136" t="n">
-        <v>6411738</v>
+        <v>6411666</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15733,7 +15724,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15751,48 +15742,57 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203083</v>
+        <v>128203228</v>
       </c>
       <c r="B137" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736442</v>
+        <v>736263</v>
       </c>
       <c r="R137" t="n">
-        <v>6411479</v>
+        <v>6411533</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203139</v>
+        <v>128203127</v>
       </c>
       <c r="B138" t="n">
-        <v>98474</v>
+        <v>98455</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15864,26 +15864,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15897,13 +15897,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736244</v>
+        <v>736239</v>
       </c>
       <c r="R138" t="n">
-        <v>6411666</v>
+        <v>6411738</v>
       </c>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,10 +6400,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203088</v>
+        <v>128203259</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>110354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,43 +6411,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736474</v>
+        <v>736176</v>
       </c>
       <c r="R51" t="n">
-        <v>6411506</v>
+        <v>6411455</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6480,6 +6471,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6511,27 +6507,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203259</v>
+        <v>128203131</v>
       </c>
       <c r="B52" t="n">
-        <v>110354</v>
+        <v>105406</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219677</v>
+        <v>221137</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6539,20 +6535,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736176</v>
+        <v>736256</v>
       </c>
       <c r="R52" t="n">
-        <v>6411455</v>
+        <v>6411743</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6584,11 +6589,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Våtmark mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6618,37 +6618,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128203131</v>
+        <v>128203088</v>
       </c>
       <c r="B53" t="n">
-        <v>105406</v>
+        <v>98448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6662,13 +6662,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736256</v>
+        <v>736474</v>
       </c>
       <c r="R53" t="n">
-        <v>6411743</v>
+        <v>6411506</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Våtmark mellan strandvallar.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203021</v>
+        <v>128203144</v>
       </c>
       <c r="B60" t="n">
-        <v>57669</v>
+        <v>109297</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,27 +7394,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7423,13 +7427,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736197</v>
+        <v>736246</v>
       </c>
       <c r="R60" t="n">
-        <v>6411554</v>
+        <v>6411634</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7459,6 +7463,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7490,42 +7499,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203233</v>
+        <v>128203021</v>
       </c>
       <c r="B61" t="n">
-        <v>98455</v>
+        <v>57669</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219799</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7534,10 +7539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736276</v>
+        <v>736197</v>
       </c>
       <c r="R61" t="n">
-        <v>6411531</v>
+        <v>6411554</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7583,7 +7588,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7601,10 +7606,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203186</v>
+        <v>128203237</v>
       </c>
       <c r="B62" t="n">
-        <v>98492</v>
+        <v>110354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7612,46 +7617,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219862</v>
+        <v>219677</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736331</v>
+        <v>736283</v>
       </c>
       <c r="R62" t="n">
-        <v>6411530</v>
+        <v>6411500</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7681,6 +7677,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7712,42 +7713,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203144</v>
+        <v>128203233</v>
       </c>
       <c r="B63" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7756,13 +7757,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736246</v>
+        <v>736276</v>
       </c>
       <c r="R63" t="n">
-        <v>6411634</v>
+        <v>6411531</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7794,11 +7795,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7810,7 +7806,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7828,42 +7824,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203220</v>
+        <v>128203186</v>
       </c>
       <c r="B64" t="n">
-        <v>109297</v>
+        <v>98492</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7872,10 +7868,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736295</v>
+        <v>736331</v>
       </c>
       <c r="R64" t="n">
-        <v>6411551</v>
+        <v>6411530</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7908,11 +7904,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7944,27 +7935,27 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203237</v>
+        <v>128203220</v>
       </c>
       <c r="B65" t="n">
-        <v>110354</v>
+        <v>109297</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7972,20 +7963,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R65" t="n">
-        <v>6411500</v>
+        <v>6411551</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Överallt!</t>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8264,48 +8264,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203239</v>
+        <v>128203209</v>
       </c>
       <c r="B68" t="n">
-        <v>109297</v>
+        <v>98472</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R68" t="n">
-        <v>6411500</v>
+        <v>6411567</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8337,11 +8346,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8353,7 +8357,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8371,7 +8375,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203095</v>
+        <v>128203239</v>
       </c>
       <c r="B69" t="n">
         <v>109297</v>
@@ -8406,13 +8410,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736474</v>
+        <v>736283</v>
       </c>
       <c r="R69" t="n">
-        <v>6411596</v>
+        <v>6411500</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8446,7 +8450,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8478,57 +8482,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203209</v>
+        <v>128203095</v>
       </c>
       <c r="B70" t="n">
-        <v>98472</v>
+        <v>109297</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736295</v>
+        <v>736474</v>
       </c>
       <c r="R70" t="n">
-        <v>6411567</v>
+        <v>6411596</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8560,6 +8555,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203185</v>
+        <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>109297</v>
+        <v>98476</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,34 +9143,43 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>742</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736331</v>
+        <v>736184</v>
       </c>
       <c r="R76" t="n">
-        <v>6411530</v>
+        <v>6411805</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9207,7 +9216,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9221,7 +9230,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9239,10 +9248,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203189</v>
+        <v>128203023</v>
       </c>
       <c r="B77" t="n">
-        <v>109297</v>
+        <v>57669</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9250,37 +9259,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736335</v>
+        <v>736365</v>
       </c>
       <c r="R77" t="n">
-        <v>6411533</v>
+        <v>6411573</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9341,48 +9359,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203199</v>
+        <v>128203099</v>
       </c>
       <c r="B78" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736314</v>
+        <v>736361</v>
       </c>
       <c r="R78" t="n">
-        <v>6411572</v>
+        <v>6411697</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9414,11 +9441,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9430,7 +9452,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9448,57 +9470,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203099</v>
+        <v>128203199</v>
       </c>
       <c r="B79" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736361</v>
+        <v>736314</v>
       </c>
       <c r="R79" t="n">
-        <v>6411697</v>
+        <v>6411572</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9530,6 +9543,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9541,7 +9559,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9781,10 +9799,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203023</v>
+        <v>128203185</v>
       </c>
       <c r="B82" t="n">
-        <v>57669</v>
+        <v>109297</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,46 +9810,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736365</v>
+        <v>736331</v>
       </c>
       <c r="R82" t="n">
-        <v>6411573</v>
+        <v>6411530</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9861,6 +9870,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9892,10 +9906,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203114</v>
+        <v>128203189</v>
       </c>
       <c r="B83" t="n">
-        <v>98476</v>
+        <v>109297</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,43 +9917,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>742</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736184</v>
+        <v>736335</v>
       </c>
       <c r="R83" t="n">
-        <v>6411805</v>
+        <v>6411533</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9974,11 +9979,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10008,32 +10008,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203132</v>
+        <v>128203249</v>
       </c>
       <c r="B84" t="n">
-        <v>107355</v>
+        <v>98448</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736242</v>
+        <v>736192</v>
       </c>
       <c r="R84" t="n">
-        <v>6411713</v>
+        <v>6411467</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203249</v>
+        <v>128203162</v>
       </c>
       <c r="B85" t="n">
         <v>98448</v>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10163,13 +10163,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736192</v>
+        <v>736250</v>
       </c>
       <c r="R85" t="n">
-        <v>6411467</v>
+        <v>6411464</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10230,10 +10230,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203162</v>
+        <v>128203111</v>
       </c>
       <c r="B86" t="n">
-        <v>98448</v>
+        <v>98401</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,26 +10241,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>219794</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10274,10 +10274,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736250</v>
+        <v>736184</v>
       </c>
       <c r="R86" t="n">
-        <v>6411464</v>
+        <v>6411805</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10312,6 +10312,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10323,7 +10328,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10341,37 +10346,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203111</v>
+        <v>128203132</v>
       </c>
       <c r="B87" t="n">
-        <v>98401</v>
+        <v>107355</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219794</v>
+        <v>220079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10385,13 +10390,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736184</v>
+        <v>736242</v>
       </c>
       <c r="R87" t="n">
-        <v>6411805</v>
+        <v>6411713</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10423,11 +10428,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B89" t="n">
-        <v>57669</v>
+        <v>98448</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R89" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203156</v>
+        <v>128203081</v>
       </c>
       <c r="B90" t="n">
-        <v>98388</v>
+        <v>98448</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10695,26 +10695,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736221</v>
+        <v>736347</v>
       </c>
       <c r="R90" t="n">
-        <v>6411593</v>
+        <v>6411466</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,48 +10795,57 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203180</v>
+        <v>128203225</v>
       </c>
       <c r="B91" t="n">
-        <v>105406</v>
+        <v>98472</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736300</v>
+        <v>736263</v>
       </c>
       <c r="R91" t="n">
-        <v>6411481</v>
+        <v>6411533</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10868,11 +10877,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10884,7 +10888,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10902,32 +10906,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203211</v>
+        <v>128203197</v>
       </c>
       <c r="B92" t="n">
-        <v>99145</v>
+        <v>98472</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10937,13 +10941,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736301</v>
+        <v>736314</v>
       </c>
       <c r="R92" t="n">
-        <v>6411564</v>
+        <v>6411572</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10973,6 +10977,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11004,42 +11013,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203165</v>
+        <v>128205915</v>
       </c>
       <c r="B93" t="n">
-        <v>98448</v>
+        <v>57669</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11048,13 +11057,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736260</v>
+        <v>736315</v>
       </c>
       <c r="R93" t="n">
-        <v>6411450</v>
+        <v>6411597</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11115,10 +11124,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203081</v>
+        <v>128203156</v>
       </c>
       <c r="B94" t="n">
-        <v>98448</v>
+        <v>98388</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11126,26 +11135,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11159,10 +11168,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736347</v>
+        <v>736221</v>
       </c>
       <c r="R94" t="n">
-        <v>6411466</v>
+        <v>6411593</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11208,7 +11217,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11226,57 +11235,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203225</v>
+        <v>128203180</v>
       </c>
       <c r="B95" t="n">
-        <v>98472</v>
+        <v>105406</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736263</v>
+        <v>736300</v>
       </c>
       <c r="R95" t="n">
-        <v>6411533</v>
+        <v>6411481</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11308,6 +11308,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11319,7 +11324,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11337,32 +11342,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203197</v>
+        <v>128203211</v>
       </c>
       <c r="B96" t="n">
-        <v>98472</v>
+        <v>99145</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11372,13 +11377,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736314</v>
+        <v>736301</v>
       </c>
       <c r="R96" t="n">
-        <v>6411572</v>
+        <v>6411564</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11408,11 +11413,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203093</v>
+        <v>128203112</v>
       </c>
       <c r="B129" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736498</v>
+        <v>736184</v>
       </c>
       <c r="R129" t="n">
-        <v>6411566</v>
+        <v>6411805</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,6 +14966,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14977,7 +14982,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -14995,10 +15000,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203178</v>
+        <v>128203113</v>
       </c>
       <c r="B130" t="n">
-        <v>97997</v>
+        <v>98472</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15006,21 +15011,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221930</v>
+        <v>219811</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15030,10 +15035,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>736300</v>
+        <v>736184</v>
       </c>
       <c r="R130" t="n">
-        <v>6411481</v>
+        <v>6411805</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15070,7 +15075,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15084,7 +15089,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15102,10 +15107,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203112</v>
+        <v>128203252</v>
       </c>
       <c r="B131" t="n">
-        <v>98455</v>
+        <v>98492</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15113,37 +15118,46 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219799</v>
+        <v>219862</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>736184</v>
+        <v>736193</v>
       </c>
       <c r="R131" t="n">
-        <v>6411805</v>
+        <v>6411456</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15175,11 +15189,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15191,7 +15200,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15209,32 +15218,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203113</v>
+        <v>128203093</v>
       </c>
       <c r="B132" t="n">
-        <v>98472</v>
+        <v>109297</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15244,10 +15253,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736184</v>
+        <v>736498</v>
       </c>
       <c r="R132" t="n">
-        <v>6411805</v>
+        <v>6411566</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15282,11 +15291,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15298,7 +15302,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15316,10 +15320,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203252</v>
+        <v>128203178</v>
       </c>
       <c r="B133" t="n">
-        <v>98492</v>
+        <v>97997</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15327,46 +15331,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219862</v>
+        <v>221930</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Wahlenb.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736193</v>
+        <v>736300</v>
       </c>
       <c r="R133" t="n">
-        <v>6411456</v>
+        <v>6411481</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15398,6 +15393,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15529,48 +15529,57 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203083</v>
+        <v>128203228</v>
       </c>
       <c r="B135" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736442</v>
+        <v>736263</v>
       </c>
       <c r="R135" t="n">
-        <v>6411479</v>
+        <v>6411533</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15613,7 +15622,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15631,10 +15640,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203139</v>
+        <v>128203127</v>
       </c>
       <c r="B136" t="n">
-        <v>98474</v>
+        <v>98455</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15642,26 +15651,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15675,13 +15684,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736244</v>
+        <v>736239</v>
       </c>
       <c r="R136" t="n">
-        <v>6411666</v>
+        <v>6411738</v>
       </c>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15724,7 +15733,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15742,10 +15751,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203228</v>
+        <v>128203139</v>
       </c>
       <c r="B137" t="n">
-        <v>98455</v>
+        <v>98474</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15753,26 +15762,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219799</v>
+        <v>741</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15786,13 +15795,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736263</v>
+        <v>736244</v>
       </c>
       <c r="R137" t="n">
-        <v>6411533</v>
+        <v>6411666</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15835,7 +15844,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15853,57 +15862,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203127</v>
+        <v>128203083</v>
       </c>
       <c r="B138" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736239</v>
+        <v>736442</v>
       </c>
       <c r="R138" t="n">
-        <v>6411738</v>
+        <v>6411479</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203144</v>
+        <v>128203021</v>
       </c>
       <c r="B60" t="n">
-        <v>109297</v>
+        <v>57669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,31 +7394,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7427,13 +7423,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736246</v>
+        <v>736197</v>
       </c>
       <c r="R60" t="n">
-        <v>6411634</v>
+        <v>6411554</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7463,11 +7459,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7499,38 +7490,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203021</v>
+        <v>128203233</v>
       </c>
       <c r="B61" t="n">
-        <v>57669</v>
+        <v>98455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>219799</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7539,10 +7534,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736197</v>
+        <v>736276</v>
       </c>
       <c r="R61" t="n">
-        <v>6411554</v>
+        <v>6411531</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7588,7 +7583,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7606,10 +7601,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203237</v>
+        <v>128203186</v>
       </c>
       <c r="B62" t="n">
-        <v>110354</v>
+        <v>98492</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,37 +7612,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219677</v>
+        <v>219862</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736283</v>
+        <v>736331</v>
       </c>
       <c r="R62" t="n">
-        <v>6411500</v>
+        <v>6411530</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7677,11 +7681,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7713,42 +7712,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203233</v>
+        <v>128203144</v>
       </c>
       <c r="B63" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7757,13 +7756,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736276</v>
+        <v>736246</v>
       </c>
       <c r="R63" t="n">
-        <v>6411531</v>
+        <v>6411634</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7795,6 +7794,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7806,7 +7810,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7824,42 +7828,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203186</v>
+        <v>128203220</v>
       </c>
       <c r="B64" t="n">
-        <v>98492</v>
+        <v>109297</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7868,10 +7872,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736331</v>
+        <v>736295</v>
       </c>
       <c r="R64" t="n">
-        <v>6411530</v>
+        <v>6411551</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7904,6 +7908,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7935,27 +7944,27 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203220</v>
+        <v>128203237</v>
       </c>
       <c r="B65" t="n">
-        <v>109297</v>
+        <v>110354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7963,29 +7972,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R65" t="n">
-        <v>6411551</v>
+        <v>6411500</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8264,57 +8264,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203209</v>
+        <v>128203239</v>
       </c>
       <c r="B68" t="n">
-        <v>98472</v>
+        <v>109297</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R68" t="n">
-        <v>6411567</v>
+        <v>6411500</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8346,6 +8337,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8357,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8375,7 +8371,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203239</v>
+        <v>128203095</v>
       </c>
       <c r="B69" t="n">
         <v>109297</v>
@@ -8410,13 +8406,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736283</v>
+        <v>736474</v>
       </c>
       <c r="R69" t="n">
-        <v>6411500</v>
+        <v>6411596</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8450,7 +8446,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8482,48 +8478,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203095</v>
+        <v>128203209</v>
       </c>
       <c r="B70" t="n">
-        <v>109297</v>
+        <v>98472</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736474</v>
+        <v>736295</v>
       </c>
       <c r="R70" t="n">
-        <v>6411596</v>
+        <v>6411567</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8555,11 +8560,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203114</v>
+        <v>128203185</v>
       </c>
       <c r="B76" t="n">
-        <v>98476</v>
+        <v>109297</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,43 +9143,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>742</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736184</v>
+        <v>736331</v>
       </c>
       <c r="R76" t="n">
-        <v>6411805</v>
+        <v>6411530</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9216,7 +9207,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9230,7 +9221,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9248,10 +9239,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203023</v>
+        <v>128203189</v>
       </c>
       <c r="B77" t="n">
-        <v>57669</v>
+        <v>109297</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,46 +9250,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736365</v>
+        <v>736335</v>
       </c>
       <c r="R77" t="n">
-        <v>6411573</v>
+        <v>6411533</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9359,57 +9341,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203099</v>
+        <v>128203199</v>
       </c>
       <c r="B78" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736361</v>
+        <v>736314</v>
       </c>
       <c r="R78" t="n">
-        <v>6411697</v>
+        <v>6411572</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9441,6 +9414,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9452,7 +9430,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9470,48 +9448,57 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203199</v>
+        <v>128203099</v>
       </c>
       <c r="B79" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736314</v>
+        <v>736361</v>
       </c>
       <c r="R79" t="n">
-        <v>6411572</v>
+        <v>6411697</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9543,11 +9530,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9559,7 +9541,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9799,10 +9781,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203185</v>
+        <v>128203023</v>
       </c>
       <c r="B82" t="n">
-        <v>109297</v>
+        <v>57669</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9810,37 +9792,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736331</v>
+        <v>736365</v>
       </c>
       <c r="R82" t="n">
-        <v>6411530</v>
+        <v>6411573</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9870,11 +9861,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9906,10 +9892,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203189</v>
+        <v>128203114</v>
       </c>
       <c r="B83" t="n">
-        <v>109297</v>
+        <v>98476</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9917,34 +9903,43 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>742</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736335</v>
+        <v>736184</v>
       </c>
       <c r="R83" t="n">
-        <v>6411533</v>
+        <v>6411805</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9979,6 +9974,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203165</v>
+        <v>128205915</v>
       </c>
       <c r="B89" t="n">
-        <v>98448</v>
+        <v>57669</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736260</v>
+        <v>736315</v>
       </c>
       <c r="R89" t="n">
-        <v>6411450</v>
+        <v>6411597</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203081</v>
+        <v>128203156</v>
       </c>
       <c r="B90" t="n">
-        <v>98448</v>
+        <v>98388</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10695,26 +10695,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736347</v>
+        <v>736221</v>
       </c>
       <c r="R90" t="n">
-        <v>6411466</v>
+        <v>6411593</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,57 +10795,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203225</v>
+        <v>128203180</v>
       </c>
       <c r="B91" t="n">
-        <v>98472</v>
+        <v>105406</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736263</v>
+        <v>736300</v>
       </c>
       <c r="R91" t="n">
-        <v>6411533</v>
+        <v>6411481</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10877,6 +10868,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10888,7 +10884,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,32 +10902,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203197</v>
+        <v>128203211</v>
       </c>
       <c r="B92" t="n">
-        <v>98472</v>
+        <v>99145</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10941,13 +10937,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736314</v>
+        <v>736301</v>
       </c>
       <c r="R92" t="n">
-        <v>6411572</v>
+        <v>6411564</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10977,11 +10973,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11013,42 +11004,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B93" t="n">
-        <v>57669</v>
+        <v>98448</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11057,13 +11048,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R93" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11124,10 +11115,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203156</v>
+        <v>128203081</v>
       </c>
       <c r="B94" t="n">
-        <v>98388</v>
+        <v>98448</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11135,26 +11126,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11168,10 +11159,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736221</v>
+        <v>736347</v>
       </c>
       <c r="R94" t="n">
-        <v>6411593</v>
+        <v>6411466</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11217,7 +11208,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11235,48 +11226,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203180</v>
+        <v>128203225</v>
       </c>
       <c r="B95" t="n">
-        <v>105406</v>
+        <v>98472</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736300</v>
+        <v>736263</v>
       </c>
       <c r="R95" t="n">
-        <v>6411481</v>
+        <v>6411533</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11308,11 +11308,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11324,7 +11319,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11342,32 +11337,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203211</v>
+        <v>128203197</v>
       </c>
       <c r="B96" t="n">
-        <v>99145</v>
+        <v>98472</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11377,13 +11372,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736301</v>
+        <v>736314</v>
       </c>
       <c r="R96" t="n">
-        <v>6411564</v>
+        <v>6411572</v>
       </c>
       <c r="S96" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11413,6 +11408,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12297,57 +12297,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203207</v>
+        <v>128203255</v>
       </c>
       <c r="B105" t="n">
-        <v>98472</v>
+        <v>109297</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736300</v>
+        <v>736200</v>
       </c>
       <c r="R105" t="n">
-        <v>6411576</v>
+        <v>6411456</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12390,7 +12381,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12408,32 +12399,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203177</v>
+        <v>128203242</v>
       </c>
       <c r="B106" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12443,10 +12434,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736300</v>
+        <v>736237</v>
       </c>
       <c r="R106" t="n">
-        <v>6411481</v>
+        <v>6411484</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12483,7 +12474,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12497,7 +12488,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12515,57 +12506,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203234</v>
+        <v>128203107</v>
       </c>
       <c r="B107" t="n">
-        <v>98448</v>
+        <v>105406</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736279</v>
+        <v>736305</v>
       </c>
       <c r="R107" t="n">
-        <v>6411517</v>
+        <v>6411739</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12597,6 +12579,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12608,7 +12595,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12626,48 +12613,57 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203107</v>
+        <v>128203207</v>
       </c>
       <c r="B108" t="n">
-        <v>105406</v>
+        <v>98472</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736305</v>
+        <v>736300</v>
       </c>
       <c r="R108" t="n">
-        <v>6411739</v>
+        <v>6411576</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12699,11 +12695,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12715,7 +12706,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12733,32 +12724,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203255</v>
+        <v>128203177</v>
       </c>
       <c r="B109" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12768,10 +12759,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736200</v>
+        <v>736300</v>
       </c>
       <c r="R109" t="n">
-        <v>6411456</v>
+        <v>6411481</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12806,6 +12797,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12817,7 +12813,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12835,48 +12831,57 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203242</v>
+        <v>128203234</v>
       </c>
       <c r="B110" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736237</v>
+        <v>736279</v>
       </c>
       <c r="R110" t="n">
-        <v>6411484</v>
+        <v>6411517</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12906,11 +12911,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14346,57 +14346,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203190</v>
+        <v>128203091</v>
       </c>
       <c r="B124" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736335</v>
+        <v>736520</v>
       </c>
       <c r="R124" t="n">
-        <v>6411533</v>
+        <v>6411544</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14457,57 +14448,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203216</v>
+        <v>128203151</v>
       </c>
       <c r="B125" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736297</v>
+        <v>736248</v>
       </c>
       <c r="R125" t="n">
-        <v>6411559</v>
+        <v>6411616</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14541,7 +14523,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Kant av våtmark.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14573,7 +14555,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203092</v>
+        <v>128203190</v>
       </c>
       <c r="B126" t="n">
         <v>98448</v>
@@ -14603,7 +14585,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14617,13 +14599,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R126" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14684,48 +14666,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203091</v>
+        <v>128203216</v>
       </c>
       <c r="B127" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736520</v>
+        <v>736297</v>
       </c>
       <c r="R127" t="n">
-        <v>6411544</v>
+        <v>6411559</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14755,6 +14746,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14786,45 +14782,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203151</v>
+        <v>128203092</v>
       </c>
       <c r="B128" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736248</v>
+        <v>736520</v>
       </c>
       <c r="R128" t="n">
-        <v>6411616</v>
+        <v>6411544</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14857,11 +14862,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD128" t="b">

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203179</v>
+        <v>128203195</v>
       </c>
       <c r="B54" t="n">
-        <v>99511</v>
+        <v>98378</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,37 +6740,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736300</v>
+        <v>736314</v>
       </c>
       <c r="R54" t="n">
-        <v>6411481</v>
+        <v>6411572</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6802,6 +6811,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6813,7 +6827,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6831,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203195</v>
+        <v>128203096</v>
       </c>
       <c r="B55" t="n">
-        <v>98378</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6842,26 +6856,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6875,13 +6889,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736314</v>
+        <v>736474</v>
       </c>
       <c r="R55" t="n">
-        <v>6411572</v>
+        <v>6411596</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6915,7 +6929,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6929,7 +6943,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6947,7 +6961,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203096</v>
+        <v>128203100</v>
       </c>
       <c r="B56" t="n">
         <v>98448</v>
@@ -6977,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6991,10 +7005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736474</v>
+        <v>736361</v>
       </c>
       <c r="R56" t="n">
-        <v>6411596</v>
+        <v>6411697</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7027,11 +7041,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7063,54 +7072,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203100</v>
+        <v>128203241</v>
       </c>
       <c r="B57" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736361</v>
+        <v>736223</v>
       </c>
       <c r="R57" t="n">
-        <v>6411697</v>
+        <v>6411512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7143,6 +7143,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7174,7 +7179,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203241</v>
+        <v>128203256</v>
       </c>
       <c r="B58" t="n">
         <v>109297</v>
@@ -7209,10 +7214,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736223</v>
+        <v>736176</v>
       </c>
       <c r="R58" t="n">
-        <v>6411512</v>
+        <v>6411455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7245,11 +7250,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7281,27 +7281,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203256</v>
+        <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>109297</v>
+        <v>99511</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736176</v>
+        <v>736300</v>
       </c>
       <c r="R59" t="n">
-        <v>6411455</v>
+        <v>6411481</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203185</v>
+        <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>109297</v>
+        <v>98476</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,34 +9143,43 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>742</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736331</v>
+        <v>736184</v>
       </c>
       <c r="R76" t="n">
-        <v>6411530</v>
+        <v>6411805</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9207,7 +9216,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9221,7 +9230,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9239,10 +9248,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203189</v>
+        <v>128203023</v>
       </c>
       <c r="B77" t="n">
-        <v>109297</v>
+        <v>57669</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9250,37 +9259,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736335</v>
+        <v>736365</v>
       </c>
       <c r="R77" t="n">
-        <v>6411533</v>
+        <v>6411573</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9341,48 +9359,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203199</v>
+        <v>128203099</v>
       </c>
       <c r="B78" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736314</v>
+        <v>736361</v>
       </c>
       <c r="R78" t="n">
-        <v>6411572</v>
+        <v>6411697</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9414,11 +9441,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9430,7 +9452,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9448,57 +9470,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203099</v>
+        <v>128203199</v>
       </c>
       <c r="B79" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736361</v>
+        <v>736314</v>
       </c>
       <c r="R79" t="n">
-        <v>6411697</v>
+        <v>6411572</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9530,6 +9543,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9541,7 +9559,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9781,10 +9799,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203023</v>
+        <v>128203185</v>
       </c>
       <c r="B82" t="n">
-        <v>57669</v>
+        <v>109297</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,46 +9810,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736365</v>
+        <v>736331</v>
       </c>
       <c r="R82" t="n">
-        <v>6411573</v>
+        <v>6411530</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9861,6 +9870,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9892,10 +9906,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203114</v>
+        <v>128203189</v>
       </c>
       <c r="B83" t="n">
-        <v>98476</v>
+        <v>109297</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,43 +9917,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>742</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736184</v>
+        <v>736335</v>
       </c>
       <c r="R83" t="n">
-        <v>6411805</v>
+        <v>6411533</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9974,11 +9979,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10008,32 +10008,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203249</v>
+        <v>128203132</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>107355</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736192</v>
+        <v>736242</v>
       </c>
       <c r="R84" t="n">
-        <v>6411467</v>
+        <v>6411713</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203162</v>
+        <v>128203249</v>
       </c>
       <c r="B85" t="n">
         <v>98448</v>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10163,13 +10163,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736250</v>
+        <v>736192</v>
       </c>
       <c r="R85" t="n">
-        <v>6411464</v>
+        <v>6411467</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10230,10 +10230,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203111</v>
+        <v>128203162</v>
       </c>
       <c r="B86" t="n">
-        <v>98401</v>
+        <v>98448</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,26 +10241,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219794</v>
+        <v>219798</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10274,10 +10274,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736184</v>
+        <v>736250</v>
       </c>
       <c r="R86" t="n">
-        <v>6411805</v>
+        <v>6411464</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10312,11 +10312,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10328,7 +10323,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10346,37 +10341,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203132</v>
+        <v>128203111</v>
       </c>
       <c r="B87" t="n">
-        <v>107355</v>
+        <v>98401</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220079</v>
+        <v>219794</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10390,13 +10385,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736242</v>
+        <v>736184</v>
       </c>
       <c r="R87" t="n">
-        <v>6411713</v>
+        <v>6411805</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10428,6 +10423,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12297,48 +12297,57 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203255</v>
+        <v>128203207</v>
       </c>
       <c r="B105" t="n">
-        <v>109297</v>
+        <v>98472</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736200</v>
+        <v>736300</v>
       </c>
       <c r="R105" t="n">
-        <v>6411456</v>
+        <v>6411576</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12381,7 +12390,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12399,32 +12408,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203242</v>
+        <v>128203177</v>
       </c>
       <c r="B106" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12434,10 +12443,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736237</v>
+        <v>736300</v>
       </c>
       <c r="R106" t="n">
-        <v>6411484</v>
+        <v>6411481</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12474,7 +12483,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12488,7 +12497,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12506,48 +12515,57 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203107</v>
+        <v>128203234</v>
       </c>
       <c r="B107" t="n">
-        <v>105406</v>
+        <v>98448</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736305</v>
+        <v>736279</v>
       </c>
       <c r="R107" t="n">
-        <v>6411739</v>
+        <v>6411517</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12579,11 +12597,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12595,7 +12608,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12613,57 +12626,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203207</v>
+        <v>128203107</v>
       </c>
       <c r="B108" t="n">
-        <v>98472</v>
+        <v>105406</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736300</v>
+        <v>736305</v>
       </c>
       <c r="R108" t="n">
-        <v>6411576</v>
+        <v>6411739</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12695,6 +12699,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12706,7 +12715,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12724,32 +12733,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203177</v>
+        <v>128203255</v>
       </c>
       <c r="B109" t="n">
-        <v>98455</v>
+        <v>109297</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12759,10 +12768,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736300</v>
+        <v>736200</v>
       </c>
       <c r="R109" t="n">
-        <v>6411481</v>
+        <v>6411456</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12797,11 +12806,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12813,7 +12817,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12831,57 +12835,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203234</v>
+        <v>128203242</v>
       </c>
       <c r="B110" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736279</v>
+        <v>736237</v>
       </c>
       <c r="R110" t="n">
-        <v>6411517</v>
+        <v>6411484</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12911,6 +12906,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14346,48 +14346,57 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203091</v>
+        <v>128203190</v>
       </c>
       <c r="B124" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R124" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14448,48 +14457,57 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203151</v>
+        <v>128203216</v>
       </c>
       <c r="B125" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736248</v>
+        <v>736297</v>
       </c>
       <c r="R125" t="n">
-        <v>6411616</v>
+        <v>6411559</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14523,7 +14541,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14555,7 +14573,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203190</v>
+        <v>128203092</v>
       </c>
       <c r="B126" t="n">
         <v>98448</v>
@@ -14585,7 +14603,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14599,13 +14617,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736335</v>
+        <v>736520</v>
       </c>
       <c r="R126" t="n">
-        <v>6411533</v>
+        <v>6411544</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14666,57 +14684,48 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203216</v>
+        <v>128203091</v>
       </c>
       <c r="B127" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736297</v>
+        <v>736520</v>
       </c>
       <c r="R127" t="n">
-        <v>6411559</v>
+        <v>6411544</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14746,11 +14755,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14782,54 +14786,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203092</v>
+        <v>128203151</v>
       </c>
       <c r="B128" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736520</v>
+        <v>736248</v>
       </c>
       <c r="R128" t="n">
-        <v>6411544</v>
+        <v>6411616</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14862,6 +14857,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15964,48 +15964,57 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203240</v>
+        <v>128203084</v>
       </c>
       <c r="B139" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736238</v>
+        <v>736442</v>
       </c>
       <c r="R139" t="n">
-        <v>6411496</v>
+        <v>6411479</v>
       </c>
       <c r="S139" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16035,11 +16044,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16071,10 +16075,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203084</v>
+        <v>128203223</v>
       </c>
       <c r="B140" t="n">
-        <v>98448</v>
+        <v>98378</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16082,26 +16086,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16115,13 +16119,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736442</v>
+        <v>736272</v>
       </c>
       <c r="R140" t="n">
-        <v>6411479</v>
+        <v>6411536</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16164,7 +16168,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16182,10 +16186,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203223</v>
+        <v>128203231</v>
       </c>
       <c r="B141" t="n">
-        <v>98378</v>
+        <v>98448</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16193,26 +16197,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16226,10 +16230,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736272</v>
+        <v>736270</v>
       </c>
       <c r="R141" t="n">
-        <v>6411536</v>
+        <v>6411530</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16275,7 +16279,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16293,57 +16297,48 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203231</v>
+        <v>128203085</v>
       </c>
       <c r="B142" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736270</v>
+        <v>736450</v>
       </c>
       <c r="R142" t="n">
-        <v>6411530</v>
+        <v>6411486</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16404,7 +16399,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128203085</v>
+        <v>128203240</v>
       </c>
       <c r="B143" t="n">
         <v>109297</v>
@@ -16439,13 +16434,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>736450</v>
+        <v>736238</v>
       </c>
       <c r="R143" t="n">
-        <v>6411486</v>
+        <v>6411496</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16475,6 +16470,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203195</v>
+        <v>128203179</v>
       </c>
       <c r="B54" t="n">
-        <v>98378</v>
+        <v>99511</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,46 +6740,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736314</v>
+        <v>736300</v>
       </c>
       <c r="R54" t="n">
-        <v>6411572</v>
+        <v>6411481</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6811,11 +6802,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6827,7 +6813,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6845,10 +6831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203096</v>
+        <v>128203195</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>98378</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6856,26 +6842,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6889,13 +6875,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736474</v>
+        <v>736314</v>
       </c>
       <c r="R55" t="n">
-        <v>6411596</v>
+        <v>6411572</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6929,7 +6915,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6943,7 +6929,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6961,7 +6947,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203100</v>
+        <v>128203096</v>
       </c>
       <c r="B56" t="n">
         <v>98448</v>
@@ -6991,7 +6977,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7005,10 +6991,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736361</v>
+        <v>736474</v>
       </c>
       <c r="R56" t="n">
-        <v>6411697</v>
+        <v>6411596</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7041,6 +7027,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7072,45 +7063,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203241</v>
+        <v>128203100</v>
       </c>
       <c r="B57" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736223</v>
+        <v>736361</v>
       </c>
       <c r="R57" t="n">
-        <v>6411512</v>
+        <v>6411697</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7143,11 +7143,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7179,7 +7174,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203256</v>
+        <v>128203241</v>
       </c>
       <c r="B58" t="n">
         <v>109297</v>
@@ -7214,10 +7209,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736176</v>
+        <v>736223</v>
       </c>
       <c r="R58" t="n">
-        <v>6411455</v>
+        <v>6411512</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7250,6 +7245,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7281,27 +7281,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203179</v>
+        <v>128203256</v>
       </c>
       <c r="B59" t="n">
-        <v>99511</v>
+        <v>109297</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736300</v>
+        <v>736176</v>
       </c>
       <c r="R59" t="n">
-        <v>6411481</v>
+        <v>6411455</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203021</v>
+        <v>128203144</v>
       </c>
       <c r="B60" t="n">
-        <v>57669</v>
+        <v>109297</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,27 +7394,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7423,13 +7427,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736197</v>
+        <v>736246</v>
       </c>
       <c r="R60" t="n">
-        <v>6411554</v>
+        <v>6411634</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7459,6 +7463,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7490,42 +7499,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203233</v>
+        <v>128203021</v>
       </c>
       <c r="B61" t="n">
-        <v>98455</v>
+        <v>57669</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219799</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7534,10 +7539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736276</v>
+        <v>736197</v>
       </c>
       <c r="R61" t="n">
-        <v>6411531</v>
+        <v>6411554</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7583,7 +7588,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7601,10 +7606,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203186</v>
+        <v>128203237</v>
       </c>
       <c r="B62" t="n">
-        <v>98492</v>
+        <v>110354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7612,46 +7617,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219862</v>
+        <v>219677</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736331</v>
+        <v>736283</v>
       </c>
       <c r="R62" t="n">
-        <v>6411530</v>
+        <v>6411500</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7681,6 +7677,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7712,42 +7713,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203144</v>
+        <v>128203233</v>
       </c>
       <c r="B63" t="n">
-        <v>109297</v>
+        <v>98455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7756,13 +7757,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736246</v>
+        <v>736276</v>
       </c>
       <c r="R63" t="n">
-        <v>6411634</v>
+        <v>6411531</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7794,11 +7795,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7810,7 +7806,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7828,42 +7824,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203220</v>
+        <v>128203186</v>
       </c>
       <c r="B64" t="n">
-        <v>109297</v>
+        <v>98492</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7872,10 +7868,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736295</v>
+        <v>736331</v>
       </c>
       <c r="R64" t="n">
-        <v>6411551</v>
+        <v>6411530</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7908,11 +7904,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7944,27 +7935,27 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203237</v>
+        <v>128203220</v>
       </c>
       <c r="B65" t="n">
-        <v>110354</v>
+        <v>109297</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7972,20 +7963,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R65" t="n">
-        <v>6411500</v>
+        <v>6411551</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Överallt!</t>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -14346,57 +14346,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203190</v>
+        <v>128203091</v>
       </c>
       <c r="B124" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736335</v>
+        <v>736520</v>
       </c>
       <c r="R124" t="n">
-        <v>6411533</v>
+        <v>6411544</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14457,57 +14448,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203216</v>
+        <v>128203151</v>
       </c>
       <c r="B125" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736297</v>
+        <v>736248</v>
       </c>
       <c r="R125" t="n">
-        <v>6411559</v>
+        <v>6411616</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14541,7 +14523,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Kant av våtmark.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14573,7 +14555,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203092</v>
+        <v>128203190</v>
       </c>
       <c r="B126" t="n">
         <v>98448</v>
@@ -14603,7 +14585,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14617,13 +14599,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R126" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14684,48 +14666,57 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203091</v>
+        <v>128203216</v>
       </c>
       <c r="B127" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736520</v>
+        <v>736297</v>
       </c>
       <c r="R127" t="n">
-        <v>6411544</v>
+        <v>6411559</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14755,6 +14746,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14786,45 +14782,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203151</v>
+        <v>128203092</v>
       </c>
       <c r="B128" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736248</v>
+        <v>736520</v>
       </c>
       <c r="R128" t="n">
-        <v>6411616</v>
+        <v>6411544</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14857,11 +14862,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15964,57 +15964,48 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203084</v>
+        <v>128203240</v>
       </c>
       <c r="B139" t="n">
-        <v>98448</v>
+        <v>109297</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736442</v>
+        <v>736238</v>
       </c>
       <c r="R139" t="n">
-        <v>6411479</v>
+        <v>6411496</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16044,6 +16035,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16075,10 +16071,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203223</v>
+        <v>128203084</v>
       </c>
       <c r="B140" t="n">
-        <v>98378</v>
+        <v>98448</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16086,26 +16082,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -16119,13 +16115,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736272</v>
+        <v>736442</v>
       </c>
       <c r="R140" t="n">
-        <v>6411536</v>
+        <v>6411479</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16168,7 +16164,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16186,10 +16182,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203231</v>
+        <v>128203223</v>
       </c>
       <c r="B141" t="n">
-        <v>98448</v>
+        <v>98378</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16197,26 +16193,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16230,10 +16226,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736270</v>
+        <v>736272</v>
       </c>
       <c r="R141" t="n">
-        <v>6411530</v>
+        <v>6411536</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -16279,7 +16275,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16297,48 +16293,57 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203085</v>
+        <v>128203231</v>
       </c>
       <c r="B142" t="n">
-        <v>109297</v>
+        <v>98448</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736450</v>
+        <v>736270</v>
       </c>
       <c r="R142" t="n">
-        <v>6411486</v>
+        <v>6411530</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16399,7 +16404,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128203240</v>
+        <v>128203085</v>
       </c>
       <c r="B143" t="n">
         <v>109297</v>
@@ -16434,13 +16439,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>736238</v>
+        <v>736450</v>
       </c>
       <c r="R143" t="n">
-        <v>6411496</v>
+        <v>6411486</v>
       </c>
       <c r="S143" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16470,11 +16475,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,10 +6400,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203259</v>
+        <v>128203088</v>
       </c>
       <c r="B51" t="n">
-        <v>110354</v>
+        <v>98456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,34 +6411,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R51" t="n">
-        <v>6411455</v>
+        <v>6411506</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6471,11 +6480,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6507,27 +6511,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203131</v>
+        <v>128203259</v>
       </c>
       <c r="B52" t="n">
-        <v>105406</v>
+        <v>110362</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221137</v>
+        <v>219677</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6535,29 +6539,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736256</v>
+        <v>736176</v>
       </c>
       <c r="R52" t="n">
-        <v>6411743</v>
+        <v>6411455</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6589,6 +6584,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Våtmark mellan strandvallar.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6618,37 +6618,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128203088</v>
+        <v>128203131</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>105414</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6662,13 +6662,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736474</v>
+        <v>736256</v>
       </c>
       <c r="R53" t="n">
-        <v>6411506</v>
+        <v>6411743</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Våtmark mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6729,27 +6729,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203179</v>
+        <v>128203241</v>
       </c>
       <c r="B54" t="n">
-        <v>99511</v>
+        <v>109305</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736300</v>
+        <v>736223</v>
       </c>
       <c r="R54" t="n">
-        <v>6411481</v>
+        <v>6411512</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6802,6 +6802,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6813,7 +6818,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6834,7 +6839,7 @@
         <v>128203195</v>
       </c>
       <c r="B55" t="n">
-        <v>98378</v>
+        <v>98386</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6950,7 +6955,7 @@
         <v>128203096</v>
       </c>
       <c r="B56" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7066,7 +7071,7 @@
         <v>128203100</v>
       </c>
       <c r="B57" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7174,10 +7179,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203241</v>
+        <v>128203256</v>
       </c>
       <c r="B58" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7209,10 +7214,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736223</v>
+        <v>736176</v>
       </c>
       <c r="R58" t="n">
-        <v>6411512</v>
+        <v>6411455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7245,11 +7250,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7281,27 +7281,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203256</v>
+        <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>109297</v>
+        <v>99519</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736176</v>
+        <v>736300</v>
       </c>
       <c r="R59" t="n">
-        <v>6411455</v>
+        <v>6411481</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203144</v>
+        <v>128203220</v>
       </c>
       <c r="B60" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7427,13 +7427,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736246</v>
+        <v>736295</v>
       </c>
       <c r="R60" t="n">
-        <v>6411634</v>
+        <v>6411551</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203021</v>
+        <v>128203144</v>
       </c>
       <c r="B61" t="n">
-        <v>57669</v>
+        <v>109305</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7510,27 +7510,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7539,13 +7543,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736197</v>
+        <v>736246</v>
       </c>
       <c r="R61" t="n">
-        <v>6411554</v>
+        <v>6411634</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7575,6 +7579,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7609,7 +7618,7 @@
         <v>128203237</v>
       </c>
       <c r="B62" t="n">
-        <v>110354</v>
+        <v>110362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7716,7 +7725,7 @@
         <v>128203233</v>
       </c>
       <c r="B63" t="n">
-        <v>98455</v>
+        <v>98463</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7827,7 +7836,7 @@
         <v>128203186</v>
       </c>
       <c r="B64" t="n">
-        <v>98492</v>
+        <v>98500</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7935,10 +7944,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203220</v>
+        <v>128203021</v>
       </c>
       <c r="B65" t="n">
-        <v>109297</v>
+        <v>57670</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7946,31 +7955,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7979,10 +7984,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736295</v>
+        <v>736197</v>
       </c>
       <c r="R65" t="n">
-        <v>6411551</v>
+        <v>6411554</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8015,11 +8020,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8051,54 +8051,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128203089</v>
+        <v>128203243</v>
       </c>
       <c r="B66" t="n">
-        <v>98448</v>
+        <v>109305</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>736488</v>
+        <v>736237</v>
       </c>
       <c r="R66" t="n">
-        <v>6411510</v>
+        <v>6411472</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8144,7 +8135,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8162,45 +8153,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128203243</v>
+        <v>128203089</v>
       </c>
       <c r="B67" t="n">
-        <v>109297</v>
+        <v>98456</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>736237</v>
+        <v>736488</v>
       </c>
       <c r="R67" t="n">
-        <v>6411472</v>
+        <v>6411510</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8267,7 +8267,7 @@
         <v>128203239</v>
       </c>
       <c r="B68" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>128203095</v>
       </c>
       <c r="B69" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8478,57 +8478,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203209</v>
+        <v>128203104</v>
       </c>
       <c r="B70" t="n">
-        <v>98472</v>
+        <v>105414</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736295</v>
+        <v>736325</v>
       </c>
       <c r="R70" t="n">
-        <v>6411567</v>
+        <v>6411730</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8560,6 +8551,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Spridd. Flera i blom.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8567,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8589,48 +8585,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203104</v>
+        <v>128203209</v>
       </c>
       <c r="B71" t="n">
-        <v>105406</v>
+        <v>98480</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736325</v>
+        <v>736295</v>
       </c>
       <c r="R71" t="n">
-        <v>6411730</v>
+        <v>6411567</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8662,11 +8667,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Spridd. Flera i blom.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8699,7 +8699,7 @@
         <v>128203181</v>
       </c>
       <c r="B72" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>128203166</v>
       </c>
       <c r="B73" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>128203182</v>
       </c>
       <c r="B74" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>128203187</v>
       </c>
       <c r="B75" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>98476</v>
+        <v>98484</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>128203023</v>
       </c>
       <c r="B77" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203099</v>
+        <v>128203189</v>
       </c>
       <c r="B78" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9387,29 +9387,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736361</v>
+        <v>736335</v>
       </c>
       <c r="R78" t="n">
-        <v>6411697</v>
+        <v>6411533</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9470,32 +9461,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203199</v>
+        <v>128203185</v>
       </c>
       <c r="B79" t="n">
-        <v>98455</v>
+        <v>109305</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9505,13 +9496,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736314</v>
+        <v>736331</v>
       </c>
       <c r="R79" t="n">
-        <v>6411572</v>
+        <v>6411530</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9545,7 +9536,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9559,7 +9550,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9577,42 +9568,42 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203086</v>
+        <v>128203099</v>
       </c>
       <c r="B80" t="n">
-        <v>98448</v>
+        <v>109305</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9621,10 +9612,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736450</v>
+        <v>736361</v>
       </c>
       <c r="R80" t="n">
-        <v>6411486</v>
+        <v>6411697</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9688,10 +9679,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203221</v>
+        <v>128203199</v>
       </c>
       <c r="B81" t="n">
-        <v>98472</v>
+        <v>98463</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9699,46 +9690,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736272</v>
+        <v>736314</v>
       </c>
       <c r="R81" t="n">
-        <v>6411546</v>
+        <v>6411572</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9770,6 +9752,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9781,7 +9768,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9799,48 +9786,57 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203185</v>
+        <v>128203086</v>
       </c>
       <c r="B82" t="n">
-        <v>109297</v>
+        <v>98456</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736331</v>
+        <v>736450</v>
       </c>
       <c r="R82" t="n">
-        <v>6411530</v>
+        <v>6411486</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9870,11 +9866,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9906,45 +9897,54 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203189</v>
+        <v>128203221</v>
       </c>
       <c r="B83" t="n">
-        <v>109297</v>
+        <v>98480</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736335</v>
+        <v>736272</v>
       </c>
       <c r="R83" t="n">
-        <v>6411533</v>
+        <v>6411546</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10008,10 +10008,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203132</v>
+        <v>128203192</v>
       </c>
       <c r="B84" t="n">
-        <v>107355</v>
+        <v>105414</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10019,26 +10019,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220079</v>
+        <v>221137</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736242</v>
+        <v>736339</v>
       </c>
       <c r="R84" t="n">
-        <v>6411713</v>
+        <v>6411571</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10090,6 +10090,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10101,7 +10106,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10122,7 +10127,7 @@
         <v>128203249</v>
       </c>
       <c r="B85" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10230,37 +10235,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203162</v>
+        <v>128203132</v>
       </c>
       <c r="B86" t="n">
-        <v>98448</v>
+        <v>107363</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10274,13 +10279,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736250</v>
+        <v>736242</v>
       </c>
       <c r="R86" t="n">
-        <v>6411464</v>
+        <v>6411713</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10323,7 +10328,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10341,10 +10346,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203111</v>
+        <v>128203162</v>
       </c>
       <c r="B87" t="n">
-        <v>98401</v>
+        <v>98456</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10352,26 +10357,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219794</v>
+        <v>219798</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10385,10 +10390,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736184</v>
+        <v>736250</v>
       </c>
       <c r="R87" t="n">
-        <v>6411805</v>
+        <v>6411464</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10423,11 +10428,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10457,32 +10457,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128203192</v>
+        <v>128203111</v>
       </c>
       <c r="B88" t="n">
-        <v>105406</v>
+        <v>98409</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221137</v>
+        <v>219794</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>736339</v>
+        <v>736184</v>
       </c>
       <c r="R88" t="n">
-        <v>6411571</v>
+        <v>6411805</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10573,10 +10573,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128205915</v>
+        <v>128203180</v>
       </c>
       <c r="B89" t="n">
-        <v>57669</v>
+        <v>105414</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10584,46 +10584,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>221137</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736315</v>
+        <v>736300</v>
       </c>
       <c r="R89" t="n">
-        <v>6411597</v>
+        <v>6411481</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10655,6 +10646,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10666,7 +10662,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10684,57 +10680,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203156</v>
+        <v>128203211</v>
       </c>
       <c r="B90" t="n">
-        <v>98388</v>
+        <v>99153</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223591</v>
+        <v>222322</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736221</v>
+        <v>736301</v>
       </c>
       <c r="R90" t="n">
-        <v>6411593</v>
+        <v>6411564</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10777,7 +10764,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,10 +10782,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203180</v>
+        <v>128205915</v>
       </c>
       <c r="B91" t="n">
-        <v>105406</v>
+        <v>57670</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,37 +10793,46 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221137</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736300</v>
+        <v>736315</v>
       </c>
       <c r="R91" t="n">
-        <v>6411481</v>
+        <v>6411597</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10868,11 +10864,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -10884,7 +10875,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10902,48 +10893,57 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203211</v>
+        <v>128203165</v>
       </c>
       <c r="B92" t="n">
-        <v>99145</v>
+        <v>98456</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736301</v>
+        <v>736260</v>
       </c>
       <c r="R92" t="n">
-        <v>6411564</v>
+        <v>6411450</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11004,10 +11004,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203165</v>
+        <v>128203081</v>
       </c>
       <c r="B93" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11048,10 +11048,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736260</v>
+        <v>736347</v>
       </c>
       <c r="R93" t="n">
-        <v>6411450</v>
+        <v>6411466</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11115,10 +11115,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203081</v>
+        <v>128203225</v>
       </c>
       <c r="B94" t="n">
-        <v>98448</v>
+        <v>98480</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11126,21 +11126,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736347</v>
+        <v>736263</v>
       </c>
       <c r="R94" t="n">
-        <v>6411466</v>
+        <v>6411533</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11226,10 +11226,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203225</v>
+        <v>128203197</v>
       </c>
       <c r="B95" t="n">
-        <v>98472</v>
+        <v>98480</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11254,29 +11254,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736263</v>
+        <v>736314</v>
       </c>
       <c r="R95" t="n">
-        <v>6411533</v>
+        <v>6411572</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11308,6 +11299,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11319,7 +11315,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11337,10 +11333,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203197</v>
+        <v>128203156</v>
       </c>
       <c r="B96" t="n">
-        <v>98472</v>
+        <v>98396</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11348,37 +11344,46 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736314</v>
+        <v>736221</v>
       </c>
       <c r="R96" t="n">
-        <v>6411572</v>
+        <v>6411593</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11410,11 +11415,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11444,32 +11444,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203106</v>
+        <v>128203087</v>
       </c>
       <c r="B97" t="n">
-        <v>98472</v>
+        <v>109305</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736305</v>
+        <v>736474</v>
       </c>
       <c r="R97" t="n">
-        <v>6411739</v>
+        <v>6411506</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11517,11 +11517,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11533,7 +11528,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11551,57 +11546,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203167</v>
+        <v>128203246</v>
       </c>
       <c r="B98" t="n">
-        <v>98448</v>
+        <v>109305</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736275</v>
+        <v>736213</v>
       </c>
       <c r="R98" t="n">
-        <v>6411455</v>
+        <v>6411456</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11631,6 +11617,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11662,10 +11653,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203246</v>
+        <v>128203080</v>
       </c>
       <c r="B99" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11697,13 +11688,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736213</v>
+        <v>736347</v>
       </c>
       <c r="R99" t="n">
-        <v>6411456</v>
+        <v>6411466</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11733,11 +11724,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11769,32 +11755,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203087</v>
+        <v>128203106</v>
       </c>
       <c r="B100" t="n">
-        <v>109297</v>
+        <v>98480</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11804,10 +11790,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736474</v>
+        <v>736305</v>
       </c>
       <c r="R100" t="n">
-        <v>6411506</v>
+        <v>6411739</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11842,6 +11828,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11853,7 +11844,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11871,45 +11862,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203080</v>
+        <v>128203167</v>
       </c>
       <c r="B101" t="n">
-        <v>109297</v>
+        <v>98456</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736347</v>
+        <v>736275</v>
       </c>
       <c r="R101" t="n">
-        <v>6411466</v>
+        <v>6411455</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11973,54 +11973,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203154</v>
+        <v>128203129</v>
       </c>
       <c r="B102" t="n">
-        <v>98378</v>
+        <v>105414</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R102" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12066,7 +12057,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12084,10 +12075,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203126</v>
+        <v>128203154</v>
       </c>
       <c r="B103" t="n">
-        <v>98472</v>
+        <v>98386</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12095,26 +12086,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219811</v>
+        <v>219788</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12128,13 +12119,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R103" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12177,7 +12168,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12195,35 +12186,44 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203129</v>
+        <v>128203126</v>
       </c>
       <c r="B104" t="n">
-        <v>105406</v>
+        <v>98480</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12297,57 +12297,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203207</v>
+        <v>128203242</v>
       </c>
       <c r="B105" t="n">
-        <v>98472</v>
+        <v>109305</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736300</v>
+        <v>736237</v>
       </c>
       <c r="R105" t="n">
-        <v>6411576</v>
+        <v>6411484</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12379,6 +12370,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12390,7 +12386,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12408,32 +12404,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203177</v>
+        <v>128203255</v>
       </c>
       <c r="B106" t="n">
-        <v>98455</v>
+        <v>109305</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12443,10 +12439,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736300</v>
+        <v>736200</v>
       </c>
       <c r="R106" t="n">
-        <v>6411481</v>
+        <v>6411456</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12481,11 +12477,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12497,7 +12488,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12515,57 +12506,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203234</v>
+        <v>128203107</v>
       </c>
       <c r="B107" t="n">
-        <v>98448</v>
+        <v>105414</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736279</v>
+        <v>736305</v>
       </c>
       <c r="R107" t="n">
-        <v>6411517</v>
+        <v>6411739</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12597,6 +12579,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12608,7 +12595,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12626,32 +12613,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203107</v>
+        <v>128203177</v>
       </c>
       <c r="B108" t="n">
-        <v>105406</v>
+        <v>98463</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221137</v>
+        <v>219799</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12661,10 +12648,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736305</v>
+        <v>736300</v>
       </c>
       <c r="R108" t="n">
-        <v>6411739</v>
+        <v>6411481</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12701,7 +12688,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12715,7 +12702,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12733,48 +12720,57 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203255</v>
+        <v>128203234</v>
       </c>
       <c r="B109" t="n">
-        <v>109297</v>
+        <v>98456</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736200</v>
+        <v>736279</v>
       </c>
       <c r="R109" t="n">
-        <v>6411456</v>
+        <v>6411517</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12835,48 +12831,57 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203242</v>
+        <v>128203207</v>
       </c>
       <c r="B110" t="n">
-        <v>109297</v>
+        <v>98480</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736237</v>
+        <v>736300</v>
       </c>
       <c r="R110" t="n">
-        <v>6411484</v>
+        <v>6411576</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12908,11 +12913,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12942,54 +12942,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128203160</v>
+        <v>128203161</v>
       </c>
       <c r="B111" t="n">
-        <v>98448</v>
+        <v>109305</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>736240</v>
+        <v>736250</v>
       </c>
       <c r="R111" t="n">
-        <v>6411466</v>
+        <v>6411464</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13053,57 +13044,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128203138</v>
+        <v>128203236</v>
       </c>
       <c r="B112" t="n">
-        <v>98455</v>
+        <v>109305</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>736231</v>
+        <v>736279</v>
       </c>
       <c r="R112" t="n">
-        <v>6411673</v>
+        <v>6411517</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13135,6 +13117,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13146,7 +13133,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13164,10 +13151,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128203094</v>
+        <v>128203160</v>
       </c>
       <c r="B113" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13208,10 +13195,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>736498</v>
+        <v>736240</v>
       </c>
       <c r="R113" t="n">
-        <v>6411566</v>
+        <v>6411466</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13275,48 +13262,57 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128203236</v>
+        <v>128203138</v>
       </c>
       <c r="B114" t="n">
-        <v>109297</v>
+        <v>98463</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>736279</v>
+        <v>736231</v>
       </c>
       <c r="R114" t="n">
-        <v>6411517</v>
+        <v>6411673</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13348,11 +13344,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13364,7 +13355,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13382,45 +13373,54 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128203161</v>
+        <v>128203094</v>
       </c>
       <c r="B115" t="n">
-        <v>109297</v>
+        <v>98456</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>736250</v>
+        <v>736498</v>
       </c>
       <c r="R115" t="n">
-        <v>6411464</v>
+        <v>6411566</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13487,7 +13487,7 @@
         <v>128203215</v>
       </c>
       <c r="B116" t="n">
-        <v>98455</v>
+        <v>98463</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>128203134</v>
       </c>
       <c r="B117" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>128203247</v>
       </c>
       <c r="B118" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>128203159</v>
       </c>
       <c r="B119" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128203101</v>
       </c>
       <c r="B120" t="n">
-        <v>98378</v>
+        <v>98386</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14026,57 +14026,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128203213</v>
+        <v>128203230</v>
       </c>
       <c r="B121" t="n">
-        <v>98472</v>
+        <v>109305</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>736301</v>
+        <v>736270</v>
       </c>
       <c r="R121" t="n">
-        <v>6411564</v>
+        <v>6411530</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14108,6 +14099,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14119,7 +14115,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14137,48 +14133,57 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128203230</v>
+        <v>128203213</v>
       </c>
       <c r="B122" t="n">
-        <v>109297</v>
+        <v>98480</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>736270</v>
+        <v>736301</v>
       </c>
       <c r="R122" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14210,11 +14215,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14244,27 +14244,27 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128203235</v>
+        <v>128203151</v>
       </c>
       <c r="B123" t="n">
-        <v>110354</v>
+        <v>109305</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -14279,13 +14279,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>736279</v>
+        <v>736248</v>
       </c>
       <c r="R123" t="n">
-        <v>6411517</v>
+        <v>6411616</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14315,6 +14315,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14349,7 +14354,7 @@
         <v>128203091</v>
       </c>
       <c r="B124" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14448,48 +14453,57 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203151</v>
+        <v>128203190</v>
       </c>
       <c r="B125" t="n">
-        <v>109297</v>
+        <v>98456</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736248</v>
+        <v>736335</v>
       </c>
       <c r="R125" t="n">
-        <v>6411616</v>
+        <v>6411533</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14519,11 +14533,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14555,10 +14564,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203190</v>
+        <v>128203216</v>
       </c>
       <c r="B126" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14599,10 +14608,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736335</v>
+        <v>736297</v>
       </c>
       <c r="R126" t="n">
-        <v>6411533</v>
+        <v>6411559</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14635,6 +14644,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14666,10 +14680,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203216</v>
+        <v>128203092</v>
       </c>
       <c r="B127" t="n">
-        <v>98448</v>
+        <v>98456</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14696,7 +14710,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -14710,13 +14724,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736297</v>
+        <v>736520</v>
       </c>
       <c r="R127" t="n">
-        <v>6411559</v>
+        <v>6411544</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14746,11 +14760,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14782,10 +14791,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203092</v>
+        <v>128203235</v>
       </c>
       <c r="B128" t="n">
-        <v>98448</v>
+        <v>110362</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14793,46 +14802,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736520</v>
+        <v>736279</v>
       </c>
       <c r="R128" t="n">
-        <v>6411544</v>
+        <v>6411517</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>128203112</v>
       </c>
       <c r="B129" t="n">
-        <v>98455</v>
+        <v>98463</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>128203113</v>
       </c>
       <c r="B130" t="n">
-        <v>98472</v>
+        <v>98480</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>128203252</v>
       </c>
       <c r="B131" t="n">
-        <v>98492</v>
+        <v>98500</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>128203093</v>
       </c>
       <c r="B132" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>128203178</v>
       </c>
       <c r="B133" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15427,48 +15427,57 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203164</v>
+        <v>128203139</v>
       </c>
       <c r="B134" t="n">
-        <v>109297</v>
+        <v>98482</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220299</v>
+        <v>741</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Wahlenb.) K. Richt.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736260</v>
+        <v>736244</v>
       </c>
       <c r="R134" t="n">
-        <v>6411450</v>
+        <v>6411666</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15529,57 +15538,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203228</v>
+        <v>128203083</v>
       </c>
       <c r="B135" t="n">
-        <v>98455</v>
+        <v>109305</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736263</v>
+        <v>736442</v>
       </c>
       <c r="R135" t="n">
-        <v>6411533</v>
+        <v>6411479</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15640,57 +15640,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203127</v>
+        <v>128203164</v>
       </c>
       <c r="B136" t="n">
-        <v>98455</v>
+        <v>109305</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736239</v>
+        <v>736260</v>
       </c>
       <c r="R136" t="n">
-        <v>6411738</v>
+        <v>6411450</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15733,7 +15724,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15751,10 +15742,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203139</v>
+        <v>128203228</v>
       </c>
       <c r="B137" t="n">
-        <v>98474</v>
+        <v>98463</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15762,26 +15753,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15795,13 +15786,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736244</v>
+        <v>736263</v>
       </c>
       <c r="R137" t="n">
-        <v>6411666</v>
+        <v>6411533</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15844,7 +15835,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15862,48 +15853,57 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203083</v>
+        <v>128203127</v>
       </c>
       <c r="B138" t="n">
-        <v>109297</v>
+        <v>98463</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736442</v>
+        <v>736239</v>
       </c>
       <c r="R138" t="n">
-        <v>6411479</v>
+        <v>6411738</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15964,10 +15964,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203240</v>
+        <v>128203085</v>
       </c>
       <c r="B139" t="n">
-        <v>109297</v>
+        <v>109305</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15999,13 +15999,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736238</v>
+        <v>736450</v>
       </c>
       <c r="R139" t="n">
-        <v>6411496</v>
+        <v>6411486</v>
       </c>
       <c r="S139" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16035,11 +16035,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16071,57 +16066,48 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203084</v>
+        <v>128203240</v>
       </c>
       <c r="B140" t="n">
-        <v>98448</v>
+        <v>109305</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736442</v>
+        <v>736238</v>
       </c>
       <c r="R140" t="n">
-        <v>6411479</v>
+        <v>6411496</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16151,6 +16137,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16182,10 +16173,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203223</v>
+        <v>128203084</v>
       </c>
       <c r="B141" t="n">
-        <v>98378</v>
+        <v>98456</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16193,26 +16184,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16226,13 +16217,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736272</v>
+        <v>736442</v>
       </c>
       <c r="R141" t="n">
-        <v>6411536</v>
+        <v>6411479</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16275,7 +16266,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16293,10 +16284,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203231</v>
+        <v>128203223</v>
       </c>
       <c r="B142" t="n">
-        <v>98448</v>
+        <v>98386</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16304,26 +16295,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16337,10 +16328,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736270</v>
+        <v>736272</v>
       </c>
       <c r="R142" t="n">
-        <v>6411530</v>
+        <v>6411536</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16386,7 +16377,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -16404,48 +16395,57 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128203085</v>
+        <v>128203231</v>
       </c>
       <c r="B143" t="n">
-        <v>109297</v>
+        <v>98456</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>736450</v>
+        <v>736270</v>
       </c>
       <c r="R143" t="n">
-        <v>6411486</v>
+        <v>6411530</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203220</v>
+        <v>128203021</v>
       </c>
       <c r="B60" t="n">
-        <v>109305</v>
+        <v>57670</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,31 +7394,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7427,10 +7423,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736295</v>
+        <v>736197</v>
       </c>
       <c r="R60" t="n">
-        <v>6411551</v>
+        <v>6411554</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7463,11 +7459,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7499,7 +7490,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203144</v>
+        <v>128203220</v>
       </c>
       <c r="B61" t="n">
         <v>109305</v>
@@ -7529,7 +7520,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7543,13 +7534,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736246</v>
+        <v>736295</v>
       </c>
       <c r="R61" t="n">
-        <v>6411634</v>
+        <v>6411551</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7583,7 +7574,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7615,27 +7606,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203237</v>
+        <v>128203144</v>
       </c>
       <c r="B62" t="n">
-        <v>110362</v>
+        <v>109305</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7643,17 +7634,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736283</v>
+        <v>736246</v>
       </c>
       <c r="R62" t="n">
-        <v>6411500</v>
+        <v>6411634</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Överallt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7722,10 +7722,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203233</v>
+        <v>128203237</v>
       </c>
       <c r="B63" t="n">
-        <v>98463</v>
+        <v>110362</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7733,46 +7733,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219799</v>
+        <v>219677</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736276</v>
+        <v>736283</v>
       </c>
       <c r="R63" t="n">
-        <v>6411531</v>
+        <v>6411500</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7804,6 +7795,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7815,7 +7811,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7833,10 +7829,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203186</v>
+        <v>128203233</v>
       </c>
       <c r="B64" t="n">
-        <v>98500</v>
+        <v>98463</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7844,26 +7840,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219862</v>
+        <v>219799</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7877,10 +7873,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736331</v>
+        <v>736276</v>
       </c>
       <c r="R64" t="n">
-        <v>6411530</v>
+        <v>6411531</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7926,7 +7922,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7944,38 +7940,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203021</v>
+        <v>128203186</v>
       </c>
       <c r="B65" t="n">
-        <v>57670</v>
+        <v>98500</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736197</v>
+        <v>736331</v>
       </c>
       <c r="R65" t="n">
-        <v>6411554</v>
+        <v>6411530</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -12297,48 +12297,57 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203242</v>
+        <v>128203207</v>
       </c>
       <c r="B105" t="n">
-        <v>109305</v>
+        <v>98480</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736237</v>
+        <v>736300</v>
       </c>
       <c r="R105" t="n">
-        <v>6411484</v>
+        <v>6411576</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12370,11 +12379,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12386,7 +12390,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12404,32 +12408,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203255</v>
+        <v>128203177</v>
       </c>
       <c r="B106" t="n">
-        <v>109305</v>
+        <v>98463</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12439,10 +12443,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736200</v>
+        <v>736300</v>
       </c>
       <c r="R106" t="n">
-        <v>6411456</v>
+        <v>6411481</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12477,6 +12481,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12488,7 +12497,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12506,48 +12515,57 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203107</v>
+        <v>128203234</v>
       </c>
       <c r="B107" t="n">
-        <v>105414</v>
+        <v>98456</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736305</v>
+        <v>736279</v>
       </c>
       <c r="R107" t="n">
-        <v>6411739</v>
+        <v>6411517</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12579,11 +12597,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12595,7 +12608,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12613,32 +12626,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203177</v>
+        <v>128203107</v>
       </c>
       <c r="B108" t="n">
-        <v>98463</v>
+        <v>105414</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12648,10 +12661,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736300</v>
+        <v>736305</v>
       </c>
       <c r="R108" t="n">
-        <v>6411481</v>
+        <v>6411739</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12688,7 +12701,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12702,7 +12715,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12720,57 +12733,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203234</v>
+        <v>128203242</v>
       </c>
       <c r="B109" t="n">
-        <v>98456</v>
+        <v>109305</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736279</v>
+        <v>736237</v>
       </c>
       <c r="R109" t="n">
-        <v>6411517</v>
+        <v>6411484</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12800,6 +12804,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12831,57 +12840,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203207</v>
+        <v>128203255</v>
       </c>
       <c r="B110" t="n">
-        <v>98480</v>
+        <v>109305</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736300</v>
+        <v>736200</v>
       </c>
       <c r="R110" t="n">
-        <v>6411576</v>
+        <v>6411456</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15538,48 +15538,57 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203083</v>
+        <v>128203228</v>
       </c>
       <c r="B135" t="n">
-        <v>109305</v>
+        <v>98463</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736442</v>
+        <v>736263</v>
       </c>
       <c r="R135" t="n">
-        <v>6411479</v>
+        <v>6411533</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15622,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15640,48 +15649,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203164</v>
+        <v>128203127</v>
       </c>
       <c r="B136" t="n">
-        <v>109305</v>
+        <v>98463</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736260</v>
+        <v>736239</v>
       </c>
       <c r="R136" t="n">
-        <v>6411450</v>
+        <v>6411738</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15724,7 +15742,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15742,57 +15760,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203228</v>
+        <v>128203083</v>
       </c>
       <c r="B137" t="n">
-        <v>98463</v>
+        <v>109305</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736263</v>
+        <v>736442</v>
       </c>
       <c r="R137" t="n">
-        <v>6411533</v>
+        <v>6411479</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15835,7 +15844,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15853,57 +15862,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203127</v>
+        <v>128203164</v>
       </c>
       <c r="B138" t="n">
-        <v>98463</v>
+        <v>109305</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736239</v>
+        <v>736260</v>
       </c>
       <c r="R138" t="n">
-        <v>6411738</v>
+        <v>6411450</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6403,7 +6403,7 @@
         <v>128203088</v>
       </c>
       <c r="B51" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128203259</v>
       </c>
       <c r="B52" t="n">
-        <v>110362</v>
+        <v>110455</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>128203131</v>
       </c>
       <c r="B53" t="n">
-        <v>105414</v>
+        <v>105507</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6729,48 +6729,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203241</v>
+        <v>128203195</v>
       </c>
       <c r="B54" t="n">
-        <v>109305</v>
+        <v>98479</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736223</v>
+        <v>736314</v>
       </c>
       <c r="R54" t="n">
-        <v>6411512</v>
+        <v>6411572</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6804,7 +6813,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6818,7 +6827,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6836,10 +6845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203195</v>
+        <v>128203096</v>
       </c>
       <c r="B55" t="n">
-        <v>98386</v>
+        <v>98549</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6847,26 +6856,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6880,13 +6889,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736314</v>
+        <v>736474</v>
       </c>
       <c r="R55" t="n">
-        <v>6411572</v>
+        <v>6411596</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6920,7 +6929,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6934,7 +6943,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6952,10 +6961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203096</v>
+        <v>128203100</v>
       </c>
       <c r="B56" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6982,7 +6991,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6996,10 +7005,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736474</v>
+        <v>736361</v>
       </c>
       <c r="R56" t="n">
-        <v>6411596</v>
+        <v>6411697</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7032,11 +7041,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7068,10 +7072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203100</v>
+        <v>128203179</v>
       </c>
       <c r="B57" t="n">
-        <v>98456</v>
+        <v>99612</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7079,43 +7083,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>222662</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736361</v>
+        <v>736300</v>
       </c>
       <c r="R57" t="n">
-        <v>6411697</v>
+        <v>6411481</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7161,7 +7156,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7182,7 +7177,7 @@
         <v>128203256</v>
       </c>
       <c r="B58" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7281,27 +7276,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203179</v>
+        <v>128203241</v>
       </c>
       <c r="B59" t="n">
-        <v>99519</v>
+        <v>109398</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7316,10 +7311,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736300</v>
+        <v>736223</v>
       </c>
       <c r="R59" t="n">
-        <v>6411481</v>
+        <v>6411512</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7354,6 +7349,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203021</v>
+        <v>128203144</v>
       </c>
       <c r="B60" t="n">
-        <v>57670</v>
+        <v>109398</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,27 +7394,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7423,13 +7427,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736197</v>
+        <v>736246</v>
       </c>
       <c r="R60" t="n">
-        <v>6411554</v>
+        <v>6411634</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7459,6 +7463,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7490,10 +7499,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203220</v>
+        <v>128203021</v>
       </c>
       <c r="B61" t="n">
-        <v>109305</v>
+        <v>57682</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7501,31 +7510,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7534,10 +7539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736295</v>
+        <v>736197</v>
       </c>
       <c r="R61" t="n">
-        <v>6411551</v>
+        <v>6411554</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7570,11 +7575,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7606,27 +7606,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203144</v>
+        <v>128203237</v>
       </c>
       <c r="B62" t="n">
-        <v>109305</v>
+        <v>110455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7634,26 +7634,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736246</v>
+        <v>736283</v>
       </c>
       <c r="R62" t="n">
-        <v>6411634</v>
+        <v>6411500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7690,7 +7681,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7722,10 +7713,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203237</v>
+        <v>128203233</v>
       </c>
       <c r="B63" t="n">
-        <v>110362</v>
+        <v>98556</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7733,37 +7724,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219677</v>
+        <v>219799</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736283</v>
+        <v>736276</v>
       </c>
       <c r="R63" t="n">
-        <v>6411500</v>
+        <v>6411531</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7795,11 +7795,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Överallt!</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7811,7 +7806,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7829,10 +7824,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203233</v>
+        <v>128203186</v>
       </c>
       <c r="B64" t="n">
-        <v>98463</v>
+        <v>98593</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7840,26 +7835,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219799</v>
+        <v>219862</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7873,10 +7868,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736276</v>
+        <v>736331</v>
       </c>
       <c r="R64" t="n">
-        <v>6411531</v>
+        <v>6411530</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7922,7 +7917,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7940,42 +7935,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203186</v>
+        <v>128203220</v>
       </c>
       <c r="B65" t="n">
-        <v>98500</v>
+        <v>109398</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7984,10 +7979,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736331</v>
+        <v>736295</v>
       </c>
       <c r="R65" t="n">
-        <v>6411530</v>
+        <v>6411551</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8020,6 +8015,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8054,7 +8054,7 @@
         <v>128203243</v>
       </c>
       <c r="B66" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>128203089</v>
       </c>
       <c r="B67" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203239</v>
+        <v>128203104</v>
       </c>
       <c r="B68" t="n">
-        <v>109305</v>
+        <v>105507</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8275,16 +8275,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8299,13 +8299,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736283</v>
+        <v>736325</v>
       </c>
       <c r="R68" t="n">
-        <v>6411500</v>
+        <v>6411730</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203095</v>
+        <v>128203239</v>
       </c>
       <c r="B69" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8406,13 +8406,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736474</v>
+        <v>736283</v>
       </c>
       <c r="R69" t="n">
-        <v>6411596</v>
+        <v>6411500</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8478,10 +8478,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203104</v>
+        <v>128203095</v>
       </c>
       <c r="B70" t="n">
-        <v>105414</v>
+        <v>109398</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8489,16 +8489,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736325</v>
+        <v>736474</v>
       </c>
       <c r="R70" t="n">
-        <v>6411730</v>
+        <v>6411596</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Spridd. Flera i blom.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8588,7 +8588,7 @@
         <v>128203209</v>
       </c>
       <c r="B71" t="n">
-        <v>98480</v>
+        <v>98573</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8696,35 +8696,44 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128203181</v>
+        <v>128203182</v>
       </c>
       <c r="B72" t="n">
-        <v>109305</v>
+        <v>98549</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8771,7 +8780,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8803,48 +8812,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128203166</v>
+        <v>128203187</v>
       </c>
       <c r="B73" t="n">
-        <v>109305</v>
+        <v>98549</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736275</v>
+        <v>736331</v>
       </c>
       <c r="R73" t="n">
-        <v>6411455</v>
+        <v>6411530</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8905,44 +8923,35 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203182</v>
+        <v>128203181</v>
       </c>
       <c r="B74" t="n">
-        <v>98456</v>
+        <v>109398</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8989,7 +8998,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Stig över våtmark; avsnitslat.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9021,57 +9030,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128203187</v>
+        <v>128203166</v>
       </c>
       <c r="B75" t="n">
-        <v>98456</v>
+        <v>109398</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736331</v>
+        <v>736275</v>
       </c>
       <c r="R75" t="n">
-        <v>6411530</v>
+        <v>6411455</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>98484</v>
+        <v>98577</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9248,54 +9248,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203023</v>
+        <v>128203199</v>
       </c>
       <c r="B77" t="n">
-        <v>57670</v>
+        <v>98556</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>219799</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736365</v>
+        <v>736314</v>
       </c>
       <c r="R77" t="n">
-        <v>6411573</v>
+        <v>6411572</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9330,6 +9321,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9341,7 +9337,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9359,48 +9355,57 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203189</v>
+        <v>128203086</v>
       </c>
       <c r="B78" t="n">
-        <v>109305</v>
+        <v>98549</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736335</v>
+        <v>736450</v>
       </c>
       <c r="R78" t="n">
-        <v>6411533</v>
+        <v>6411486</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9461,45 +9466,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203185</v>
+        <v>128203221</v>
       </c>
       <c r="B79" t="n">
-        <v>109305</v>
+        <v>98573</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736331</v>
+        <v>736272</v>
       </c>
       <c r="R79" t="n">
-        <v>6411530</v>
+        <v>6411546</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9534,11 +9548,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9550,7 +9559,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9568,10 +9577,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203099</v>
+        <v>128203189</v>
       </c>
       <c r="B80" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9596,29 +9605,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736361</v>
+        <v>736335</v>
       </c>
       <c r="R80" t="n">
-        <v>6411697</v>
+        <v>6411533</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9679,32 +9679,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203199</v>
+        <v>128203185</v>
       </c>
       <c r="B81" t="n">
-        <v>98463</v>
+        <v>109398</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9714,13 +9714,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736314</v>
+        <v>736331</v>
       </c>
       <c r="R81" t="n">
-        <v>6411572</v>
+        <v>6411530</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9786,42 +9786,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203086</v>
+        <v>128203099</v>
       </c>
       <c r="B82" t="n">
-        <v>98456</v>
+        <v>109398</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9830,10 +9830,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736450</v>
+        <v>736361</v>
       </c>
       <c r="R82" t="n">
-        <v>6411486</v>
+        <v>6411697</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9897,32 +9897,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203221</v>
+        <v>128203023</v>
       </c>
       <c r="B83" t="n">
-        <v>98480</v>
+        <v>57682</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219811</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9930,9 +9930,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736272</v>
+        <v>736365</v>
       </c>
       <c r="R83" t="n">
-        <v>6411546</v>
+        <v>6411573</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10008,37 +10008,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203192</v>
+        <v>128203249</v>
       </c>
       <c r="B84" t="n">
-        <v>105414</v>
+        <v>98549</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736339</v>
+        <v>736192</v>
       </c>
       <c r="R84" t="n">
-        <v>6411571</v>
+        <v>6411467</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10090,11 +10090,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10106,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10124,10 +10119,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203249</v>
+        <v>128203162</v>
       </c>
       <c r="B85" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10154,7 +10149,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10168,13 +10163,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736192</v>
+        <v>736250</v>
       </c>
       <c r="R85" t="n">
-        <v>6411467</v>
+        <v>6411464</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10235,37 +10230,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203132</v>
+        <v>128203111</v>
       </c>
       <c r="B86" t="n">
-        <v>107363</v>
+        <v>98502</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220079</v>
+        <v>219794</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10279,13 +10274,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736242</v>
+        <v>736184</v>
       </c>
       <c r="R86" t="n">
-        <v>6411713</v>
+        <v>6411805</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10317,6 +10312,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10346,37 +10346,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203162</v>
+        <v>128203192</v>
       </c>
       <c r="B87" t="n">
-        <v>98456</v>
+        <v>105507</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736250</v>
+        <v>736339</v>
       </c>
       <c r="R87" t="n">
-        <v>6411464</v>
+        <v>6411571</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10428,6 +10428,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10444,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10457,37 +10462,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128203111</v>
+        <v>128203132</v>
       </c>
       <c r="B88" t="n">
-        <v>98409</v>
+        <v>107456</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219794</v>
+        <v>220079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10501,13 +10506,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>736184</v>
+        <v>736242</v>
       </c>
       <c r="R88" t="n">
-        <v>6411805</v>
+        <v>6411713</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10539,11 +10544,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10573,45 +10573,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203180</v>
+        <v>128203156</v>
       </c>
       <c r="B89" t="n">
-        <v>105414</v>
+        <v>98489</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221137</v>
+        <v>223591</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736300</v>
+        <v>736221</v>
       </c>
       <c r="R89" t="n">
-        <v>6411481</v>
+        <v>6411593</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10646,11 +10655,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10662,7 +10666,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10680,10 +10684,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203211</v>
+        <v>128205915</v>
       </c>
       <c r="B90" t="n">
-        <v>99153</v>
+        <v>57682</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10691,37 +10695,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736301</v>
+        <v>736315</v>
       </c>
       <c r="R90" t="n">
-        <v>6411564</v>
+        <v>6411597</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10764,7 +10777,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10782,42 +10795,42 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B91" t="n">
-        <v>57670</v>
+        <v>98549</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10826,13 +10839,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R91" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10893,10 +10906,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203165</v>
+        <v>128203081</v>
       </c>
       <c r="B92" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10923,7 +10936,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10937,10 +10950,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736260</v>
+        <v>736347</v>
       </c>
       <c r="R92" t="n">
-        <v>6411450</v>
+        <v>6411466</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11004,10 +11017,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203081</v>
+        <v>128203225</v>
       </c>
       <c r="B93" t="n">
-        <v>98456</v>
+        <v>98573</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11015,21 +11028,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11048,13 +11061,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736347</v>
+        <v>736263</v>
       </c>
       <c r="R93" t="n">
-        <v>6411466</v>
+        <v>6411533</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11097,7 +11110,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11115,10 +11128,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203225</v>
+        <v>128203197</v>
       </c>
       <c r="B94" t="n">
-        <v>98480</v>
+        <v>98573</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11143,29 +11156,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736263</v>
+        <v>736314</v>
       </c>
       <c r="R94" t="n">
-        <v>6411533</v>
+        <v>6411572</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11197,6 +11201,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11208,7 +11217,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11226,32 +11235,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203197</v>
+        <v>128203211</v>
       </c>
       <c r="B95" t="n">
-        <v>98480</v>
+        <v>99246</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11261,13 +11270,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736314</v>
+        <v>736301</v>
       </c>
       <c r="R95" t="n">
-        <v>6411572</v>
+        <v>6411564</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11297,11 +11306,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11333,54 +11337,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203156</v>
+        <v>128203180</v>
       </c>
       <c r="B96" t="n">
-        <v>98396</v>
+        <v>105507</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>223591</v>
+        <v>221137</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736221</v>
+        <v>736300</v>
       </c>
       <c r="R96" t="n">
-        <v>6411593</v>
+        <v>6411481</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11415,6 +11410,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11444,10 +11444,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203087</v>
+        <v>128203246</v>
       </c>
       <c r="B97" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11479,13 +11479,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736474</v>
+        <v>736213</v>
       </c>
       <c r="R97" t="n">
-        <v>6411506</v>
+        <v>6411456</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11515,6 +11515,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11546,32 +11551,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203246</v>
+        <v>128203106</v>
       </c>
       <c r="B98" t="n">
-        <v>109305</v>
+        <v>98573</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11581,13 +11586,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736213</v>
+        <v>736305</v>
       </c>
       <c r="R98" t="n">
-        <v>6411456</v>
+        <v>6411739</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11621,7 +11626,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11635,7 +11640,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11653,45 +11658,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203080</v>
+        <v>128203167</v>
       </c>
       <c r="B99" t="n">
-        <v>109305</v>
+        <v>98549</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736347</v>
+        <v>736275</v>
       </c>
       <c r="R99" t="n">
-        <v>6411466</v>
+        <v>6411455</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11755,32 +11769,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203106</v>
+        <v>128203087</v>
       </c>
       <c r="B100" t="n">
-        <v>98480</v>
+        <v>109398</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11790,10 +11804,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736305</v>
+        <v>736474</v>
       </c>
       <c r="R100" t="n">
-        <v>6411739</v>
+        <v>6411506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11828,11 +11842,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11844,7 +11853,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11862,54 +11871,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203167</v>
+        <v>128203080</v>
       </c>
       <c r="B101" t="n">
-        <v>98456</v>
+        <v>109398</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736275</v>
+        <v>736347</v>
       </c>
       <c r="R101" t="n">
-        <v>6411455</v>
+        <v>6411466</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11976,7 +11976,7 @@
         <v>128203129</v>
       </c>
       <c r="B102" t="n">
-        <v>105414</v>
+        <v>105507</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>128203154</v>
       </c>
       <c r="B103" t="n">
-        <v>98386</v>
+        <v>98479</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>128203126</v>
       </c>
       <c r="B104" t="n">
-        <v>98480</v>
+        <v>98573</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>128203207</v>
       </c>
       <c r="B105" t="n">
-        <v>98480</v>
+        <v>98573</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>128203177</v>
       </c>
       <c r="B106" t="n">
-        <v>98463</v>
+        <v>98556</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>128203234</v>
       </c>
       <c r="B107" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>128203107</v>
       </c>
       <c r="B108" t="n">
-        <v>105414</v>
+        <v>105507</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>128203242</v>
       </c>
       <c r="B109" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>128203255</v>
       </c>
       <c r="B110" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12942,45 +12942,54 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128203161</v>
+        <v>128203160</v>
       </c>
       <c r="B111" t="n">
-        <v>109305</v>
+        <v>98549</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>736250</v>
+        <v>736240</v>
       </c>
       <c r="R111" t="n">
-        <v>6411464</v>
+        <v>6411466</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13044,48 +13053,57 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128203236</v>
+        <v>128203138</v>
       </c>
       <c r="B112" t="n">
-        <v>109305</v>
+        <v>98556</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>736279</v>
+        <v>736231</v>
       </c>
       <c r="R112" t="n">
-        <v>6411517</v>
+        <v>6411673</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13117,11 +13135,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13133,7 +13146,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13151,10 +13164,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128203160</v>
+        <v>128203094</v>
       </c>
       <c r="B113" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13195,10 +13208,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>736240</v>
+        <v>736498</v>
       </c>
       <c r="R113" t="n">
-        <v>6411466</v>
+        <v>6411566</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13262,57 +13275,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128203138</v>
+        <v>128203161</v>
       </c>
       <c r="B114" t="n">
-        <v>98463</v>
+        <v>109398</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>736231</v>
+        <v>736250</v>
       </c>
       <c r="R114" t="n">
-        <v>6411673</v>
+        <v>6411464</v>
       </c>
       <c r="S114" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13355,7 +13359,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13373,57 +13377,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128203094</v>
+        <v>128203236</v>
       </c>
       <c r="B115" t="n">
-        <v>98456</v>
+        <v>109398</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>736498</v>
+        <v>736279</v>
       </c>
       <c r="R115" t="n">
-        <v>6411566</v>
+        <v>6411517</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13453,6 +13448,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13487,7 +13487,7 @@
         <v>128203215</v>
       </c>
       <c r="B116" t="n">
-        <v>98463</v>
+        <v>98556</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>128203134</v>
       </c>
       <c r="B117" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>128203247</v>
       </c>
       <c r="B118" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13808,48 +13808,57 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128203159</v>
+        <v>128203101</v>
       </c>
       <c r="B119" t="n">
-        <v>109305</v>
+        <v>98479</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>736240</v>
+        <v>736358</v>
       </c>
       <c r="R119" t="n">
-        <v>6411466</v>
+        <v>6411725</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13881,11 +13890,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13897,7 +13901,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13915,57 +13919,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128203101</v>
+        <v>128203159</v>
       </c>
       <c r="B120" t="n">
-        <v>98386</v>
+        <v>109398</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>736358</v>
+        <v>736240</v>
       </c>
       <c r="R120" t="n">
-        <v>6411725</v>
+        <v>6411466</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13997,6 +13992,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14026,48 +14026,57 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128203230</v>
+        <v>128203213</v>
       </c>
       <c r="B121" t="n">
-        <v>109305</v>
+        <v>98573</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>736270</v>
+        <v>736301</v>
       </c>
       <c r="R121" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14099,11 +14108,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14115,7 +14119,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14133,57 +14137,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128203213</v>
+        <v>128203230</v>
       </c>
       <c r="B122" t="n">
-        <v>98480</v>
+        <v>109398</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>736301</v>
+        <v>736270</v>
       </c>
       <c r="R122" t="n">
-        <v>6411564</v>
+        <v>6411530</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14215,6 +14210,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14244,48 +14244,57 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128203151</v>
+        <v>128203190</v>
       </c>
       <c r="B123" t="n">
-        <v>109305</v>
+        <v>98549</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>736248</v>
+        <v>736335</v>
       </c>
       <c r="R123" t="n">
-        <v>6411616</v>
+        <v>6411533</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14315,11 +14324,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14351,48 +14355,57 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203091</v>
+        <v>128203216</v>
       </c>
       <c r="B124" t="n">
-        <v>109305</v>
+        <v>98549</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736520</v>
+        <v>736297</v>
       </c>
       <c r="R124" t="n">
-        <v>6411544</v>
+        <v>6411559</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14422,6 +14435,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14453,10 +14471,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203190</v>
+        <v>128203092</v>
       </c>
       <c r="B125" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14483,7 +14501,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14497,13 +14515,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736335</v>
+        <v>736520</v>
       </c>
       <c r="R125" t="n">
-        <v>6411533</v>
+        <v>6411544</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14564,10 +14582,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203216</v>
+        <v>128203235</v>
       </c>
       <c r="B126" t="n">
-        <v>98456</v>
+        <v>110455</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14575,43 +14593,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736297</v>
+        <v>736279</v>
       </c>
       <c r="R126" t="n">
-        <v>6411559</v>
+        <v>6411517</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14644,11 +14653,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14680,54 +14684,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203092</v>
+        <v>128203151</v>
       </c>
       <c r="B127" t="n">
-        <v>98456</v>
+        <v>109398</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736520</v>
+        <v>736248</v>
       </c>
       <c r="R127" t="n">
-        <v>6411544</v>
+        <v>6411616</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14760,6 +14755,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14791,27 +14791,27 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203235</v>
+        <v>128203091</v>
       </c>
       <c r="B128" t="n">
-        <v>110362</v>
+        <v>109398</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -14826,13 +14826,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736279</v>
+        <v>736520</v>
       </c>
       <c r="R128" t="n">
-        <v>6411517</v>
+        <v>6411544</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>128203112</v>
       </c>
       <c r="B129" t="n">
-        <v>98463</v>
+        <v>98556</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>128203113</v>
       </c>
       <c r="B130" t="n">
-        <v>98480</v>
+        <v>98573</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>128203252</v>
       </c>
       <c r="B131" t="n">
-        <v>98500</v>
+        <v>98593</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15218,32 +15218,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203093</v>
+        <v>128203178</v>
       </c>
       <c r="B132" t="n">
-        <v>109305</v>
+        <v>98098</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>221930</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15253,10 +15253,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736498</v>
+        <v>736300</v>
       </c>
       <c r="R132" t="n">
-        <v>6411566</v>
+        <v>6411481</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15291,6 +15291,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15302,7 +15307,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15320,32 +15325,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203178</v>
+        <v>128203093</v>
       </c>
       <c r="B133" t="n">
-        <v>98005</v>
+        <v>109398</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221930</v>
+        <v>220299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15355,10 +15360,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736300</v>
+        <v>736498</v>
       </c>
       <c r="R133" t="n">
-        <v>6411481</v>
+        <v>6411566</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15393,11 +15398,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203139</v>
+        <v>128203228</v>
       </c>
       <c r="B134" t="n">
-        <v>98482</v>
+        <v>98556</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15438,26 +15438,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736244</v>
+        <v>736263</v>
       </c>
       <c r="R134" t="n">
-        <v>6411666</v>
+        <v>6411533</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,10 +15538,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203228</v>
+        <v>128203127</v>
       </c>
       <c r="B135" t="n">
-        <v>98463</v>
+        <v>98556</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15582,10 +15582,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736263</v>
+        <v>736239</v>
       </c>
       <c r="R135" t="n">
-        <v>6411533</v>
+        <v>6411738</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15649,57 +15649,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203127</v>
+        <v>128203083</v>
       </c>
       <c r="B136" t="n">
-        <v>98463</v>
+        <v>109398</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736239</v>
+        <v>736442</v>
       </c>
       <c r="R136" t="n">
-        <v>6411738</v>
+        <v>6411479</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15742,7 +15733,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15760,10 +15751,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203083</v>
+        <v>128203164</v>
       </c>
       <c r="B137" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15795,10 +15786,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736442</v>
+        <v>736260</v>
       </c>
       <c r="R137" t="n">
-        <v>6411479</v>
+        <v>6411450</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15862,48 +15853,57 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203164</v>
+        <v>128203139</v>
       </c>
       <c r="B138" t="n">
-        <v>109305</v>
+        <v>98575</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220299</v>
+        <v>741</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Wahlenb.) K. Richt.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736260</v>
+        <v>736244</v>
       </c>
       <c r="R138" t="n">
-        <v>6411450</v>
+        <v>6411666</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15967,7 +15967,7 @@
         <v>128203085</v>
       </c>
       <c r="B139" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>128203240</v>
       </c>
       <c r="B140" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>128203084</v>
       </c>
       <c r="B141" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>128203223</v>
       </c>
       <c r="B142" t="n">
-        <v>98386</v>
+        <v>98479</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>128203231</v>
       </c>
       <c r="B143" t="n">
-        <v>98456</v>
+        <v>98549</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -7072,27 +7072,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203179</v>
+        <v>128203256</v>
       </c>
       <c r="B57" t="n">
-        <v>99612</v>
+        <v>109398</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736300</v>
+        <v>736176</v>
       </c>
       <c r="R57" t="n">
-        <v>6411481</v>
+        <v>6411455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7174,7 +7174,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203256</v>
+        <v>128203241</v>
       </c>
       <c r="B58" t="n">
         <v>109398</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736176</v>
+        <v>736223</v>
       </c>
       <c r="R58" t="n">
-        <v>6411455</v>
+        <v>6411512</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7245,6 +7245,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7276,27 +7281,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203241</v>
+        <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>109398</v>
+        <v>99612</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7311,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736223</v>
+        <v>736300</v>
       </c>
       <c r="R59" t="n">
-        <v>6411512</v>
+        <v>6411481</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7349,11 +7354,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203144</v>
+        <v>128203021</v>
       </c>
       <c r="B60" t="n">
-        <v>109398</v>
+        <v>57682</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,31 +7394,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7427,13 +7423,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736246</v>
+        <v>736197</v>
       </c>
       <c r="R60" t="n">
-        <v>6411634</v>
+        <v>6411554</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7463,11 +7459,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7499,53 +7490,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203021</v>
+        <v>128203237</v>
       </c>
       <c r="B61" t="n">
-        <v>57682</v>
+        <v>110455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736197</v>
+        <v>736283</v>
       </c>
       <c r="R61" t="n">
-        <v>6411554</v>
+        <v>6411500</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7575,6 +7561,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7606,10 +7597,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203237</v>
+        <v>128203233</v>
       </c>
       <c r="B62" t="n">
-        <v>110455</v>
+        <v>98556</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,37 +7608,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219677</v>
+        <v>219799</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736283</v>
+        <v>736276</v>
       </c>
       <c r="R62" t="n">
-        <v>6411500</v>
+        <v>6411531</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7679,11 +7679,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Överallt!</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7695,7 +7690,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7713,10 +7708,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203233</v>
+        <v>128203186</v>
       </c>
       <c r="B63" t="n">
-        <v>98556</v>
+        <v>98593</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7724,26 +7719,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219799</v>
+        <v>219862</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7757,10 +7752,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736276</v>
+        <v>736331</v>
       </c>
       <c r="R63" t="n">
-        <v>6411531</v>
+        <v>6411530</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7806,7 +7801,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7824,42 +7819,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203186</v>
+        <v>128203220</v>
       </c>
       <c r="B64" t="n">
-        <v>98593</v>
+        <v>109398</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7868,10 +7863,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736331</v>
+        <v>736295</v>
       </c>
       <c r="R64" t="n">
-        <v>6411530</v>
+        <v>6411551</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7904,6 +7899,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7935,7 +7935,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203220</v>
+        <v>128203144</v>
       </c>
       <c r="B65" t="n">
         <v>109398</v>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7979,13 +7979,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736295</v>
+        <v>736246</v>
       </c>
       <c r="R65" t="n">
-        <v>6411551</v>
+        <v>6411634</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8051,45 +8051,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128203243</v>
+        <v>128203089</v>
       </c>
       <c r="B66" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>736237</v>
+        <v>736488</v>
       </c>
       <c r="R66" t="n">
-        <v>6411472</v>
+        <v>6411510</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8135,7 +8144,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8153,54 +8162,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128203089</v>
+        <v>128203243</v>
       </c>
       <c r="B67" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>736488</v>
+        <v>736237</v>
       </c>
       <c r="R67" t="n">
-        <v>6411510</v>
+        <v>6411472</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8264,48 +8264,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203104</v>
+        <v>128203209</v>
       </c>
       <c r="B68" t="n">
-        <v>105507</v>
+        <v>98573</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736325</v>
+        <v>736295</v>
       </c>
       <c r="R68" t="n">
-        <v>6411730</v>
+        <v>6411567</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8337,11 +8346,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spridd. Flera i blom.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8353,7 +8357,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8585,57 +8589,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203209</v>
+        <v>128203104</v>
       </c>
       <c r="B71" t="n">
-        <v>98573</v>
+        <v>105507</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736295</v>
+        <v>736325</v>
       </c>
       <c r="R71" t="n">
-        <v>6411567</v>
+        <v>6411730</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8667,6 +8662,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Spridd. Flera i blom.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8696,44 +8696,35 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128203182</v>
+        <v>128203181</v>
       </c>
       <c r="B72" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8780,7 +8771,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Stig över våtmark; avsnitslat.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8812,57 +8803,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128203187</v>
+        <v>128203166</v>
       </c>
       <c r="B73" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736331</v>
+        <v>736275</v>
       </c>
       <c r="R73" t="n">
-        <v>6411530</v>
+        <v>6411455</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8923,35 +8905,44 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203181</v>
+        <v>128203182</v>
       </c>
       <c r="B74" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8998,7 +8989,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9030,48 +9021,57 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128203166</v>
+        <v>128203187</v>
       </c>
       <c r="B75" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736275</v>
+        <v>736331</v>
       </c>
       <c r="R75" t="n">
-        <v>6411455</v>
+        <v>6411530</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10346,10 +10346,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203192</v>
+        <v>128203132</v>
       </c>
       <c r="B87" t="n">
-        <v>105507</v>
+        <v>107456</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10357,26 +10357,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221137</v>
+        <v>220079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736339</v>
+        <v>736242</v>
       </c>
       <c r="R87" t="n">
-        <v>6411571</v>
+        <v>6411713</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10428,11 +10428,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10444,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10462,10 +10457,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128203132</v>
+        <v>128203192</v>
       </c>
       <c r="B88" t="n">
-        <v>107456</v>
+        <v>105507</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10473,26 +10468,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220079</v>
+        <v>221137</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10506,13 +10501,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>736242</v>
+        <v>736339</v>
       </c>
       <c r="R88" t="n">
-        <v>6411713</v>
+        <v>6411571</v>
       </c>
       <c r="S88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10544,6 +10539,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203156</v>
+        <v>128205915</v>
       </c>
       <c r="B89" t="n">
-        <v>98489</v>
+        <v>57682</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736221</v>
+        <v>736315</v>
       </c>
       <c r="R89" t="n">
-        <v>6411593</v>
+        <v>6411597</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10684,42 +10684,42 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B90" t="n">
-        <v>57682</v>
+        <v>98549</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10728,13 +10728,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R90" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203165</v>
+        <v>128203081</v>
       </c>
       <c r="B91" t="n">
         <v>98549</v>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10839,10 +10839,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736260</v>
+        <v>736347</v>
       </c>
       <c r="R91" t="n">
-        <v>6411450</v>
+        <v>6411466</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10906,10 +10906,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203081</v>
+        <v>128203225</v>
       </c>
       <c r="B92" t="n">
-        <v>98549</v>
+        <v>98573</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10917,21 +10917,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10950,13 +10950,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736347</v>
+        <v>736263</v>
       </c>
       <c r="R92" t="n">
-        <v>6411466</v>
+        <v>6411533</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11017,7 +11017,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203225</v>
+        <v>128203197</v>
       </c>
       <c r="B93" t="n">
         <v>98573</v>
@@ -11045,29 +11045,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736263</v>
+        <v>736314</v>
       </c>
       <c r="R93" t="n">
-        <v>6411533</v>
+        <v>6411572</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11099,6 +11090,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -11110,7 +11106,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11128,10 +11124,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203197</v>
+        <v>128203156</v>
       </c>
       <c r="B94" t="n">
-        <v>98573</v>
+        <v>98489</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11139,37 +11135,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736314</v>
+        <v>736221</v>
       </c>
       <c r="R94" t="n">
-        <v>6411572</v>
+        <v>6411593</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11201,11 +11206,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203246</v>
+        <v>128203087</v>
       </c>
       <c r="B97" t="n">
         <v>109398</v>
@@ -11479,13 +11479,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736213</v>
+        <v>736474</v>
       </c>
       <c r="R97" t="n">
-        <v>6411456</v>
+        <v>6411506</v>
       </c>
       <c r="S97" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11515,11 +11515,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11551,32 +11546,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203106</v>
+        <v>128203246</v>
       </c>
       <c r="B98" t="n">
-        <v>98573</v>
+        <v>109398</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11586,13 +11581,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736305</v>
+        <v>736213</v>
       </c>
       <c r="R98" t="n">
-        <v>6411739</v>
+        <v>6411456</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11626,7 +11621,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11640,7 +11635,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11658,54 +11653,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203167</v>
+        <v>128203080</v>
       </c>
       <c r="B99" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736275</v>
+        <v>736347</v>
       </c>
       <c r="R99" t="n">
-        <v>6411455</v>
+        <v>6411466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11769,32 +11755,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203087</v>
+        <v>128203106</v>
       </c>
       <c r="B100" t="n">
-        <v>109398</v>
+        <v>98573</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11804,10 +11790,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736474</v>
+        <v>736305</v>
       </c>
       <c r="R100" t="n">
-        <v>6411506</v>
+        <v>6411739</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11842,6 +11828,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -11853,7 +11844,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11871,45 +11862,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203080</v>
+        <v>128203167</v>
       </c>
       <c r="B101" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736347</v>
+        <v>736275</v>
       </c>
       <c r="R101" t="n">
-        <v>6411466</v>
+        <v>6411455</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11973,45 +11973,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203129</v>
+        <v>128203154</v>
       </c>
       <c r="B102" t="n">
-        <v>105507</v>
+        <v>98479</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221137</v>
+        <v>219788</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R102" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12057,7 +12066,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12075,10 +12084,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203154</v>
+        <v>128203126</v>
       </c>
       <c r="B103" t="n">
-        <v>98479</v>
+        <v>98573</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12086,26 +12095,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219788</v>
+        <v>219811</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12119,13 +12128,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R103" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12168,7 +12177,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12186,44 +12195,35 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203126</v>
+        <v>128203129</v>
       </c>
       <c r="B104" t="n">
-        <v>98573</v>
+        <v>105507</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12297,57 +12297,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203207</v>
+        <v>128203242</v>
       </c>
       <c r="B105" t="n">
-        <v>98573</v>
+        <v>109398</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736300</v>
+        <v>736237</v>
       </c>
       <c r="R105" t="n">
-        <v>6411576</v>
+        <v>6411484</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12379,6 +12370,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12390,7 +12386,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12408,32 +12404,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203177</v>
+        <v>128203255</v>
       </c>
       <c r="B106" t="n">
-        <v>98556</v>
+        <v>109398</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12443,10 +12439,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736300</v>
+        <v>736200</v>
       </c>
       <c r="R106" t="n">
-        <v>6411481</v>
+        <v>6411456</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12481,11 +12477,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12497,7 +12488,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12515,10 +12506,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203234</v>
+        <v>128203207</v>
       </c>
       <c r="B107" t="n">
-        <v>98549</v>
+        <v>98573</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12526,26 +12517,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12559,10 +12550,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736279</v>
+        <v>736300</v>
       </c>
       <c r="R107" t="n">
-        <v>6411517</v>
+        <v>6411576</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12608,7 +12599,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12626,32 +12617,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203107</v>
+        <v>128203177</v>
       </c>
       <c r="B108" t="n">
-        <v>105507</v>
+        <v>98556</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221137</v>
+        <v>219799</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12661,10 +12652,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736305</v>
+        <v>736300</v>
       </c>
       <c r="R108" t="n">
-        <v>6411739</v>
+        <v>6411481</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12701,7 +12692,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12715,7 +12706,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12733,48 +12724,57 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203242</v>
+        <v>128203234</v>
       </c>
       <c r="B109" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736237</v>
+        <v>736279</v>
       </c>
       <c r="R109" t="n">
-        <v>6411484</v>
+        <v>6411517</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12804,11 +12804,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12840,10 +12835,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203255</v>
+        <v>128203107</v>
       </c>
       <c r="B110" t="n">
-        <v>109398</v>
+        <v>105507</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12851,16 +12846,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12875,10 +12870,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736200</v>
+        <v>736305</v>
       </c>
       <c r="R110" t="n">
-        <v>6411456</v>
+        <v>6411739</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12913,6 +12908,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15218,32 +15218,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203178</v>
+        <v>128203093</v>
       </c>
       <c r="B132" t="n">
-        <v>98098</v>
+        <v>109398</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221930</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15253,10 +15253,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736300</v>
+        <v>736498</v>
       </c>
       <c r="R132" t="n">
-        <v>6411481</v>
+        <v>6411566</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15291,11 +15291,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15307,7 +15302,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15325,32 +15320,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203093</v>
+        <v>128203178</v>
       </c>
       <c r="B133" t="n">
-        <v>109398</v>
+        <v>98098</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>221930</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15360,10 +15355,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736498</v>
+        <v>736300</v>
       </c>
       <c r="R133" t="n">
-        <v>6411566</v>
+        <v>6411481</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15398,6 +15393,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203228</v>
+        <v>128203139</v>
       </c>
       <c r="B134" t="n">
-        <v>98556</v>
+        <v>98575</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15438,26 +15438,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219799</v>
+        <v>741</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736263</v>
+        <v>736244</v>
       </c>
       <c r="R134" t="n">
-        <v>6411533</v>
+        <v>6411666</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,7 +15538,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203127</v>
+        <v>128203228</v>
       </c>
       <c r="B135" t="n">
         <v>98556</v>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15582,10 +15582,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736239</v>
+        <v>736263</v>
       </c>
       <c r="R135" t="n">
-        <v>6411738</v>
+        <v>6411533</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15649,48 +15649,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203083</v>
+        <v>128203127</v>
       </c>
       <c r="B136" t="n">
-        <v>109398</v>
+        <v>98556</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736442</v>
+        <v>736239</v>
       </c>
       <c r="R136" t="n">
-        <v>6411479</v>
+        <v>6411738</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15733,7 +15742,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15751,7 +15760,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203164</v>
+        <v>128203083</v>
       </c>
       <c r="B137" t="n">
         <v>109398</v>
@@ -15786,10 +15795,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736260</v>
+        <v>736442</v>
       </c>
       <c r="R137" t="n">
-        <v>6411450</v>
+        <v>6411479</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15853,57 +15862,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203139</v>
+        <v>128203164</v>
       </c>
       <c r="B138" t="n">
-        <v>98575</v>
+        <v>109398</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>741</v>
+        <v>220299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736244</v>
+        <v>736260</v>
       </c>
       <c r="R138" t="n">
-        <v>6411666</v>
+        <v>6411450</v>
       </c>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15964,45 +15964,54 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203085</v>
+        <v>128203084</v>
       </c>
       <c r="B139" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736450</v>
+        <v>736442</v>
       </c>
       <c r="R139" t="n">
-        <v>6411486</v>
+        <v>6411479</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16066,48 +16075,57 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203240</v>
+        <v>128203223</v>
       </c>
       <c r="B140" t="n">
-        <v>109398</v>
+        <v>98479</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736238</v>
+        <v>736272</v>
       </c>
       <c r="R140" t="n">
-        <v>6411496</v>
+        <v>6411536</v>
       </c>
       <c r="S140" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16139,11 +16157,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -16155,7 +16168,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16173,7 +16186,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203084</v>
+        <v>128203231</v>
       </c>
       <c r="B141" t="n">
         <v>98549</v>
@@ -16203,7 +16216,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16217,13 +16230,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736442</v>
+        <v>736270</v>
       </c>
       <c r="R141" t="n">
-        <v>6411479</v>
+        <v>6411530</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16284,57 +16297,48 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203223</v>
+        <v>128203085</v>
       </c>
       <c r="B142" t="n">
-        <v>98479</v>
+        <v>109398</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736272</v>
+        <v>736450</v>
       </c>
       <c r="R142" t="n">
-        <v>6411536</v>
+        <v>6411486</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16377,7 +16381,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -16395,57 +16399,48 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128203231</v>
+        <v>128203240</v>
       </c>
       <c r="B143" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>736270</v>
+        <v>736238</v>
       </c>
       <c r="R143" t="n">
-        <v>6411530</v>
+        <v>6411496</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16475,6 +16470,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -8264,57 +8264,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203209</v>
+        <v>128203239</v>
       </c>
       <c r="B68" t="n">
-        <v>98573</v>
+        <v>109398</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R68" t="n">
-        <v>6411567</v>
+        <v>6411500</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8346,6 +8337,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8357,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8375,48 +8371,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203239</v>
+        <v>128203209</v>
       </c>
       <c r="B69" t="n">
-        <v>109398</v>
+        <v>98573</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R69" t="n">
-        <v>6411500</v>
+        <v>6411567</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8448,11 +8453,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8696,35 +8696,44 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128203181</v>
+        <v>128203182</v>
       </c>
       <c r="B72" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8771,7 +8780,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8803,48 +8812,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128203166</v>
+        <v>128203187</v>
       </c>
       <c r="B73" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736275</v>
+        <v>736331</v>
       </c>
       <c r="R73" t="n">
-        <v>6411455</v>
+        <v>6411530</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8905,44 +8923,35 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203182</v>
+        <v>128203181</v>
       </c>
       <c r="B74" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8989,7 +8998,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Stig över våtmark; avsnitslat.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9021,57 +9030,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128203187</v>
+        <v>128203166</v>
       </c>
       <c r="B75" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736331</v>
+        <v>736275</v>
       </c>
       <c r="R75" t="n">
-        <v>6411530</v>
+        <v>6411455</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203114</v>
+        <v>128203023</v>
       </c>
       <c r="B76" t="n">
-        <v>98577</v>
+        <v>57682</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,31 +9143,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>742</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9176,13 +9176,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736184</v>
+        <v>736365</v>
       </c>
       <c r="R76" t="n">
-        <v>6411805</v>
+        <v>6411573</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9214,11 +9214,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9230,7 +9225,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9248,32 +9243,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203199</v>
+        <v>128203185</v>
       </c>
       <c r="B77" t="n">
-        <v>98556</v>
+        <v>109398</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9283,13 +9278,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736314</v>
+        <v>736331</v>
       </c>
       <c r="R77" t="n">
-        <v>6411572</v>
+        <v>6411530</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9323,7 +9318,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9337,7 +9332,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9355,42 +9350,42 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203086</v>
+        <v>128203099</v>
       </c>
       <c r="B78" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9399,10 +9394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736450</v>
+        <v>736361</v>
       </c>
       <c r="R78" t="n">
-        <v>6411486</v>
+        <v>6411697</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9466,37 +9461,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203221</v>
+        <v>128203114</v>
       </c>
       <c r="B79" t="n">
-        <v>98573</v>
+        <v>98577</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219811</v>
+        <v>742</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9510,10 +9505,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736272</v>
+        <v>736184</v>
       </c>
       <c r="R79" t="n">
-        <v>6411546</v>
+        <v>6411805</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9548,6 +9543,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9577,32 +9577,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203189</v>
+        <v>128203199</v>
       </c>
       <c r="B80" t="n">
-        <v>109398</v>
+        <v>98556</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9612,13 +9612,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736335</v>
+        <v>736314</v>
       </c>
       <c r="R80" t="n">
-        <v>6411533</v>
+        <v>6411572</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9650,6 +9650,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9661,7 +9666,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9679,48 +9684,57 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203185</v>
+        <v>128203086</v>
       </c>
       <c r="B81" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736331</v>
+        <v>736450</v>
       </c>
       <c r="R81" t="n">
-        <v>6411530</v>
+        <v>6411486</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9750,11 +9764,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9786,42 +9795,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203099</v>
+        <v>128203221</v>
       </c>
       <c r="B82" t="n">
-        <v>109398</v>
+        <v>98573</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9830,13 +9839,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736361</v>
+        <v>736272</v>
       </c>
       <c r="R82" t="n">
-        <v>6411697</v>
+        <v>6411546</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9879,7 +9888,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,10 +9906,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203023</v>
+        <v>128203189</v>
       </c>
       <c r="B83" t="n">
-        <v>57682</v>
+        <v>109398</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9908,46 +9917,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736365</v>
+        <v>736335</v>
       </c>
       <c r="R83" t="n">
-        <v>6411573</v>
+        <v>6411533</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10008,10 +10008,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203249</v>
+        <v>128203111</v>
       </c>
       <c r="B84" t="n">
-        <v>98549</v>
+        <v>98502</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10019,26 +10019,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>219794</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736192</v>
+        <v>736184</v>
       </c>
       <c r="R84" t="n">
-        <v>6411467</v>
+        <v>6411805</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10090,6 +10090,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10101,7 +10106,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10119,7 +10124,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203162</v>
+        <v>128203249</v>
       </c>
       <c r="B85" t="n">
         <v>98549</v>
@@ -10149,7 +10154,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10163,13 +10168,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736250</v>
+        <v>736192</v>
       </c>
       <c r="R85" t="n">
-        <v>6411464</v>
+        <v>6411467</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10230,37 +10235,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203111</v>
+        <v>128203132</v>
       </c>
       <c r="B86" t="n">
-        <v>98502</v>
+        <v>107456</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219794</v>
+        <v>220079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10274,13 +10279,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736184</v>
+        <v>736242</v>
       </c>
       <c r="R86" t="n">
-        <v>6411805</v>
+        <v>6411713</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10312,11 +10317,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10346,37 +10346,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203132</v>
+        <v>128203162</v>
       </c>
       <c r="B87" t="n">
-        <v>107456</v>
+        <v>98549</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736242</v>
+        <v>736250</v>
       </c>
       <c r="R87" t="n">
-        <v>6411713</v>
+        <v>6411464</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10684,54 +10684,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203165</v>
+        <v>128203180</v>
       </c>
       <c r="B90" t="n">
-        <v>98549</v>
+        <v>105507</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736260</v>
+        <v>736300</v>
       </c>
       <c r="R90" t="n">
-        <v>6411450</v>
+        <v>6411481</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10766,6 +10757,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -10777,7 +10773,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,57 +10791,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203081</v>
+        <v>128203211</v>
       </c>
       <c r="B91" t="n">
-        <v>98549</v>
+        <v>99246</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736347</v>
+        <v>736301</v>
       </c>
       <c r="R91" t="n">
-        <v>6411466</v>
+        <v>6411564</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10888,7 +10875,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,10 +10893,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203225</v>
+        <v>128203156</v>
       </c>
       <c r="B92" t="n">
-        <v>98573</v>
+        <v>98489</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10917,26 +10904,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10950,13 +10937,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736263</v>
+        <v>736221</v>
       </c>
       <c r="R92" t="n">
-        <v>6411533</v>
+        <v>6411593</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10999,7 +10986,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11017,10 +11004,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203197</v>
+        <v>128203165</v>
       </c>
       <c r="B93" t="n">
-        <v>98573</v>
+        <v>98549</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11028,37 +11015,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736314</v>
+        <v>736260</v>
       </c>
       <c r="R93" t="n">
-        <v>6411572</v>
+        <v>6411450</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11090,11 +11086,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -11106,7 +11097,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11124,10 +11115,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203156</v>
+        <v>128203081</v>
       </c>
       <c r="B94" t="n">
-        <v>98489</v>
+        <v>98549</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11135,26 +11126,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11168,10 +11159,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736221</v>
+        <v>736347</v>
       </c>
       <c r="R94" t="n">
-        <v>6411593</v>
+        <v>6411466</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11217,7 +11208,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11235,48 +11226,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203211</v>
+        <v>128203225</v>
       </c>
       <c r="B95" t="n">
-        <v>99246</v>
+        <v>98573</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736301</v>
+        <v>736263</v>
       </c>
       <c r="R95" t="n">
-        <v>6411564</v>
+        <v>6411533</v>
       </c>
       <c r="S95" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11337,32 +11337,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203180</v>
+        <v>128203197</v>
       </c>
       <c r="B96" t="n">
-        <v>105507</v>
+        <v>98573</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11372,13 +11372,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736300</v>
+        <v>736314</v>
       </c>
       <c r="R96" t="n">
-        <v>6411481</v>
+        <v>6411572</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11973,54 +11973,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203154</v>
+        <v>128203129</v>
       </c>
       <c r="B102" t="n">
-        <v>98479</v>
+        <v>105507</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R102" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12066,7 +12057,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12084,10 +12075,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203126</v>
+        <v>128203154</v>
       </c>
       <c r="B103" t="n">
-        <v>98573</v>
+        <v>98479</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12095,26 +12086,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219811</v>
+        <v>219788</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12128,13 +12119,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R103" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12177,7 +12168,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12195,35 +12186,44 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203129</v>
+        <v>128203126</v>
       </c>
       <c r="B104" t="n">
-        <v>105507</v>
+        <v>98573</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12506,57 +12506,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203207</v>
+        <v>128203107</v>
       </c>
       <c r="B107" t="n">
-        <v>98573</v>
+        <v>105507</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736300</v>
+        <v>736305</v>
       </c>
       <c r="R107" t="n">
-        <v>6411576</v>
+        <v>6411739</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12588,6 +12579,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12599,7 +12595,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12617,10 +12613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203177</v>
+        <v>128203207</v>
       </c>
       <c r="B108" t="n">
-        <v>98556</v>
+        <v>98573</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12628,24 +12624,33 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12655,10 +12660,10 @@
         <v>736300</v>
       </c>
       <c r="R108" t="n">
-        <v>6411481</v>
+        <v>6411576</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12690,11 +12695,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203234</v>
+        <v>128203177</v>
       </c>
       <c r="B109" t="n">
-        <v>98549</v>
+        <v>98556</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12735,16 +12735,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12752,29 +12752,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736279</v>
+        <v>736300</v>
       </c>
       <c r="R109" t="n">
-        <v>6411517</v>
+        <v>6411481</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12806,6 +12797,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12817,7 +12813,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12835,48 +12831,57 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203107</v>
+        <v>128203234</v>
       </c>
       <c r="B110" t="n">
-        <v>105507</v>
+        <v>98549</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736305</v>
+        <v>736279</v>
       </c>
       <c r="R110" t="n">
-        <v>6411739</v>
+        <v>6411517</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12908,11 +12913,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12942,57 +12942,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128203160</v>
+        <v>128203236</v>
       </c>
       <c r="B111" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>736240</v>
+        <v>736279</v>
       </c>
       <c r="R111" t="n">
-        <v>6411466</v>
+        <v>6411517</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13022,6 +13013,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13053,10 +13049,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128203138</v>
+        <v>128203160</v>
       </c>
       <c r="B112" t="n">
-        <v>98556</v>
+        <v>98549</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13064,16 +13060,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -13083,7 +13079,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13097,13 +13093,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>736231</v>
+        <v>736240</v>
       </c>
       <c r="R112" t="n">
-        <v>6411673</v>
+        <v>6411466</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13146,7 +13142,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13164,10 +13160,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128203094</v>
+        <v>128203138</v>
       </c>
       <c r="B113" t="n">
-        <v>98549</v>
+        <v>98556</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13175,16 +13171,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -13194,7 +13190,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13208,13 +13204,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>736498</v>
+        <v>736231</v>
       </c>
       <c r="R113" t="n">
-        <v>6411566</v>
+        <v>6411673</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13257,7 +13253,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13275,45 +13271,54 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128203161</v>
+        <v>128203094</v>
       </c>
       <c r="B114" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>736250</v>
+        <v>736498</v>
       </c>
       <c r="R114" t="n">
-        <v>6411464</v>
+        <v>6411566</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13377,7 +13382,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128203236</v>
+        <v>128203161</v>
       </c>
       <c r="B115" t="n">
         <v>109398</v>
@@ -13412,13 +13417,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>736279</v>
+        <v>736250</v>
       </c>
       <c r="R115" t="n">
-        <v>6411517</v>
+        <v>6411464</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13448,11 +13453,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13808,57 +13808,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128203101</v>
+        <v>128203159</v>
       </c>
       <c r="B119" t="n">
-        <v>98479</v>
+        <v>109398</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>736358</v>
+        <v>736240</v>
       </c>
       <c r="R119" t="n">
-        <v>6411725</v>
+        <v>6411466</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13890,6 +13881,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13901,7 +13897,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13919,48 +13915,57 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128203159</v>
+        <v>128203101</v>
       </c>
       <c r="B120" t="n">
-        <v>109398</v>
+        <v>98479</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>736240</v>
+        <v>736358</v>
       </c>
       <c r="R120" t="n">
-        <v>6411466</v>
+        <v>6411725</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13992,11 +13997,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14026,57 +14026,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128203213</v>
+        <v>128203230</v>
       </c>
       <c r="B121" t="n">
-        <v>98573</v>
+        <v>109398</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>736301</v>
+        <v>736270</v>
       </c>
       <c r="R121" t="n">
-        <v>6411564</v>
+        <v>6411530</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14108,6 +14099,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14119,7 +14115,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14137,48 +14133,57 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128203230</v>
+        <v>128203213</v>
       </c>
       <c r="B122" t="n">
-        <v>109398</v>
+        <v>98573</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>736270</v>
+        <v>736301</v>
       </c>
       <c r="R122" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14210,11 +14215,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128203190</v>
+        <v>128203092</v>
       </c>
       <c r="B123" t="n">
         <v>98549</v>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>736335</v>
+        <v>736520</v>
       </c>
       <c r="R123" t="n">
-        <v>6411533</v>
+        <v>6411544</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203216</v>
+        <v>128203190</v>
       </c>
       <c r="B124" t="n">
         <v>98549</v>
@@ -14399,10 +14399,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736297</v>
+        <v>736335</v>
       </c>
       <c r="R124" t="n">
-        <v>6411559</v>
+        <v>6411533</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14435,11 +14435,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14471,7 +14466,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203092</v>
+        <v>128203216</v>
       </c>
       <c r="B125" t="n">
         <v>98549</v>
@@ -14501,7 +14496,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14515,13 +14510,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736520</v>
+        <v>736297</v>
       </c>
       <c r="R125" t="n">
-        <v>6411544</v>
+        <v>6411559</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14551,6 +14546,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14893,10 +14893,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203112</v>
+        <v>128203178</v>
       </c>
       <c r="B129" t="n">
-        <v>98556</v>
+        <v>98098</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14904,21 +14904,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219799</v>
+        <v>221930</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736184</v>
+        <v>736300</v>
       </c>
       <c r="R129" t="n">
-        <v>6411805</v>
+        <v>6411481</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15000,10 +15000,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203113</v>
+        <v>128203112</v>
       </c>
       <c r="B130" t="n">
-        <v>98573</v>
+        <v>98556</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15011,21 +15011,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15107,10 +15107,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203252</v>
+        <v>128203113</v>
       </c>
       <c r="B131" t="n">
-        <v>98593</v>
+        <v>98573</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15118,46 +15118,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219862</v>
+        <v>219811</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>736193</v>
+        <v>736184</v>
       </c>
       <c r="R131" t="n">
-        <v>6411456</v>
+        <v>6411805</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15189,6 +15180,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15200,7 +15196,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15218,48 +15214,57 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203093</v>
+        <v>128203252</v>
       </c>
       <c r="B132" t="n">
-        <v>109398</v>
+        <v>98593</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736498</v>
+        <v>736193</v>
       </c>
       <c r="R132" t="n">
-        <v>6411566</v>
+        <v>6411456</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15320,32 +15325,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203178</v>
+        <v>128203093</v>
       </c>
       <c r="B133" t="n">
-        <v>98098</v>
+        <v>109398</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221930</v>
+        <v>220299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15355,10 +15360,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736300</v>
+        <v>736498</v>
       </c>
       <c r="R133" t="n">
-        <v>6411481</v>
+        <v>6411566</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15393,11 +15398,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203139</v>
+        <v>128203127</v>
       </c>
       <c r="B134" t="n">
-        <v>98575</v>
+        <v>98556</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15438,26 +15438,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736244</v>
+        <v>736239</v>
       </c>
       <c r="R134" t="n">
-        <v>6411666</v>
+        <v>6411738</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,57 +15538,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203228</v>
+        <v>128203083</v>
       </c>
       <c r="B135" t="n">
-        <v>98556</v>
+        <v>109398</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736263</v>
+        <v>736442</v>
       </c>
       <c r="R135" t="n">
-        <v>6411533</v>
+        <v>6411479</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15631,7 +15622,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15649,57 +15640,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203127</v>
+        <v>128203164</v>
       </c>
       <c r="B136" t="n">
-        <v>98556</v>
+        <v>109398</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736239</v>
+        <v>736260</v>
       </c>
       <c r="R136" t="n">
-        <v>6411738</v>
+        <v>6411450</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15742,7 +15724,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15760,48 +15742,57 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203083</v>
+        <v>128203139</v>
       </c>
       <c r="B137" t="n">
-        <v>109398</v>
+        <v>98575</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220299</v>
+        <v>741</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Wahlenb.) K. Richt.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736442</v>
+        <v>736244</v>
       </c>
       <c r="R137" t="n">
-        <v>6411479</v>
+        <v>6411666</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15844,7 +15835,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15862,48 +15853,57 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203164</v>
+        <v>128203228</v>
       </c>
       <c r="B138" t="n">
-        <v>109398</v>
+        <v>98556</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736260</v>
+        <v>736263</v>
       </c>
       <c r="R138" t="n">
-        <v>6411450</v>
+        <v>6411533</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6729,57 +6729,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203195</v>
+        <v>128203256</v>
       </c>
       <c r="B54" t="n">
-        <v>98479</v>
+        <v>109398</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736314</v>
+        <v>736176</v>
       </c>
       <c r="R54" t="n">
-        <v>6411572</v>
+        <v>6411455</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6811,11 +6802,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6827,7 +6813,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6845,54 +6831,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203096</v>
+        <v>128203241</v>
       </c>
       <c r="B55" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736474</v>
+        <v>736223</v>
       </c>
       <c r="R55" t="n">
-        <v>6411596</v>
+        <v>6411512</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6929,7 +6906,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6961,10 +6938,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203100</v>
+        <v>128203195</v>
       </c>
       <c r="B56" t="n">
-        <v>98549</v>
+        <v>98479</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6972,26 +6949,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7005,13 +6982,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736361</v>
+        <v>736314</v>
       </c>
       <c r="R56" t="n">
-        <v>6411697</v>
+        <v>6411572</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7043,6 +7020,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7054,7 +7036,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7072,45 +7054,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203256</v>
+        <v>128203096</v>
       </c>
       <c r="B57" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R57" t="n">
-        <v>6411455</v>
+        <v>6411596</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7143,6 +7134,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7174,45 +7170,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203241</v>
+        <v>128203100</v>
       </c>
       <c r="B58" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736223</v>
+        <v>736361</v>
       </c>
       <c r="R58" t="n">
-        <v>6411512</v>
+        <v>6411697</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7245,11 +7250,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8371,57 +8371,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203209</v>
+        <v>128203095</v>
       </c>
       <c r="B69" t="n">
-        <v>98573</v>
+        <v>109398</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736295</v>
+        <v>736474</v>
       </c>
       <c r="R69" t="n">
-        <v>6411567</v>
+        <v>6411596</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8453,6 +8444,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8464,7 +8460,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8482,10 +8478,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203095</v>
+        <v>128203104</v>
       </c>
       <c r="B70" t="n">
-        <v>109398</v>
+        <v>105507</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8493,16 +8489,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8517,13 +8513,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736474</v>
+        <v>736325</v>
       </c>
       <c r="R70" t="n">
-        <v>6411596</v>
+        <v>6411730</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8557,7 +8553,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8571,7 +8567,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8589,48 +8585,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203104</v>
+        <v>128203209</v>
       </c>
       <c r="B71" t="n">
-        <v>105507</v>
+        <v>98573</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736325</v>
+        <v>736295</v>
       </c>
       <c r="R71" t="n">
-        <v>6411730</v>
+        <v>6411567</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8662,11 +8667,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Spridd. Flera i blom.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203023</v>
+        <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>57682</v>
+        <v>98577</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,31 +9143,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>742</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9176,13 +9176,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736365</v>
+        <v>736184</v>
       </c>
       <c r="R76" t="n">
-        <v>6411573</v>
+        <v>6411805</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9214,6 +9214,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9225,7 +9230,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9243,10 +9248,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203185</v>
+        <v>128203023</v>
       </c>
       <c r="B77" t="n">
-        <v>109398</v>
+        <v>57682</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9254,37 +9259,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736331</v>
+        <v>736365</v>
       </c>
       <c r="R77" t="n">
-        <v>6411530</v>
+        <v>6411573</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9314,11 +9328,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9350,57 +9359,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203099</v>
+        <v>128203199</v>
       </c>
       <c r="B78" t="n">
-        <v>109398</v>
+        <v>98556</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736361</v>
+        <v>736314</v>
       </c>
       <c r="R78" t="n">
-        <v>6411697</v>
+        <v>6411572</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9432,6 +9432,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9443,7 +9448,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9461,37 +9466,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203114</v>
+        <v>128203086</v>
       </c>
       <c r="B79" t="n">
-        <v>98577</v>
+        <v>98549</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>742</v>
+        <v>219798</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9505,13 +9510,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736184</v>
+        <v>736450</v>
       </c>
       <c r="R79" t="n">
-        <v>6411805</v>
+        <v>6411486</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9543,11 +9548,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203199</v>
+        <v>128203221</v>
       </c>
       <c r="B80" t="n">
-        <v>98556</v>
+        <v>98573</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9588,37 +9588,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736314</v>
+        <v>736272</v>
       </c>
       <c r="R80" t="n">
-        <v>6411572</v>
+        <v>6411546</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9650,11 +9659,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9666,7 +9670,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9684,57 +9688,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203086</v>
+        <v>128203189</v>
       </c>
       <c r="B81" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736450</v>
+        <v>736335</v>
       </c>
       <c r="R81" t="n">
-        <v>6411486</v>
+        <v>6411533</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9795,54 +9790,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203221</v>
+        <v>128203185</v>
       </c>
       <c r="B82" t="n">
-        <v>98573</v>
+        <v>109398</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736272</v>
+        <v>736331</v>
       </c>
       <c r="R82" t="n">
-        <v>6411546</v>
+        <v>6411530</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9877,6 +9863,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9888,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9906,7 +9897,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203189</v>
+        <v>128203099</v>
       </c>
       <c r="B83" t="n">
         <v>109398</v>
@@ -9934,20 +9925,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736335</v>
+        <v>736361</v>
       </c>
       <c r="R83" t="n">
-        <v>6411533</v>
+        <v>6411697</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10008,10 +10008,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203111</v>
+        <v>128203162</v>
       </c>
       <c r="B84" t="n">
-        <v>98502</v>
+        <v>98549</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10019,26 +10019,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219794</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736184</v>
+        <v>736250</v>
       </c>
       <c r="R84" t="n">
-        <v>6411805</v>
+        <v>6411464</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10090,11 +10090,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10106,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10124,10 +10119,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203249</v>
+        <v>128203111</v>
       </c>
       <c r="B85" t="n">
-        <v>98549</v>
+        <v>98502</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10135,26 +10130,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219798</v>
+        <v>219794</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10168,13 +10163,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736192</v>
+        <v>736184</v>
       </c>
       <c r="R85" t="n">
-        <v>6411467</v>
+        <v>6411805</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10206,6 +10201,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10235,10 +10235,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203132</v>
+        <v>128203192</v>
       </c>
       <c r="B86" t="n">
-        <v>107456</v>
+        <v>105507</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,26 +10246,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220079</v>
+        <v>221137</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10279,13 +10279,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736242</v>
+        <v>736339</v>
       </c>
       <c r="R86" t="n">
-        <v>6411713</v>
+        <v>6411571</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10317,6 +10317,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10328,7 +10333,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10346,7 +10351,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203162</v>
+        <v>128203249</v>
       </c>
       <c r="B87" t="n">
         <v>98549</v>
@@ -10376,7 +10381,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10390,13 +10395,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736250</v>
+        <v>736192</v>
       </c>
       <c r="R87" t="n">
-        <v>6411464</v>
+        <v>6411467</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10457,10 +10462,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128203192</v>
+        <v>128203132</v>
       </c>
       <c r="B88" t="n">
-        <v>105507</v>
+        <v>107456</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10468,26 +10473,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221137</v>
+        <v>220079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10501,13 +10506,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>736339</v>
+        <v>736242</v>
       </c>
       <c r="R88" t="n">
-        <v>6411571</v>
+        <v>6411713</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10539,11 +10544,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12506,48 +12506,57 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203107</v>
+        <v>128203207</v>
       </c>
       <c r="B107" t="n">
-        <v>105507</v>
+        <v>98573</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736305</v>
+        <v>736300</v>
       </c>
       <c r="R107" t="n">
-        <v>6411739</v>
+        <v>6411576</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12579,11 +12588,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12595,7 +12599,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12613,10 +12617,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203207</v>
+        <v>128203177</v>
       </c>
       <c r="B108" t="n">
-        <v>98573</v>
+        <v>98556</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12624,33 +12628,24 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12660,10 +12655,10 @@
         <v>736300</v>
       </c>
       <c r="R108" t="n">
-        <v>6411576</v>
+        <v>6411481</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12695,6 +12690,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203177</v>
+        <v>128203234</v>
       </c>
       <c r="B109" t="n">
-        <v>98556</v>
+        <v>98549</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12735,16 +12735,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12752,20 +12752,29 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736300</v>
+        <v>736279</v>
       </c>
       <c r="R109" t="n">
-        <v>6411481</v>
+        <v>6411517</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12797,11 +12806,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12813,7 +12817,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12831,57 +12835,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203234</v>
+        <v>128203107</v>
       </c>
       <c r="B110" t="n">
-        <v>98549</v>
+        <v>105507</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736279</v>
+        <v>736305</v>
       </c>
       <c r="R110" t="n">
-        <v>6411517</v>
+        <v>6411739</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12913,6 +12908,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12942,48 +12942,57 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128203236</v>
+        <v>128203160</v>
       </c>
       <c r="B111" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>736279</v>
+        <v>736240</v>
       </c>
       <c r="R111" t="n">
-        <v>6411517</v>
+        <v>6411466</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13013,11 +13022,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13049,10 +13053,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128203160</v>
+        <v>128203138</v>
       </c>
       <c r="B112" t="n">
-        <v>98549</v>
+        <v>98556</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13060,16 +13064,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -13079,7 +13083,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13093,13 +13097,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>736240</v>
+        <v>736231</v>
       </c>
       <c r="R112" t="n">
-        <v>6411466</v>
+        <v>6411673</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13142,7 +13146,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13160,10 +13164,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128203138</v>
+        <v>128203094</v>
       </c>
       <c r="B113" t="n">
-        <v>98556</v>
+        <v>98549</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13171,16 +13175,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -13190,7 +13194,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13204,13 +13208,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>736231</v>
+        <v>736498</v>
       </c>
       <c r="R113" t="n">
-        <v>6411673</v>
+        <v>6411566</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13253,7 +13257,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13271,54 +13275,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128203094</v>
+        <v>128203161</v>
       </c>
       <c r="B114" t="n">
-        <v>98549</v>
+        <v>109398</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>736498</v>
+        <v>736250</v>
       </c>
       <c r="R114" t="n">
-        <v>6411566</v>
+        <v>6411464</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13382,7 +13377,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128203161</v>
+        <v>128203236</v>
       </c>
       <c r="B115" t="n">
         <v>109398</v>
@@ -13417,13 +13412,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>736250</v>
+        <v>736279</v>
       </c>
       <c r="R115" t="n">
-        <v>6411464</v>
+        <v>6411517</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13453,6 +13448,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14026,48 +14026,57 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128203230</v>
+        <v>128203213</v>
       </c>
       <c r="B121" t="n">
-        <v>109398</v>
+        <v>98573</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>736270</v>
+        <v>736301</v>
       </c>
       <c r="R121" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14099,11 +14108,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14115,7 +14119,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14133,57 +14137,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128203213</v>
+        <v>128203230</v>
       </c>
       <c r="B122" t="n">
-        <v>98573</v>
+        <v>109398</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>736301</v>
+        <v>736270</v>
       </c>
       <c r="R122" t="n">
-        <v>6411564</v>
+        <v>6411530</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14215,6 +14210,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14244,7 +14244,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128203092</v>
+        <v>128203190</v>
       </c>
       <c r="B123" t="n">
         <v>98549</v>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R123" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203190</v>
+        <v>128203216</v>
       </c>
       <c r="B124" t="n">
         <v>98549</v>
@@ -14399,10 +14399,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736335</v>
+        <v>736297</v>
       </c>
       <c r="R124" t="n">
-        <v>6411533</v>
+        <v>6411559</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14435,6 +14435,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14466,10 +14471,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203216</v>
+        <v>128203235</v>
       </c>
       <c r="B125" t="n">
-        <v>98549</v>
+        <v>110455</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14477,43 +14482,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736297</v>
+        <v>736279</v>
       </c>
       <c r="R125" t="n">
-        <v>6411559</v>
+        <v>6411517</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14546,11 +14542,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14582,27 +14573,27 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203235</v>
+        <v>128203151</v>
       </c>
       <c r="B126" t="n">
-        <v>110455</v>
+        <v>109398</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -14617,13 +14608,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736279</v>
+        <v>736248</v>
       </c>
       <c r="R126" t="n">
-        <v>6411517</v>
+        <v>6411616</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14653,6 +14644,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14684,7 +14680,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203151</v>
+        <v>128203091</v>
       </c>
       <c r="B127" t="n">
         <v>109398</v>
@@ -14719,10 +14715,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736248</v>
+        <v>736520</v>
       </c>
       <c r="R127" t="n">
-        <v>6411616</v>
+        <v>6411544</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14755,11 +14751,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14791,35 +14782,44 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203091</v>
+        <v>128203092</v>
       </c>
       <c r="B128" t="n">
-        <v>109398</v>
+        <v>98549</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203178</v>
+        <v>128203093</v>
       </c>
       <c r="B129" t="n">
-        <v>98098</v>
+        <v>109398</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221930</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736300</v>
+        <v>736498</v>
       </c>
       <c r="R129" t="n">
-        <v>6411481</v>
+        <v>6411566</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,11 +14966,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14982,7 +14977,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15000,10 +14995,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203112</v>
+        <v>128203178</v>
       </c>
       <c r="B130" t="n">
-        <v>98556</v>
+        <v>98098</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15011,21 +15006,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219799</v>
+        <v>221930</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15035,10 +15030,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>736184</v>
+        <v>736300</v>
       </c>
       <c r="R130" t="n">
-        <v>6411805</v>
+        <v>6411481</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15075,7 +15070,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15089,7 +15084,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15107,10 +15102,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203113</v>
+        <v>128203112</v>
       </c>
       <c r="B131" t="n">
-        <v>98573</v>
+        <v>98556</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15118,21 +15113,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15214,10 +15209,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203252</v>
+        <v>128203113</v>
       </c>
       <c r="B132" t="n">
-        <v>98593</v>
+        <v>98573</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15225,46 +15220,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219862</v>
+        <v>219811</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736193</v>
+        <v>736184</v>
       </c>
       <c r="R132" t="n">
-        <v>6411456</v>
+        <v>6411805</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15296,6 +15282,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15307,7 +15298,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15325,48 +15316,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203093</v>
+        <v>128203252</v>
       </c>
       <c r="B133" t="n">
-        <v>109398</v>
+        <v>98593</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736498</v>
+        <v>736193</v>
       </c>
       <c r="R133" t="n">
-        <v>6411566</v>
+        <v>6411456</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,37 +6400,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203088</v>
+        <v>128203131</v>
       </c>
       <c r="B51" t="n">
-        <v>98549</v>
+        <v>105528</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6444,13 +6444,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736474</v>
+        <v>736256</v>
       </c>
       <c r="R51" t="n">
-        <v>6411506</v>
+        <v>6411743</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Våtmark mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203259</v>
+        <v>128203088</v>
       </c>
       <c r="B52" t="n">
-        <v>110455</v>
+        <v>98563</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6522,34 +6522,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R52" t="n">
-        <v>6411455</v>
+        <v>6411506</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6582,11 +6591,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6618,27 +6622,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128203131</v>
+        <v>128203259</v>
       </c>
       <c r="B53" t="n">
-        <v>105507</v>
+        <v>110480</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221137</v>
+        <v>219677</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6646,29 +6650,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736256</v>
+        <v>736176</v>
       </c>
       <c r="R53" t="n">
-        <v>6411743</v>
+        <v>6411455</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6700,6 +6695,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Våtmark mellan strandvallar.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
         <v>128203256</v>
       </c>
       <c r="B54" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>128203241</v>
       </c>
       <c r="B55" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6938,10 +6938,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203195</v>
+        <v>128203179</v>
       </c>
       <c r="B56" t="n">
-        <v>98479</v>
+        <v>99626</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6949,46 +6949,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736314</v>
+        <v>736300</v>
       </c>
       <c r="R56" t="n">
-        <v>6411572</v>
+        <v>6411481</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7020,11 +7011,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7036,7 +7022,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7054,10 +7040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203096</v>
+        <v>128203195</v>
       </c>
       <c r="B57" t="n">
-        <v>98549</v>
+        <v>98493</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7065,26 +7051,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7098,13 +7084,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736474</v>
+        <v>736314</v>
       </c>
       <c r="R57" t="n">
-        <v>6411596</v>
+        <v>6411572</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7138,7 +7124,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7152,7 +7138,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7170,10 +7156,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203100</v>
+        <v>128203096</v>
       </c>
       <c r="B58" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7200,7 +7186,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7214,10 +7200,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736361</v>
+        <v>736474</v>
       </c>
       <c r="R58" t="n">
-        <v>6411697</v>
+        <v>6411596</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7250,6 +7236,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7281,10 +7272,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203179</v>
+        <v>128203100</v>
       </c>
       <c r="B59" t="n">
-        <v>99612</v>
+        <v>98563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7292,34 +7283,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222662</v>
+        <v>219798</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736300</v>
+        <v>736361</v>
       </c>
       <c r="R59" t="n">
-        <v>6411481</v>
+        <v>6411697</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7386,7 +7386,7 @@
         <v>128203021</v>
       </c>
       <c r="B60" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>128203237</v>
       </c>
       <c r="B61" t="n">
-        <v>110455</v>
+        <v>110480</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>128203233</v>
       </c>
       <c r="B62" t="n">
-        <v>98556</v>
+        <v>98570</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>128203186</v>
       </c>
       <c r="B63" t="n">
-        <v>98593</v>
+        <v>98607</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>128203220</v>
       </c>
       <c r="B64" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>128203144</v>
       </c>
       <c r="B65" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>128203089</v>
       </c>
       <c r="B66" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>128203243</v>
       </c>
       <c r="B67" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>128203239</v>
       </c>
       <c r="B68" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8371,10 +8371,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203095</v>
+        <v>128203104</v>
       </c>
       <c r="B69" t="n">
-        <v>109398</v>
+        <v>105528</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,16 +8382,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8406,13 +8406,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736474</v>
+        <v>736325</v>
       </c>
       <c r="R69" t="n">
-        <v>6411596</v>
+        <v>6411730</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8478,48 +8478,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203104</v>
+        <v>128203209</v>
       </c>
       <c r="B70" t="n">
-        <v>105507</v>
+        <v>98587</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736325</v>
+        <v>736295</v>
       </c>
       <c r="R70" t="n">
-        <v>6411730</v>
+        <v>6411567</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8551,11 +8560,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Spridd. Flera i blom.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8567,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8585,57 +8589,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203209</v>
+        <v>128203095</v>
       </c>
       <c r="B71" t="n">
-        <v>98573</v>
+        <v>109422</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736295</v>
+        <v>736474</v>
       </c>
       <c r="R71" t="n">
-        <v>6411567</v>
+        <v>6411596</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8667,6 +8662,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8699,7 +8699,7 @@
         <v>128203182</v>
       </c>
       <c r="B72" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>128203187</v>
       </c>
       <c r="B73" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>128203181</v>
       </c>
       <c r="B74" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>128203166</v>
       </c>
       <c r="B75" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9132,57 +9132,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203114</v>
+        <v>128203199</v>
       </c>
       <c r="B76" t="n">
-        <v>98577</v>
+        <v>98570</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>742</v>
+        <v>219799</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736184</v>
+        <v>736314</v>
       </c>
       <c r="R76" t="n">
-        <v>6411805</v>
+        <v>6411572</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9216,7 +9207,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9230,7 +9221,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9248,42 +9239,42 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203023</v>
+        <v>128203086</v>
       </c>
       <c r="B77" t="n">
-        <v>57682</v>
+        <v>98563</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9292,13 +9283,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736365</v>
+        <v>736450</v>
       </c>
       <c r="R77" t="n">
-        <v>6411573</v>
+        <v>6411486</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9359,10 +9350,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203199</v>
+        <v>128203221</v>
       </c>
       <c r="B78" t="n">
-        <v>98556</v>
+        <v>98587</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9370,37 +9361,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736314</v>
+        <v>736272</v>
       </c>
       <c r="R78" t="n">
-        <v>6411572</v>
+        <v>6411546</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9432,11 +9432,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9448,7 +9443,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9466,57 +9461,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203086</v>
+        <v>128203189</v>
       </c>
       <c r="B79" t="n">
-        <v>98549</v>
+        <v>109422</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736450</v>
+        <v>736335</v>
       </c>
       <c r="R79" t="n">
-        <v>6411486</v>
+        <v>6411533</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9577,54 +9563,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203221</v>
+        <v>128203185</v>
       </c>
       <c r="B80" t="n">
-        <v>98573</v>
+        <v>109422</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736272</v>
+        <v>736331</v>
       </c>
       <c r="R80" t="n">
-        <v>6411546</v>
+        <v>6411530</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9659,6 +9636,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9670,7 +9652,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9688,10 +9670,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203189</v>
+        <v>128203099</v>
       </c>
       <c r="B81" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9716,20 +9698,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736335</v>
+        <v>736361</v>
       </c>
       <c r="R81" t="n">
-        <v>6411533</v>
+        <v>6411697</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9790,10 +9781,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203185</v>
+        <v>128203114</v>
       </c>
       <c r="B82" t="n">
-        <v>109398</v>
+        <v>98591</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9801,34 +9792,43 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>742</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736331</v>
+        <v>736184</v>
       </c>
       <c r="R82" t="n">
-        <v>6411530</v>
+        <v>6411805</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,10 +9897,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203099</v>
+        <v>128203023</v>
       </c>
       <c r="B83" t="n">
-        <v>109398</v>
+        <v>57686</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9908,31 +9908,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736361</v>
+        <v>736365</v>
       </c>
       <c r="R83" t="n">
-        <v>6411697</v>
+        <v>6411573</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10008,37 +10008,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203162</v>
+        <v>128203192</v>
       </c>
       <c r="B84" t="n">
-        <v>98549</v>
+        <v>105528</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736250</v>
+        <v>736339</v>
       </c>
       <c r="R84" t="n">
-        <v>6411464</v>
+        <v>6411571</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10090,6 +10090,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10101,7 +10106,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10119,10 +10124,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203111</v>
+        <v>128203249</v>
       </c>
       <c r="B85" t="n">
-        <v>98502</v>
+        <v>98563</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10130,26 +10135,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219794</v>
+        <v>219798</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10163,13 +10168,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736184</v>
+        <v>736192</v>
       </c>
       <c r="R85" t="n">
-        <v>6411805</v>
+        <v>6411467</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10201,11 +10206,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10235,10 +10235,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203192</v>
+        <v>128203132</v>
       </c>
       <c r="B86" t="n">
-        <v>105507</v>
+        <v>107479</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10246,26 +10246,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221137</v>
+        <v>220079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10279,13 +10279,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736339</v>
+        <v>736242</v>
       </c>
       <c r="R86" t="n">
-        <v>6411571</v>
+        <v>6411713</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10317,11 +10317,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10333,7 +10328,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10351,10 +10346,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203249</v>
+        <v>128203162</v>
       </c>
       <c r="B87" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10381,7 +10376,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10395,13 +10390,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736192</v>
+        <v>736250</v>
       </c>
       <c r="R87" t="n">
-        <v>6411467</v>
+        <v>6411464</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10462,37 +10457,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128203132</v>
+        <v>128203111</v>
       </c>
       <c r="B88" t="n">
-        <v>107456</v>
+        <v>98516</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220079</v>
+        <v>219794</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10506,13 +10501,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>736242</v>
+        <v>736184</v>
       </c>
       <c r="R88" t="n">
-        <v>6411713</v>
+        <v>6411805</v>
       </c>
       <c r="S88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10544,6 +10539,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10576,7 +10576,7 @@
         <v>128205915</v>
       </c>
       <c r="B89" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>128203180</v>
       </c>
       <c r="B90" t="n">
-        <v>105507</v>
+        <v>105528</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10791,48 +10791,57 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203211</v>
+        <v>128203156</v>
       </c>
       <c r="B91" t="n">
-        <v>99246</v>
+        <v>98503</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222322</v>
+        <v>223591</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736301</v>
+        <v>736221</v>
       </c>
       <c r="R91" t="n">
-        <v>6411564</v>
+        <v>6411593</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10875,7 +10884,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10893,10 +10902,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203156</v>
+        <v>128203165</v>
       </c>
       <c r="B92" t="n">
-        <v>98489</v>
+        <v>98563</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10904,26 +10913,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10937,10 +10946,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736221</v>
+        <v>736260</v>
       </c>
       <c r="R92" t="n">
-        <v>6411593</v>
+        <v>6411450</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10986,7 +10995,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11004,57 +11013,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203165</v>
+        <v>128203211</v>
       </c>
       <c r="B93" t="n">
-        <v>98549</v>
+        <v>99260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736260</v>
+        <v>736301</v>
       </c>
       <c r="R93" t="n">
-        <v>6411450</v>
+        <v>6411564</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11118,7 +11118,7 @@
         <v>128203081</v>
       </c>
       <c r="B94" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>128203225</v>
       </c>
       <c r="B95" t="n">
-        <v>98573</v>
+        <v>98587</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>128203197</v>
       </c>
       <c r="B96" t="n">
-        <v>98573</v>
+        <v>98587</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>128203087</v>
       </c>
       <c r="B97" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>128203246</v>
       </c>
       <c r="B98" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>128203080</v>
       </c>
       <c r="B99" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>128203106</v>
       </c>
       <c r="B100" t="n">
-        <v>98573</v>
+        <v>98587</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>128203167</v>
       </c>
       <c r="B101" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11973,45 +11973,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203129</v>
+        <v>128203154</v>
       </c>
       <c r="B102" t="n">
-        <v>105507</v>
+        <v>98493</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221137</v>
+        <v>219788</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R102" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12057,7 +12066,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12075,10 +12084,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203154</v>
+        <v>128203126</v>
       </c>
       <c r="B103" t="n">
-        <v>98479</v>
+        <v>98587</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12086,26 +12095,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219788</v>
+        <v>219811</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12119,13 +12128,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R103" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12168,7 +12177,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12186,44 +12195,35 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203126</v>
+        <v>128203129</v>
       </c>
       <c r="B104" t="n">
-        <v>98573</v>
+        <v>105528</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>128203242</v>
       </c>
       <c r="B105" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>128203255</v>
       </c>
       <c r="B106" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12506,57 +12506,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203207</v>
+        <v>128203107</v>
       </c>
       <c r="B107" t="n">
-        <v>98573</v>
+        <v>105528</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736300</v>
+        <v>736305</v>
       </c>
       <c r="R107" t="n">
-        <v>6411576</v>
+        <v>6411739</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12588,6 +12579,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12599,7 +12595,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12617,10 +12613,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203177</v>
+        <v>128203207</v>
       </c>
       <c r="B108" t="n">
-        <v>98556</v>
+        <v>98587</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12628,24 +12624,33 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12655,10 +12660,10 @@
         <v>736300</v>
       </c>
       <c r="R108" t="n">
-        <v>6411481</v>
+        <v>6411576</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12690,11 +12695,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203234</v>
+        <v>128203177</v>
       </c>
       <c r="B109" t="n">
-        <v>98549</v>
+        <v>98570</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12735,16 +12735,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12752,29 +12752,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736279</v>
+        <v>736300</v>
       </c>
       <c r="R109" t="n">
-        <v>6411517</v>
+        <v>6411481</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12806,6 +12797,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12817,7 +12813,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12835,48 +12831,57 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203107</v>
+        <v>128203234</v>
       </c>
       <c r="B110" t="n">
-        <v>105507</v>
+        <v>98563</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736305</v>
+        <v>736279</v>
       </c>
       <c r="R110" t="n">
-        <v>6411739</v>
+        <v>6411517</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12908,11 +12913,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12945,7 +12945,7 @@
         <v>128203160</v>
       </c>
       <c r="B111" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>128203138</v>
       </c>
       <c r="B112" t="n">
-        <v>98556</v>
+        <v>98570</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>128203094</v>
       </c>
       <c r="B113" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>128203161</v>
       </c>
       <c r="B114" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>128203236</v>
       </c>
       <c r="B115" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>128203215</v>
       </c>
       <c r="B116" t="n">
-        <v>98556</v>
+        <v>98570</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>128203134</v>
       </c>
       <c r="B117" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>128203247</v>
       </c>
       <c r="B118" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>128203159</v>
       </c>
       <c r="B119" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128203101</v>
       </c>
       <c r="B120" t="n">
-        <v>98479</v>
+        <v>98493</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>128203213</v>
       </c>
       <c r="B121" t="n">
-        <v>98573</v>
+        <v>98587</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>128203230</v>
       </c>
       <c r="B122" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>128203190</v>
       </c>
       <c r="B123" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>128203216</v>
       </c>
       <c r="B124" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14471,10 +14471,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203235</v>
+        <v>128203092</v>
       </c>
       <c r="B125" t="n">
-        <v>110455</v>
+        <v>98563</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14482,37 +14482,46 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736279</v>
+        <v>736520</v>
       </c>
       <c r="R125" t="n">
-        <v>6411517</v>
+        <v>6411544</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14573,27 +14582,27 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203151</v>
+        <v>128203235</v>
       </c>
       <c r="B126" t="n">
-        <v>109398</v>
+        <v>110480</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -14608,13 +14617,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736248</v>
+        <v>736279</v>
       </c>
       <c r="R126" t="n">
-        <v>6411616</v>
+        <v>6411517</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14644,11 +14653,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14680,10 +14684,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203091</v>
+        <v>128203151</v>
       </c>
       <c r="B127" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14715,10 +14719,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736520</v>
+        <v>736248</v>
       </c>
       <c r="R127" t="n">
-        <v>6411544</v>
+        <v>6411616</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14751,6 +14755,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14782,44 +14791,35 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203092</v>
+        <v>128203091</v>
       </c>
       <c r="B128" t="n">
-        <v>98549</v>
+        <v>109422</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203093</v>
+        <v>128203178</v>
       </c>
       <c r="B129" t="n">
-        <v>109398</v>
+        <v>98111</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>221930</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736498</v>
+        <v>736300</v>
       </c>
       <c r="R129" t="n">
-        <v>6411566</v>
+        <v>6411481</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,6 +14966,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14977,7 +14982,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -14995,10 +15000,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203178</v>
+        <v>128203112</v>
       </c>
       <c r="B130" t="n">
-        <v>98098</v>
+        <v>98570</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15006,21 +15011,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221930</v>
+        <v>219799</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15030,10 +15035,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>736300</v>
+        <v>736184</v>
       </c>
       <c r="R130" t="n">
-        <v>6411481</v>
+        <v>6411805</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15070,7 +15075,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15084,7 +15089,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15102,10 +15107,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203112</v>
+        <v>128203113</v>
       </c>
       <c r="B131" t="n">
-        <v>98556</v>
+        <v>98587</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15113,21 +15118,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15209,10 +15214,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203113</v>
+        <v>128203252</v>
       </c>
       <c r="B132" t="n">
-        <v>98573</v>
+        <v>98607</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15220,37 +15225,46 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219811</v>
+        <v>219862</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736184</v>
+        <v>736193</v>
       </c>
       <c r="R132" t="n">
-        <v>6411805</v>
+        <v>6411456</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15282,11 +15296,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15298,7 +15307,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15316,57 +15325,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203252</v>
+        <v>128203093</v>
       </c>
       <c r="B133" t="n">
-        <v>98593</v>
+        <v>109422</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736193</v>
+        <v>736498</v>
       </c>
       <c r="R133" t="n">
-        <v>6411456</v>
+        <v>6411566</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203127</v>
+        <v>128203139</v>
       </c>
       <c r="B134" t="n">
-        <v>98556</v>
+        <v>98589</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15438,26 +15438,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219799</v>
+        <v>741</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736239</v>
+        <v>736244</v>
       </c>
       <c r="R134" t="n">
-        <v>6411738</v>
+        <v>6411666</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,48 +15538,57 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203083</v>
+        <v>128203228</v>
       </c>
       <c r="B135" t="n">
-        <v>109398</v>
+        <v>98570</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736442</v>
+        <v>736263</v>
       </c>
       <c r="R135" t="n">
-        <v>6411479</v>
+        <v>6411533</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15622,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15640,48 +15649,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203164</v>
+        <v>128203127</v>
       </c>
       <c r="B136" t="n">
-        <v>109398</v>
+        <v>98570</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736260</v>
+        <v>736239</v>
       </c>
       <c r="R136" t="n">
-        <v>6411450</v>
+        <v>6411738</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15724,7 +15742,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15742,57 +15760,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203139</v>
+        <v>128203083</v>
       </c>
       <c r="B137" t="n">
-        <v>98575</v>
+        <v>109422</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>741</v>
+        <v>220299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736244</v>
+        <v>736442</v>
       </c>
       <c r="R137" t="n">
-        <v>6411666</v>
+        <v>6411479</v>
       </c>
       <c r="S137" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15835,7 +15844,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15853,57 +15862,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203228</v>
+        <v>128203164</v>
       </c>
       <c r="B138" t="n">
-        <v>98556</v>
+        <v>109422</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736263</v>
+        <v>736260</v>
       </c>
       <c r="R138" t="n">
-        <v>6411533</v>
+        <v>6411450</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15967,7 +15967,7 @@
         <v>128203084</v>
       </c>
       <c r="B139" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>128203223</v>
       </c>
       <c r="B140" t="n">
-        <v>98479</v>
+        <v>98493</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>128203231</v>
       </c>
       <c r="B141" t="n">
-        <v>98549</v>
+        <v>98563</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>128203085</v>
       </c>
       <c r="B142" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>128203240</v>
       </c>
       <c r="B143" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6729,48 +6729,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203256</v>
+        <v>128203195</v>
       </c>
       <c r="B54" t="n">
-        <v>109422</v>
+        <v>98493</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736176</v>
+        <v>736314</v>
       </c>
       <c r="R54" t="n">
-        <v>6411455</v>
+        <v>6411572</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6802,6 +6811,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6813,7 +6827,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6831,45 +6845,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203241</v>
+        <v>128203096</v>
       </c>
       <c r="B55" t="n">
-        <v>109422</v>
+        <v>98563</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736223</v>
+        <v>736474</v>
       </c>
       <c r="R55" t="n">
-        <v>6411512</v>
+        <v>6411596</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6906,7 +6929,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6938,10 +6961,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203179</v>
+        <v>128203100</v>
       </c>
       <c r="B56" t="n">
-        <v>99626</v>
+        <v>98563</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6949,34 +6972,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222662</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736300</v>
+        <v>736361</v>
       </c>
       <c r="R56" t="n">
-        <v>6411481</v>
+        <v>6411697</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7022,7 +7054,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7040,10 +7072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203195</v>
+        <v>128203179</v>
       </c>
       <c r="B57" t="n">
-        <v>98493</v>
+        <v>99626</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7051,46 +7083,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219788</v>
+        <v>222662</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736314</v>
+        <v>736300</v>
       </c>
       <c r="R57" t="n">
-        <v>6411572</v>
+        <v>6411481</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7122,11 +7145,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7138,7 +7156,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7156,54 +7174,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203096</v>
+        <v>128203256</v>
       </c>
       <c r="B58" t="n">
-        <v>98563</v>
+        <v>109422</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736474</v>
+        <v>736176</v>
       </c>
       <c r="R58" t="n">
-        <v>6411596</v>
+        <v>6411455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7236,11 +7245,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7272,54 +7276,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203100</v>
+        <v>128203241</v>
       </c>
       <c r="B59" t="n">
-        <v>98563</v>
+        <v>109422</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736361</v>
+        <v>736223</v>
       </c>
       <c r="R59" t="n">
-        <v>6411697</v>
+        <v>6411512</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7352,6 +7347,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8264,48 +8264,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203239</v>
+        <v>128203209</v>
       </c>
       <c r="B68" t="n">
-        <v>109422</v>
+        <v>98587</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R68" t="n">
-        <v>6411500</v>
+        <v>6411567</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8337,11 +8346,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8353,7 +8357,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8478,57 +8482,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203209</v>
+        <v>128203239</v>
       </c>
       <c r="B70" t="n">
-        <v>98587</v>
+        <v>109422</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R70" t="n">
-        <v>6411567</v>
+        <v>6411500</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8560,6 +8555,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9132,48 +9132,57 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203199</v>
+        <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>98570</v>
+        <v>98591</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219799</v>
+        <v>742</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736314</v>
+        <v>736184</v>
       </c>
       <c r="R76" t="n">
-        <v>6411572</v>
+        <v>6411805</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9207,7 +9216,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9221,7 +9230,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9239,42 +9248,42 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203086</v>
+        <v>128203023</v>
       </c>
       <c r="B77" t="n">
-        <v>98563</v>
+        <v>57686</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9283,13 +9292,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736450</v>
+        <v>736365</v>
       </c>
       <c r="R77" t="n">
-        <v>6411486</v>
+        <v>6411573</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9350,10 +9359,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203221</v>
+        <v>128203199</v>
       </c>
       <c r="B78" t="n">
-        <v>98587</v>
+        <v>98570</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9361,46 +9370,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736272</v>
+        <v>736314</v>
       </c>
       <c r="R78" t="n">
-        <v>6411546</v>
+        <v>6411572</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9432,6 +9432,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9443,7 +9448,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9461,45 +9466,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203189</v>
+        <v>128203221</v>
       </c>
       <c r="B79" t="n">
-        <v>109422</v>
+        <v>98587</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736335</v>
+        <v>736272</v>
       </c>
       <c r="R79" t="n">
-        <v>6411533</v>
+        <v>6411546</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9545,7 +9559,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9563,48 +9577,57 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203185</v>
+        <v>128203086</v>
       </c>
       <c r="B80" t="n">
-        <v>109422</v>
+        <v>98563</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736331</v>
+        <v>736450</v>
       </c>
       <c r="R80" t="n">
-        <v>6411530</v>
+        <v>6411486</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9634,11 +9657,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9670,7 +9688,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203099</v>
+        <v>128203189</v>
       </c>
       <c r="B81" t="n">
         <v>109422</v>
@@ -9698,29 +9716,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736361</v>
+        <v>736335</v>
       </c>
       <c r="R81" t="n">
-        <v>6411697</v>
+        <v>6411533</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9781,10 +9790,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203114</v>
+        <v>128203185</v>
       </c>
       <c r="B82" t="n">
-        <v>98591</v>
+        <v>109422</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,43 +9801,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>742</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736184</v>
+        <v>736331</v>
       </c>
       <c r="R82" t="n">
-        <v>6411805</v>
+        <v>6411530</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,10 +9897,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203023</v>
+        <v>128203099</v>
       </c>
       <c r="B83" t="n">
-        <v>57686</v>
+        <v>109422</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9908,31 +9908,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736365</v>
+        <v>736361</v>
       </c>
       <c r="R83" t="n">
-        <v>6411573</v>
+        <v>6411697</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10573,10 +10573,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128205915</v>
+        <v>128203180</v>
       </c>
       <c r="B89" t="n">
-        <v>57686</v>
+        <v>105528</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10584,46 +10584,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>221137</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736315</v>
+        <v>736300</v>
       </c>
       <c r="R89" t="n">
-        <v>6411597</v>
+        <v>6411481</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10655,6 +10646,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10666,7 +10662,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10684,45 +10680,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203180</v>
+        <v>128203156</v>
       </c>
       <c r="B90" t="n">
-        <v>105528</v>
+        <v>98503</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221137</v>
+        <v>223591</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736300</v>
+        <v>736221</v>
       </c>
       <c r="R90" t="n">
-        <v>6411481</v>
+        <v>6411593</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10757,11 +10762,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10791,42 +10791,42 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203156</v>
+        <v>128205915</v>
       </c>
       <c r="B91" t="n">
-        <v>98503</v>
+        <v>57686</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10835,13 +10835,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736221</v>
+        <v>736315</v>
       </c>
       <c r="R91" t="n">
-        <v>6411593</v>
+        <v>6411597</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13484,42 +13484,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128203215</v>
+        <v>128203134</v>
       </c>
       <c r="B116" t="n">
-        <v>98570</v>
+        <v>109422</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13528,13 +13528,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>736301</v>
+        <v>736242</v>
       </c>
       <c r="R116" t="n">
-        <v>6411564</v>
+        <v>6411713</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128203134</v>
+        <v>128203247</v>
       </c>
       <c r="B117" t="n">
         <v>109422</v>
@@ -13623,26 +13623,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>736242</v>
+        <v>736192</v>
       </c>
       <c r="R117" t="n">
-        <v>6411713</v>
+        <v>6411467</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -13688,7 +13679,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13706,48 +13697,57 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128203247</v>
+        <v>128203215</v>
       </c>
       <c r="B118" t="n">
-        <v>109422</v>
+        <v>98570</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>736192</v>
+        <v>736301</v>
       </c>
       <c r="R118" t="n">
-        <v>6411467</v>
+        <v>6411564</v>
       </c>
       <c r="S118" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203139</v>
+        <v>128203228</v>
       </c>
       <c r="B134" t="n">
-        <v>98589</v>
+        <v>98570</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15438,26 +15438,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736244</v>
+        <v>736263</v>
       </c>
       <c r="R134" t="n">
-        <v>6411666</v>
+        <v>6411533</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,7 +15538,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203228</v>
+        <v>128203127</v>
       </c>
       <c r="B135" t="n">
         <v>98570</v>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15582,10 +15582,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736263</v>
+        <v>736239</v>
       </c>
       <c r="R135" t="n">
-        <v>6411533</v>
+        <v>6411738</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15649,10 +15649,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203127</v>
+        <v>128203139</v>
       </c>
       <c r="B136" t="n">
-        <v>98570</v>
+        <v>98589</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15660,26 +15660,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219799</v>
+        <v>741</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15693,13 +15693,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736239</v>
+        <v>736244</v>
       </c>
       <c r="R136" t="n">
-        <v>6411738</v>
+        <v>6411666</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,37 +6400,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203131</v>
+        <v>128203088</v>
       </c>
       <c r="B51" t="n">
-        <v>105528</v>
+        <v>98566</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6444,13 +6444,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736256</v>
+        <v>736474</v>
       </c>
       <c r="R51" t="n">
-        <v>6411743</v>
+        <v>6411506</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Våtmark mellan strandvallar.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203088</v>
+        <v>128203259</v>
       </c>
       <c r="B52" t="n">
-        <v>98563</v>
+        <v>110493</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6522,43 +6522,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736474</v>
+        <v>736176</v>
       </c>
       <c r="R52" t="n">
-        <v>6411506</v>
+        <v>6411455</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6591,6 +6582,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6622,27 +6618,27 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128203259</v>
+        <v>128203131</v>
       </c>
       <c r="B53" t="n">
-        <v>110480</v>
+        <v>105540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219677</v>
+        <v>221137</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6650,20 +6646,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736176</v>
+        <v>736256</v>
       </c>
       <c r="R53" t="n">
-        <v>6411455</v>
+        <v>6411743</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6695,11 +6700,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Våtmark mellan strandvallar.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
         <v>128203195</v>
       </c>
       <c r="B54" t="n">
-        <v>98493</v>
+        <v>98496</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>128203096</v>
       </c>
       <c r="B55" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128203100</v>
       </c>
       <c r="B56" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7072,27 +7072,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203179</v>
+        <v>128203256</v>
       </c>
       <c r="B57" t="n">
-        <v>99626</v>
+        <v>109435</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222662</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736300</v>
+        <v>736176</v>
       </c>
       <c r="R57" t="n">
-        <v>6411481</v>
+        <v>6411455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7174,10 +7174,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203256</v>
+        <v>128203241</v>
       </c>
       <c r="B58" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736176</v>
+        <v>736223</v>
       </c>
       <c r="R58" t="n">
-        <v>6411455</v>
+        <v>6411512</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7245,6 +7245,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7276,27 +7281,27 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203241</v>
+        <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>109422</v>
+        <v>99629</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7311,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736223</v>
+        <v>736300</v>
       </c>
       <c r="R59" t="n">
-        <v>6411512</v>
+        <v>6411481</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7349,11 +7354,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203021</v>
+        <v>128203220</v>
       </c>
       <c r="B60" t="n">
-        <v>57686</v>
+        <v>109435</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,27 +7394,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7423,10 +7427,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736197</v>
+        <v>736295</v>
       </c>
       <c r="R60" t="n">
-        <v>6411554</v>
+        <v>6411551</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7459,6 +7463,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7490,27 +7499,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203237</v>
+        <v>128203144</v>
       </c>
       <c r="B61" t="n">
-        <v>110480</v>
+        <v>109435</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7518,17 +7527,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736283</v>
+        <v>736246</v>
       </c>
       <c r="R61" t="n">
-        <v>6411500</v>
+        <v>6411634</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7565,7 +7583,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Överallt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7597,42 +7615,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203233</v>
+        <v>128203021</v>
       </c>
       <c r="B62" t="n">
-        <v>98570</v>
+        <v>57686</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219799</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7641,10 +7655,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736276</v>
+        <v>736197</v>
       </c>
       <c r="R62" t="n">
-        <v>6411531</v>
+        <v>6411554</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7690,7 +7704,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7708,10 +7722,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203186</v>
+        <v>128203237</v>
       </c>
       <c r="B63" t="n">
-        <v>98607</v>
+        <v>110493</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7719,46 +7733,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219862</v>
+        <v>219677</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736331</v>
+        <v>736283</v>
       </c>
       <c r="R63" t="n">
-        <v>6411530</v>
+        <v>6411500</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7788,6 +7793,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7819,42 +7829,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203220</v>
+        <v>128203233</v>
       </c>
       <c r="B64" t="n">
-        <v>109422</v>
+        <v>98573</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7863,10 +7873,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736295</v>
+        <v>736276</v>
       </c>
       <c r="R64" t="n">
-        <v>6411551</v>
+        <v>6411531</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7901,11 +7911,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7917,7 +7922,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7935,42 +7940,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203144</v>
+        <v>128203186</v>
       </c>
       <c r="B65" t="n">
-        <v>109422</v>
+        <v>98610</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7979,13 +7984,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736246</v>
+        <v>736331</v>
       </c>
       <c r="R65" t="n">
-        <v>6411634</v>
+        <v>6411530</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8015,11 +8020,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8054,7 +8054,7 @@
         <v>128203089</v>
       </c>
       <c r="B66" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>128203243</v>
       </c>
       <c r="B67" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>128203209</v>
       </c>
       <c r="B68" t="n">
-        <v>98587</v>
+        <v>98590</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8375,10 +8375,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203104</v>
+        <v>128203239</v>
       </c>
       <c r="B69" t="n">
-        <v>105528</v>
+        <v>109435</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8386,16 +8386,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8410,13 +8410,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736325</v>
+        <v>736283</v>
       </c>
       <c r="R69" t="n">
-        <v>6411730</v>
+        <v>6411500</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Spridd. Flera i blom.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8482,10 +8482,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203239</v>
+        <v>128203095</v>
       </c>
       <c r="B70" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8517,13 +8517,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736283</v>
+        <v>736474</v>
       </c>
       <c r="R70" t="n">
-        <v>6411500</v>
+        <v>6411596</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8589,10 +8589,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203095</v>
+        <v>128203104</v>
       </c>
       <c r="B71" t="n">
-        <v>109422</v>
+        <v>105540</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,16 +8600,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8624,13 +8624,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736474</v>
+        <v>736325</v>
       </c>
       <c r="R71" t="n">
-        <v>6411596</v>
+        <v>6411730</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8696,44 +8696,35 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128203182</v>
+        <v>128203181</v>
       </c>
       <c r="B72" t="n">
-        <v>98563</v>
+        <v>109435</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8780,7 +8771,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Stig över våtmark; avsnitslat.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8812,57 +8803,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128203187</v>
+        <v>128203166</v>
       </c>
       <c r="B73" t="n">
-        <v>98563</v>
+        <v>109435</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736331</v>
+        <v>736275</v>
       </c>
       <c r="R73" t="n">
-        <v>6411530</v>
+        <v>6411455</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8923,35 +8905,44 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203181</v>
+        <v>128203182</v>
       </c>
       <c r="B74" t="n">
-        <v>109422</v>
+        <v>98566</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8998,7 +8989,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9030,48 +9021,57 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128203166</v>
+        <v>128203187</v>
       </c>
       <c r="B75" t="n">
-        <v>109422</v>
+        <v>98566</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736275</v>
+        <v>736331</v>
       </c>
       <c r="R75" t="n">
-        <v>6411455</v>
+        <v>6411530</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>98591</v>
+        <v>98594</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9359,32 +9359,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203199</v>
+        <v>128203189</v>
       </c>
       <c r="B78" t="n">
-        <v>98570</v>
+        <v>109435</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9394,13 +9394,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736314</v>
+        <v>736335</v>
       </c>
       <c r="R78" t="n">
-        <v>6411572</v>
+        <v>6411533</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9432,11 +9432,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9448,7 +9443,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9466,54 +9461,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203221</v>
+        <v>128203185</v>
       </c>
       <c r="B79" t="n">
-        <v>98587</v>
+        <v>109435</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736272</v>
+        <v>736331</v>
       </c>
       <c r="R79" t="n">
-        <v>6411546</v>
+        <v>6411530</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9548,6 +9534,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9559,7 +9550,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9577,42 +9568,42 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203086</v>
+        <v>128203099</v>
       </c>
       <c r="B80" t="n">
-        <v>98563</v>
+        <v>109435</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9621,10 +9612,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736450</v>
+        <v>736361</v>
       </c>
       <c r="R80" t="n">
-        <v>6411486</v>
+        <v>6411697</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9688,32 +9679,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203189</v>
+        <v>128203199</v>
       </c>
       <c r="B81" t="n">
-        <v>109422</v>
+        <v>98573</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9723,13 +9714,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736335</v>
+        <v>736314</v>
       </c>
       <c r="R81" t="n">
-        <v>6411533</v>
+        <v>6411572</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9761,6 +9752,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9772,7 +9768,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9790,48 +9786,57 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203185</v>
+        <v>128203086</v>
       </c>
       <c r="B82" t="n">
-        <v>109422</v>
+        <v>98566</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736331</v>
+        <v>736450</v>
       </c>
       <c r="R82" t="n">
-        <v>6411530</v>
+        <v>6411486</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9861,11 +9866,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9897,42 +9897,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203099</v>
+        <v>128203221</v>
       </c>
       <c r="B83" t="n">
-        <v>109422</v>
+        <v>98590</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736361</v>
+        <v>736272</v>
       </c>
       <c r="R83" t="n">
-        <v>6411697</v>
+        <v>6411546</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10011,7 +10011,7 @@
         <v>128203192</v>
       </c>
       <c r="B84" t="n">
-        <v>105528</v>
+        <v>105540</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>128203249</v>
       </c>
       <c r="B85" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>128203132</v>
       </c>
       <c r="B86" t="n">
-        <v>107479</v>
+        <v>107491</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>128203162</v>
       </c>
       <c r="B87" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>128203111</v>
       </c>
       <c r="B88" t="n">
-        <v>98516</v>
+        <v>98519</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10573,10 +10573,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203180</v>
+        <v>128205915</v>
       </c>
       <c r="B89" t="n">
-        <v>105528</v>
+        <v>57686</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10584,37 +10584,46 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221137</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736300</v>
+        <v>736315</v>
       </c>
       <c r="R89" t="n">
-        <v>6411481</v>
+        <v>6411597</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10646,11 +10655,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10662,7 +10666,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10680,10 +10684,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203156</v>
+        <v>128203165</v>
       </c>
       <c r="B90" t="n">
-        <v>98503</v>
+        <v>98566</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10691,26 +10695,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10724,10 +10728,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736221</v>
+        <v>736260</v>
       </c>
       <c r="R90" t="n">
-        <v>6411593</v>
+        <v>6411450</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10773,7 +10777,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10791,32 +10795,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128205915</v>
+        <v>128203081</v>
       </c>
       <c r="B91" t="n">
-        <v>57686</v>
+        <v>98566</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10824,9 +10828,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10835,13 +10839,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736315</v>
+        <v>736347</v>
       </c>
       <c r="R91" t="n">
-        <v>6411597</v>
+        <v>6411466</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10902,10 +10906,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203165</v>
+        <v>128203225</v>
       </c>
       <c r="B92" t="n">
-        <v>98563</v>
+        <v>98590</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10913,26 +10917,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10946,13 +10950,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736260</v>
+        <v>736263</v>
       </c>
       <c r="R92" t="n">
-        <v>6411450</v>
+        <v>6411533</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10995,7 +10999,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11013,32 +11017,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203211</v>
+        <v>128203197</v>
       </c>
       <c r="B93" t="n">
-        <v>99260</v>
+        <v>98590</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11048,13 +11052,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736301</v>
+        <v>736314</v>
       </c>
       <c r="R93" t="n">
-        <v>6411564</v>
+        <v>6411572</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11084,6 +11088,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11115,54 +11124,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203081</v>
+        <v>128203180</v>
       </c>
       <c r="B94" t="n">
-        <v>98563</v>
+        <v>105540</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736347</v>
+        <v>736300</v>
       </c>
       <c r="R94" t="n">
-        <v>6411466</v>
+        <v>6411481</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11197,6 +11197,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11208,7 +11213,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11226,57 +11231,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203225</v>
+        <v>128203211</v>
       </c>
       <c r="B95" t="n">
-        <v>98587</v>
+        <v>99263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736263</v>
+        <v>736301</v>
       </c>
       <c r="R95" t="n">
-        <v>6411533</v>
+        <v>6411564</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11319,7 +11315,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11337,10 +11333,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203197</v>
+        <v>128203156</v>
       </c>
       <c r="B96" t="n">
-        <v>98587</v>
+        <v>98506</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11348,37 +11344,46 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736314</v>
+        <v>736221</v>
       </c>
       <c r="R96" t="n">
-        <v>6411572</v>
+        <v>6411593</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11410,11 +11415,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11444,32 +11444,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203087</v>
+        <v>128203106</v>
       </c>
       <c r="B97" t="n">
-        <v>109422</v>
+        <v>98590</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736474</v>
+        <v>736305</v>
       </c>
       <c r="R97" t="n">
-        <v>6411506</v>
+        <v>6411739</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11517,6 +11517,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11528,7 +11533,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11546,48 +11551,57 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203246</v>
+        <v>128203167</v>
       </c>
       <c r="B98" t="n">
-        <v>109422</v>
+        <v>98566</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736213</v>
+        <v>736275</v>
       </c>
       <c r="R98" t="n">
-        <v>6411456</v>
+        <v>6411455</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11617,11 +11631,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11653,10 +11662,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203080</v>
+        <v>128203087</v>
       </c>
       <c r="B99" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11688,10 +11697,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736347</v>
+        <v>736474</v>
       </c>
       <c r="R99" t="n">
-        <v>6411466</v>
+        <v>6411506</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11755,32 +11764,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203106</v>
+        <v>128203246</v>
       </c>
       <c r="B100" t="n">
-        <v>98587</v>
+        <v>109435</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11790,13 +11799,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736305</v>
+        <v>736213</v>
       </c>
       <c r="R100" t="n">
-        <v>6411739</v>
+        <v>6411456</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11830,7 +11839,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11844,7 +11853,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11862,54 +11871,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203167</v>
+        <v>128203080</v>
       </c>
       <c r="B101" t="n">
-        <v>98563</v>
+        <v>109435</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736275</v>
+        <v>736347</v>
       </c>
       <c r="R101" t="n">
-        <v>6411455</v>
+        <v>6411466</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11973,54 +11973,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203154</v>
+        <v>128203129</v>
       </c>
       <c r="B102" t="n">
-        <v>98493</v>
+        <v>105540</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R102" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12066,7 +12057,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12084,10 +12075,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203126</v>
+        <v>128203154</v>
       </c>
       <c r="B103" t="n">
-        <v>98587</v>
+        <v>98496</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12095,26 +12086,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219811</v>
+        <v>219788</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12128,13 +12119,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R103" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12177,7 +12168,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12195,35 +12186,44 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203129</v>
+        <v>128203126</v>
       </c>
       <c r="B104" t="n">
-        <v>105528</v>
+        <v>98590</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12297,10 +12297,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203242</v>
+        <v>128203107</v>
       </c>
       <c r="B105" t="n">
-        <v>109422</v>
+        <v>105540</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12308,16 +12308,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736237</v>
+        <v>736305</v>
       </c>
       <c r="R105" t="n">
-        <v>6411484</v>
+        <v>6411739</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12404,48 +12404,57 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203255</v>
+        <v>128203207</v>
       </c>
       <c r="B106" t="n">
-        <v>109422</v>
+        <v>98590</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736200</v>
+        <v>736300</v>
       </c>
       <c r="R106" t="n">
-        <v>6411456</v>
+        <v>6411576</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12488,7 +12497,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12506,32 +12515,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203107</v>
+        <v>128203177</v>
       </c>
       <c r="B107" t="n">
-        <v>105528</v>
+        <v>98573</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221137</v>
+        <v>219799</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12541,10 +12550,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736305</v>
+        <v>736300</v>
       </c>
       <c r="R107" t="n">
-        <v>6411739</v>
+        <v>6411481</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12581,7 +12590,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12595,7 +12604,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12613,10 +12622,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203207</v>
+        <v>128203234</v>
       </c>
       <c r="B108" t="n">
-        <v>98587</v>
+        <v>98566</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12624,26 +12633,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -12657,10 +12666,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736300</v>
+        <v>736279</v>
       </c>
       <c r="R108" t="n">
-        <v>6411576</v>
+        <v>6411517</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12706,7 +12715,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12724,32 +12733,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203177</v>
+        <v>128203242</v>
       </c>
       <c r="B109" t="n">
-        <v>98570</v>
+        <v>109435</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12759,10 +12768,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736300</v>
+        <v>736237</v>
       </c>
       <c r="R109" t="n">
-        <v>6411481</v>
+        <v>6411484</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12799,7 +12808,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12813,7 +12822,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12831,57 +12840,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203234</v>
+        <v>128203255</v>
       </c>
       <c r="B110" t="n">
-        <v>98563</v>
+        <v>109435</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736279</v>
+        <v>736200</v>
       </c>
       <c r="R110" t="n">
-        <v>6411517</v>
+        <v>6411456</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>128203160</v>
       </c>
       <c r="B111" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>128203138</v>
       </c>
       <c r="B112" t="n">
-        <v>98570</v>
+        <v>98573</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>128203094</v>
       </c>
       <c r="B113" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>128203161</v>
       </c>
       <c r="B114" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>128203236</v>
       </c>
       <c r="B115" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>128203134</v>
       </c>
       <c r="B116" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>128203247</v>
       </c>
       <c r="B117" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>128203215</v>
       </c>
       <c r="B118" t="n">
-        <v>98570</v>
+        <v>98573</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13808,48 +13808,57 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128203159</v>
+        <v>128203101</v>
       </c>
       <c r="B119" t="n">
-        <v>109422</v>
+        <v>98496</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>736240</v>
+        <v>736358</v>
       </c>
       <c r="R119" t="n">
-        <v>6411466</v>
+        <v>6411725</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13881,11 +13890,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13897,7 +13901,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13915,57 +13919,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128203101</v>
+        <v>128203159</v>
       </c>
       <c r="B120" t="n">
-        <v>98493</v>
+        <v>109435</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>736358</v>
+        <v>736240</v>
       </c>
       <c r="R120" t="n">
-        <v>6411725</v>
+        <v>6411466</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13997,6 +13992,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14029,7 +14029,7 @@
         <v>128203213</v>
       </c>
       <c r="B121" t="n">
-        <v>98587</v>
+        <v>98590</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>128203230</v>
       </c>
       <c r="B122" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>128203190</v>
       </c>
       <c r="B123" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>128203216</v>
       </c>
       <c r="B124" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>128203092</v>
       </c>
       <c r="B125" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>128203235</v>
       </c>
       <c r="B126" t="n">
-        <v>110480</v>
+        <v>110493</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>128203151</v>
       </c>
       <c r="B127" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>128203091</v>
       </c>
       <c r="B128" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14893,10 +14893,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203178</v>
+        <v>128203112</v>
       </c>
       <c r="B129" t="n">
-        <v>98111</v>
+        <v>98573</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14904,21 +14904,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221930</v>
+        <v>219799</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736300</v>
+        <v>736184</v>
       </c>
       <c r="R129" t="n">
-        <v>6411481</v>
+        <v>6411805</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15000,10 +15000,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203112</v>
+        <v>128203113</v>
       </c>
       <c r="B130" t="n">
-        <v>98570</v>
+        <v>98590</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15011,21 +15011,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15107,10 +15107,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203113</v>
+        <v>128203252</v>
       </c>
       <c r="B131" t="n">
-        <v>98587</v>
+        <v>98610</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15118,37 +15118,46 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219811</v>
+        <v>219862</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>736184</v>
+        <v>736193</v>
       </c>
       <c r="R131" t="n">
-        <v>6411805</v>
+        <v>6411456</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15180,11 +15189,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15196,7 +15200,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15214,10 +15218,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203252</v>
+        <v>128203178</v>
       </c>
       <c r="B132" t="n">
-        <v>98607</v>
+        <v>98114</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15225,46 +15229,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219862</v>
+        <v>221930</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Wahlenb.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736193</v>
+        <v>736300</v>
       </c>
       <c r="R132" t="n">
-        <v>6411456</v>
+        <v>6411481</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15296,6 +15291,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15328,7 +15328,7 @@
         <v>128203093</v>
       </c>
       <c r="B133" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203228</v>
+        <v>128203139</v>
       </c>
       <c r="B134" t="n">
-        <v>98570</v>
+        <v>98592</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15438,26 +15438,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219799</v>
+        <v>741</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736263</v>
+        <v>736244</v>
       </c>
       <c r="R134" t="n">
-        <v>6411533</v>
+        <v>6411666</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,10 +15538,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203127</v>
+        <v>128203228</v>
       </c>
       <c r="B135" t="n">
-        <v>98570</v>
+        <v>98573</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15582,10 +15582,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736239</v>
+        <v>736263</v>
       </c>
       <c r="R135" t="n">
-        <v>6411738</v>
+        <v>6411533</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15649,10 +15649,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203139</v>
+        <v>128203127</v>
       </c>
       <c r="B136" t="n">
-        <v>98589</v>
+        <v>98573</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15660,26 +15660,26 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15693,13 +15693,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736244</v>
+        <v>736239</v>
       </c>
       <c r="R136" t="n">
-        <v>6411666</v>
+        <v>6411738</v>
       </c>
       <c r="S136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15763,7 +15763,7 @@
         <v>128203083</v>
       </c>
       <c r="B137" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>128203164</v>
       </c>
       <c r="B138" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15964,54 +15964,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203084</v>
+        <v>128203085</v>
       </c>
       <c r="B139" t="n">
-        <v>98563</v>
+        <v>109435</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736442</v>
+        <v>736450</v>
       </c>
       <c r="R139" t="n">
-        <v>6411479</v>
+        <v>6411486</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16075,57 +16066,48 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203223</v>
+        <v>128203240</v>
       </c>
       <c r="B140" t="n">
-        <v>98493</v>
+        <v>109435</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736272</v>
+        <v>736238</v>
       </c>
       <c r="R140" t="n">
-        <v>6411536</v>
+        <v>6411496</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16157,6 +16139,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -16168,7 +16155,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16186,10 +16173,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203231</v>
+        <v>128203084</v>
       </c>
       <c r="B141" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16216,7 +16203,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16230,13 +16217,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736270</v>
+        <v>736442</v>
       </c>
       <c r="R141" t="n">
-        <v>6411530</v>
+        <v>6411479</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16297,48 +16284,57 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203085</v>
+        <v>128203223</v>
       </c>
       <c r="B142" t="n">
-        <v>109422</v>
+        <v>98496</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736450</v>
+        <v>736272</v>
       </c>
       <c r="R142" t="n">
-        <v>6411486</v>
+        <v>6411536</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16381,7 +16377,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -16399,48 +16395,57 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128203240</v>
+        <v>128203231</v>
       </c>
       <c r="B143" t="n">
-        <v>109422</v>
+        <v>98566</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>736238</v>
+        <v>736270</v>
       </c>
       <c r="R143" t="n">
-        <v>6411496</v>
+        <v>6411530</v>
       </c>
       <c r="S143" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16470,11 +16475,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6403,7 +6403,7 @@
         <v>128203088</v>
       </c>
       <c r="B51" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128203259</v>
       </c>
       <c r="B52" t="n">
-        <v>110493</v>
+        <v>110502</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>128203131</v>
       </c>
       <c r="B53" t="n">
-        <v>105540</v>
+        <v>105549</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6729,57 +6729,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203195</v>
+        <v>128203256</v>
       </c>
       <c r="B54" t="n">
-        <v>98496</v>
+        <v>109444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736314</v>
+        <v>736176</v>
       </c>
       <c r="R54" t="n">
-        <v>6411572</v>
+        <v>6411455</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6811,11 +6802,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6827,7 +6813,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6845,54 +6831,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203096</v>
+        <v>128203241</v>
       </c>
       <c r="B55" t="n">
-        <v>98566</v>
+        <v>109444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736474</v>
+        <v>736223</v>
       </c>
       <c r="R55" t="n">
-        <v>6411596</v>
+        <v>6411512</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6929,7 +6906,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6961,10 +6938,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203100</v>
+        <v>128203195</v>
       </c>
       <c r="B56" t="n">
-        <v>98566</v>
+        <v>98499</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6972,26 +6949,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7005,13 +6982,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736361</v>
+        <v>736314</v>
       </c>
       <c r="R56" t="n">
-        <v>6411697</v>
+        <v>6411572</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7043,6 +7020,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7054,7 +7036,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7072,45 +7054,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203256</v>
+        <v>128203096</v>
       </c>
       <c r="B57" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R57" t="n">
-        <v>6411455</v>
+        <v>6411596</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7143,6 +7134,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7174,45 +7170,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203241</v>
+        <v>128203100</v>
       </c>
       <c r="B58" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736223</v>
+        <v>736361</v>
       </c>
       <c r="R58" t="n">
-        <v>6411512</v>
+        <v>6411697</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7245,11 +7250,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7284,7 +7284,7 @@
         <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>99629</v>
+        <v>99634</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>128203220</v>
       </c>
       <c r="B60" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7499,27 +7499,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203144</v>
+        <v>128203237</v>
       </c>
       <c r="B61" t="n">
-        <v>109435</v>
+        <v>110502</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7527,26 +7527,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736246</v>
+        <v>736283</v>
       </c>
       <c r="R61" t="n">
-        <v>6411634</v>
+        <v>6411500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7583,7 +7574,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7615,38 +7606,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203021</v>
+        <v>128203233</v>
       </c>
       <c r="B62" t="n">
-        <v>57686</v>
+        <v>98576</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>219799</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7655,10 +7650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736197</v>
+        <v>736276</v>
       </c>
       <c r="R62" t="n">
-        <v>6411554</v>
+        <v>6411531</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7704,7 +7699,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7722,10 +7717,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203237</v>
+        <v>128203186</v>
       </c>
       <c r="B63" t="n">
-        <v>110493</v>
+        <v>98613</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7733,37 +7728,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219677</v>
+        <v>219862</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736283</v>
+        <v>736331</v>
       </c>
       <c r="R63" t="n">
-        <v>6411500</v>
+        <v>6411530</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7793,11 +7797,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7829,42 +7828,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203233</v>
+        <v>128203021</v>
       </c>
       <c r="B64" t="n">
-        <v>98573</v>
+        <v>57686</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219799</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7873,10 +7868,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736276</v>
+        <v>736197</v>
       </c>
       <c r="R64" t="n">
-        <v>6411531</v>
+        <v>6411554</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7922,7 +7917,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7940,42 +7935,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203186</v>
+        <v>128203144</v>
       </c>
       <c r="B65" t="n">
-        <v>98610</v>
+        <v>109444</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7984,13 +7979,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736331</v>
+        <v>736246</v>
       </c>
       <c r="R65" t="n">
-        <v>6411530</v>
+        <v>6411634</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8020,6 +8015,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8051,54 +8051,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128203089</v>
+        <v>128203243</v>
       </c>
       <c r="B66" t="n">
-        <v>98566</v>
+        <v>109444</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>736488</v>
+        <v>736237</v>
       </c>
       <c r="R66" t="n">
-        <v>6411510</v>
+        <v>6411472</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8144,7 +8135,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8162,45 +8153,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128203243</v>
+        <v>128203089</v>
       </c>
       <c r="B67" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>736237</v>
+        <v>736488</v>
       </c>
       <c r="R67" t="n">
-        <v>6411472</v>
+        <v>6411510</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8264,57 +8264,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203209</v>
+        <v>128203239</v>
       </c>
       <c r="B68" t="n">
-        <v>98590</v>
+        <v>109444</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R68" t="n">
-        <v>6411567</v>
+        <v>6411500</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8346,6 +8337,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8357,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8375,10 +8371,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203239</v>
+        <v>128203095</v>
       </c>
       <c r="B69" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8410,13 +8406,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736283</v>
+        <v>736474</v>
       </c>
       <c r="R69" t="n">
-        <v>6411500</v>
+        <v>6411596</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8450,7 +8446,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8482,48 +8478,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203095</v>
+        <v>128203209</v>
       </c>
       <c r="B70" t="n">
-        <v>109435</v>
+        <v>98593</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736474</v>
+        <v>736295</v>
       </c>
       <c r="R70" t="n">
-        <v>6411596</v>
+        <v>6411567</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8555,11 +8560,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8592,7 +8592,7 @@
         <v>128203104</v>
       </c>
       <c r="B71" t="n">
-        <v>105540</v>
+        <v>105549</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>128203181</v>
       </c>
       <c r="B72" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>128203166</v>
       </c>
       <c r="B73" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>128203182</v>
       </c>
       <c r="B74" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>128203187</v>
       </c>
       <c r="B75" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9132,57 +9132,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203114</v>
+        <v>128203199</v>
       </c>
       <c r="B76" t="n">
-        <v>98594</v>
+        <v>98576</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>742</v>
+        <v>219799</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736184</v>
+        <v>736314</v>
       </c>
       <c r="R76" t="n">
-        <v>6411805</v>
+        <v>6411572</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9216,7 +9207,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9230,7 +9221,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9248,42 +9239,42 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203023</v>
+        <v>128203086</v>
       </c>
       <c r="B77" t="n">
-        <v>57686</v>
+        <v>98569</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9292,13 +9283,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736365</v>
+        <v>736450</v>
       </c>
       <c r="R77" t="n">
-        <v>6411573</v>
+        <v>6411486</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9359,45 +9350,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203189</v>
+        <v>128203221</v>
       </c>
       <c r="B78" t="n">
-        <v>109435</v>
+        <v>98593</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736335</v>
+        <v>736272</v>
       </c>
       <c r="R78" t="n">
-        <v>6411533</v>
+        <v>6411546</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9461,10 +9461,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203185</v>
+        <v>128203114</v>
       </c>
       <c r="B79" t="n">
-        <v>109435</v>
+        <v>98597</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9472,34 +9472,43 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220299</v>
+        <v>742</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736331</v>
+        <v>736184</v>
       </c>
       <c r="R79" t="n">
-        <v>6411530</v>
+        <v>6411805</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9536,7 +9545,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9550,7 +9559,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9568,10 +9577,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203099</v>
+        <v>128203023</v>
       </c>
       <c r="B80" t="n">
-        <v>109435</v>
+        <v>57686</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9579,31 +9588,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9612,13 +9621,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736361</v>
+        <v>736365</v>
       </c>
       <c r="R80" t="n">
-        <v>6411697</v>
+        <v>6411573</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9679,32 +9688,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203199</v>
+        <v>128203189</v>
       </c>
       <c r="B81" t="n">
-        <v>98573</v>
+        <v>109444</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9714,13 +9723,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736314</v>
+        <v>736335</v>
       </c>
       <c r="R81" t="n">
-        <v>6411572</v>
+        <v>6411533</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9752,11 +9761,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9768,7 +9772,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9786,57 +9790,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203086</v>
+        <v>128203185</v>
       </c>
       <c r="B82" t="n">
-        <v>98566</v>
+        <v>109444</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736450</v>
+        <v>736331</v>
       </c>
       <c r="R82" t="n">
-        <v>6411486</v>
+        <v>6411530</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9866,6 +9861,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9897,42 +9897,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203221</v>
+        <v>128203099</v>
       </c>
       <c r="B83" t="n">
-        <v>98590</v>
+        <v>109444</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736272</v>
+        <v>736361</v>
       </c>
       <c r="R83" t="n">
-        <v>6411546</v>
+        <v>6411697</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10011,7 +10011,7 @@
         <v>128203192</v>
       </c>
       <c r="B84" t="n">
-        <v>105540</v>
+        <v>105549</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10124,32 +10124,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203249</v>
+        <v>128203132</v>
       </c>
       <c r="B85" t="n">
-        <v>98566</v>
+        <v>107500</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219798</v>
+        <v>220079</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736192</v>
+        <v>736242</v>
       </c>
       <c r="R85" t="n">
-        <v>6411467</v>
+        <v>6411713</v>
       </c>
       <c r="S85" t="n">
         <v>3</v>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10235,32 +10235,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203132</v>
+        <v>128203249</v>
       </c>
       <c r="B86" t="n">
-        <v>107491</v>
+        <v>98569</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736242</v>
+        <v>736192</v>
       </c>
       <c r="R86" t="n">
-        <v>6411713</v>
+        <v>6411467</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10349,7 +10349,7 @@
         <v>128203162</v>
       </c>
       <c r="B87" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>128203111</v>
       </c>
       <c r="B88" t="n">
-        <v>98519</v>
+        <v>98522</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B89" t="n">
-        <v>57686</v>
+        <v>98569</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R89" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203165</v>
+        <v>128203081</v>
       </c>
       <c r="B90" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736260</v>
+        <v>736347</v>
       </c>
       <c r="R90" t="n">
-        <v>6411450</v>
+        <v>6411466</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10795,10 +10795,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203081</v>
+        <v>128203225</v>
       </c>
       <c r="B91" t="n">
-        <v>98566</v>
+        <v>98593</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,21 +10806,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10839,13 +10839,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736347</v>
+        <v>736263</v>
       </c>
       <c r="R91" t="n">
-        <v>6411466</v>
+        <v>6411533</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203225</v>
+        <v>128203197</v>
       </c>
       <c r="B92" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10934,29 +10934,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736263</v>
+        <v>736314</v>
       </c>
       <c r="R92" t="n">
-        <v>6411533</v>
+        <v>6411572</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10988,6 +10979,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10999,7 +10995,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11017,32 +11013,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203197</v>
+        <v>128203180</v>
       </c>
       <c r="B93" t="n">
-        <v>98590</v>
+        <v>105549</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11052,13 +11048,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736314</v>
+        <v>736300</v>
       </c>
       <c r="R93" t="n">
-        <v>6411572</v>
+        <v>6411481</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11092,7 +11088,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11106,7 +11102,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11124,10 +11120,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203180</v>
+        <v>128203211</v>
       </c>
       <c r="B94" t="n">
-        <v>105540</v>
+        <v>99268</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11135,21 +11131,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221137</v>
+        <v>222322</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11159,13 +11155,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736300</v>
+        <v>736301</v>
       </c>
       <c r="R94" t="n">
-        <v>6411481</v>
+        <v>6411564</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11197,11 +11193,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11213,7 +11204,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11231,48 +11222,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203211</v>
+        <v>128203156</v>
       </c>
       <c r="B95" t="n">
-        <v>99263</v>
+        <v>98509</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222322</v>
+        <v>223591</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736301</v>
+        <v>736221</v>
       </c>
       <c r="R95" t="n">
-        <v>6411564</v>
+        <v>6411593</v>
       </c>
       <c r="S95" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11333,42 +11333,42 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203156</v>
+        <v>128205915</v>
       </c>
       <c r="B96" t="n">
-        <v>98506</v>
+        <v>57686</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11377,13 +11377,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736221</v>
+        <v>736315</v>
       </c>
       <c r="R96" t="n">
-        <v>6411593</v>
+        <v>6411597</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11447,7 +11447,7 @@
         <v>128203106</v>
       </c>
       <c r="B97" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>128203167</v>
       </c>
       <c r="B98" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>128203087</v>
       </c>
       <c r="B99" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>128203246</v>
       </c>
       <c r="B100" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>128203080</v>
       </c>
       <c r="B101" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11973,45 +11973,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203129</v>
+        <v>128203154</v>
       </c>
       <c r="B102" t="n">
-        <v>105540</v>
+        <v>98499</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221137</v>
+        <v>219788</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R102" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12057,7 +12066,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12075,10 +12084,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203154</v>
+        <v>128203126</v>
       </c>
       <c r="B103" t="n">
-        <v>98496</v>
+        <v>98593</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12086,26 +12095,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219788</v>
+        <v>219811</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12119,13 +12128,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R103" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12168,7 +12177,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12186,44 +12195,35 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203126</v>
+        <v>128203129</v>
       </c>
       <c r="B104" t="n">
-        <v>98590</v>
+        <v>105549</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12297,10 +12297,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203107</v>
+        <v>128203242</v>
       </c>
       <c r="B105" t="n">
-        <v>105540</v>
+        <v>109444</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12308,16 +12308,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736305</v>
+        <v>736237</v>
       </c>
       <c r="R105" t="n">
-        <v>6411739</v>
+        <v>6411484</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12404,57 +12404,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203207</v>
+        <v>128203255</v>
       </c>
       <c r="B106" t="n">
-        <v>98590</v>
+        <v>109444</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736300</v>
+        <v>736200</v>
       </c>
       <c r="R106" t="n">
-        <v>6411576</v>
+        <v>6411456</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12497,7 +12488,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12515,10 +12506,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203177</v>
+        <v>128203207</v>
       </c>
       <c r="B107" t="n">
-        <v>98573</v>
+        <v>98593</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12526,24 +12517,33 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12553,10 +12553,10 @@
         <v>736300</v>
       </c>
       <c r="R107" t="n">
-        <v>6411481</v>
+        <v>6411576</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12588,11 +12588,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12604,7 +12599,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12622,10 +12617,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203234</v>
+        <v>128203177</v>
       </c>
       <c r="B108" t="n">
-        <v>98566</v>
+        <v>98576</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12633,16 +12628,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12650,29 +12645,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736279</v>
+        <v>736300</v>
       </c>
       <c r="R108" t="n">
-        <v>6411517</v>
+        <v>6411481</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12704,6 +12690,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -12715,7 +12706,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12733,48 +12724,57 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203242</v>
+        <v>128203234</v>
       </c>
       <c r="B109" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736237</v>
+        <v>736279</v>
       </c>
       <c r="R109" t="n">
-        <v>6411484</v>
+        <v>6411517</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12804,11 +12804,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12840,10 +12835,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203255</v>
+        <v>128203107</v>
       </c>
       <c r="B110" t="n">
-        <v>109435</v>
+        <v>105549</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12851,16 +12846,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12875,10 +12870,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736200</v>
+        <v>736305</v>
       </c>
       <c r="R110" t="n">
-        <v>6411456</v>
+        <v>6411739</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12913,6 +12908,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12942,54 +12942,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128203160</v>
+        <v>128203161</v>
       </c>
       <c r="B111" t="n">
-        <v>98566</v>
+        <v>109444</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>736240</v>
+        <v>736250</v>
       </c>
       <c r="R111" t="n">
-        <v>6411466</v>
+        <v>6411464</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13053,57 +13044,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128203138</v>
+        <v>128203236</v>
       </c>
       <c r="B112" t="n">
-        <v>98573</v>
+        <v>109444</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>736231</v>
+        <v>736279</v>
       </c>
       <c r="R112" t="n">
-        <v>6411673</v>
+        <v>6411517</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13135,6 +13117,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -13146,7 +13133,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13164,10 +13151,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128203094</v>
+        <v>128203160</v>
       </c>
       <c r="B113" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13208,10 +13195,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>736498</v>
+        <v>736240</v>
       </c>
       <c r="R113" t="n">
-        <v>6411566</v>
+        <v>6411466</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13275,48 +13262,57 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128203161</v>
+        <v>128203138</v>
       </c>
       <c r="B114" t="n">
-        <v>109435</v>
+        <v>98576</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>736250</v>
+        <v>736231</v>
       </c>
       <c r="R114" t="n">
-        <v>6411464</v>
+        <v>6411673</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13359,7 +13355,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13377,48 +13373,57 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128203236</v>
+        <v>128203094</v>
       </c>
       <c r="B115" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>736279</v>
+        <v>736498</v>
       </c>
       <c r="R115" t="n">
-        <v>6411517</v>
+        <v>6411566</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13448,11 +13453,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13487,7 +13487,7 @@
         <v>128203134</v>
       </c>
       <c r="B116" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>128203247</v>
       </c>
       <c r="B117" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>128203215</v>
       </c>
       <c r="B118" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>128203101</v>
       </c>
       <c r="B119" t="n">
-        <v>98496</v>
+        <v>98499</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>128203159</v>
       </c>
       <c r="B120" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>128203213</v>
       </c>
       <c r="B121" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>128203230</v>
       </c>
       <c r="B122" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14244,57 +14244,48 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128203190</v>
+        <v>128203151</v>
       </c>
       <c r="B123" t="n">
-        <v>98566</v>
+        <v>109444</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>736335</v>
+        <v>736248</v>
       </c>
       <c r="R123" t="n">
-        <v>6411533</v>
+        <v>6411616</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14324,6 +14315,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14355,57 +14351,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203216</v>
+        <v>128203091</v>
       </c>
       <c r="B124" t="n">
-        <v>98566</v>
+        <v>109444</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736297</v>
+        <v>736520</v>
       </c>
       <c r="R124" t="n">
-        <v>6411559</v>
+        <v>6411544</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14435,11 +14422,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14471,10 +14453,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203092</v>
+        <v>128203190</v>
       </c>
       <c r="B125" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14501,7 +14483,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14515,13 +14497,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736520</v>
+        <v>736335</v>
       </c>
       <c r="R125" t="n">
-        <v>6411544</v>
+        <v>6411533</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14582,10 +14564,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203235</v>
+        <v>128203216</v>
       </c>
       <c r="B126" t="n">
-        <v>110493</v>
+        <v>98569</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14593,34 +14575,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736279</v>
+        <v>736297</v>
       </c>
       <c r="R126" t="n">
-        <v>6411517</v>
+        <v>6411559</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14653,6 +14644,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14684,45 +14680,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203151</v>
+        <v>128203092</v>
       </c>
       <c r="B127" t="n">
-        <v>109435</v>
+        <v>98569</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736248</v>
+        <v>736520</v>
       </c>
       <c r="R127" t="n">
-        <v>6411616</v>
+        <v>6411544</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14755,11 +14760,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14791,27 +14791,27 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203091</v>
+        <v>128203235</v>
       </c>
       <c r="B128" t="n">
-        <v>109435</v>
+        <v>110502</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220299</v>
+        <v>219677</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -14826,13 +14826,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736520</v>
+        <v>736279</v>
       </c>
       <c r="R128" t="n">
-        <v>6411544</v>
+        <v>6411517</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203112</v>
+        <v>128203093</v>
       </c>
       <c r="B129" t="n">
-        <v>98573</v>
+        <v>109444</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736184</v>
+        <v>736498</v>
       </c>
       <c r="R129" t="n">
-        <v>6411805</v>
+        <v>6411566</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,11 +14966,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14982,7 +14977,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15000,10 +14995,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203113</v>
+        <v>128203178</v>
       </c>
       <c r="B130" t="n">
-        <v>98590</v>
+        <v>98116</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15011,21 +15006,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219811</v>
+        <v>221930</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15035,10 +15030,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>736184</v>
+        <v>736300</v>
       </c>
       <c r="R130" t="n">
-        <v>6411805</v>
+        <v>6411481</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15075,7 +15070,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15089,7 +15084,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15107,10 +15102,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203252</v>
+        <v>128203112</v>
       </c>
       <c r="B131" t="n">
-        <v>98610</v>
+        <v>98576</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15118,46 +15113,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219862</v>
+        <v>219799</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>736193</v>
+        <v>736184</v>
       </c>
       <c r="R131" t="n">
-        <v>6411456</v>
+        <v>6411805</v>
       </c>
       <c r="S131" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15189,6 +15175,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15200,7 +15191,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15218,10 +15209,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203178</v>
+        <v>128203113</v>
       </c>
       <c r="B132" t="n">
-        <v>98114</v>
+        <v>98593</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15229,21 +15220,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221930</v>
+        <v>219811</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15253,10 +15244,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736300</v>
+        <v>736184</v>
       </c>
       <c r="R132" t="n">
-        <v>6411481</v>
+        <v>6411805</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15293,7 +15284,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15307,7 +15298,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15325,48 +15316,57 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203093</v>
+        <v>128203252</v>
       </c>
       <c r="B133" t="n">
-        <v>109435</v>
+        <v>98613</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736498</v>
+        <v>736193</v>
       </c>
       <c r="R133" t="n">
-        <v>6411566</v>
+        <v>6411456</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203139</v>
+        <v>128203228</v>
       </c>
       <c r="B134" t="n">
-        <v>98592</v>
+        <v>98576</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15438,26 +15438,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736244</v>
+        <v>736263</v>
       </c>
       <c r="R134" t="n">
-        <v>6411666</v>
+        <v>6411533</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,10 +15538,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203228</v>
+        <v>128203127</v>
       </c>
       <c r="B135" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15582,10 +15582,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736263</v>
+        <v>736239</v>
       </c>
       <c r="R135" t="n">
-        <v>6411533</v>
+        <v>6411738</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15649,57 +15649,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203127</v>
+        <v>128203083</v>
       </c>
       <c r="B136" t="n">
-        <v>98573</v>
+        <v>109444</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736239</v>
+        <v>736442</v>
       </c>
       <c r="R136" t="n">
-        <v>6411738</v>
+        <v>6411479</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15742,7 +15733,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15760,10 +15751,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203083</v>
+        <v>128203164</v>
       </c>
       <c r="B137" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15795,10 +15786,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736442</v>
+        <v>736260</v>
       </c>
       <c r="R137" t="n">
-        <v>6411479</v>
+        <v>6411450</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15862,48 +15853,57 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203164</v>
+        <v>128203139</v>
       </c>
       <c r="B138" t="n">
-        <v>109435</v>
+        <v>98595</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220299</v>
+        <v>741</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Wahlenb.) K. Richt.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736260</v>
+        <v>736244</v>
       </c>
       <c r="R138" t="n">
-        <v>6411450</v>
+        <v>6411666</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15967,7 +15967,7 @@
         <v>128203085</v>
       </c>
       <c r="B139" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>128203240</v>
       </c>
       <c r="B140" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>128203084</v>
       </c>
       <c r="B141" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>128203223</v>
       </c>
       <c r="B142" t="n">
-        <v>98496</v>
+        <v>98499</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>128203231</v>
       </c>
       <c r="B143" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -7499,27 +7499,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203237</v>
+        <v>128203144</v>
       </c>
       <c r="B61" t="n">
-        <v>110502</v>
+        <v>109444</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7527,17 +7527,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736283</v>
+        <v>736246</v>
       </c>
       <c r="R61" t="n">
-        <v>6411500</v>
+        <v>6411634</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7574,7 +7583,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Överallt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7606,10 +7615,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203233</v>
+        <v>128203237</v>
       </c>
       <c r="B62" t="n">
-        <v>98576</v>
+        <v>110502</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,46 +7626,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219799</v>
+        <v>219677</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736276</v>
+        <v>736283</v>
       </c>
       <c r="R62" t="n">
-        <v>6411531</v>
+        <v>6411500</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7688,6 +7688,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7699,7 +7704,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7717,10 +7722,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203186</v>
+        <v>128203233</v>
       </c>
       <c r="B63" t="n">
-        <v>98613</v>
+        <v>98576</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,26 +7733,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219862</v>
+        <v>219799</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7761,10 +7766,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736331</v>
+        <v>736276</v>
       </c>
       <c r="R63" t="n">
-        <v>6411530</v>
+        <v>6411531</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7810,7 +7815,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7828,38 +7833,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203021</v>
+        <v>128203186</v>
       </c>
       <c r="B64" t="n">
-        <v>57686</v>
+        <v>98613</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7868,10 +7877,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736197</v>
+        <v>736331</v>
       </c>
       <c r="R64" t="n">
-        <v>6411554</v>
+        <v>6411530</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7935,10 +7944,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203144</v>
+        <v>128203021</v>
       </c>
       <c r="B65" t="n">
-        <v>109444</v>
+        <v>57686</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7946,31 +7955,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7979,13 +7984,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736246</v>
+        <v>736197</v>
       </c>
       <c r="R65" t="n">
-        <v>6411634</v>
+        <v>6411554</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8015,11 +8020,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9132,48 +9132,57 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203199</v>
+        <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>98576</v>
+        <v>98597</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219799</v>
+        <v>742</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736314</v>
+        <v>736184</v>
       </c>
       <c r="R76" t="n">
-        <v>6411572</v>
+        <v>6411805</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9207,7 +9216,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9221,7 +9230,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9239,57 +9248,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203086</v>
+        <v>128203189</v>
       </c>
       <c r="B77" t="n">
-        <v>98569</v>
+        <v>109444</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736450</v>
+        <v>736335</v>
       </c>
       <c r="R77" t="n">
-        <v>6411486</v>
+        <v>6411533</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9350,54 +9350,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203221</v>
+        <v>128203185</v>
       </c>
       <c r="B78" t="n">
-        <v>98593</v>
+        <v>109444</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736272</v>
+        <v>736331</v>
       </c>
       <c r="R78" t="n">
-        <v>6411546</v>
+        <v>6411530</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9432,6 +9423,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9443,7 +9439,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9461,10 +9457,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203114</v>
+        <v>128203099</v>
       </c>
       <c r="B79" t="n">
-        <v>98597</v>
+        <v>109444</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9472,31 +9468,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>742</v>
+        <v>220299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9505,13 +9501,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736184</v>
+        <v>736361</v>
       </c>
       <c r="R79" t="n">
-        <v>6411805</v>
+        <v>6411697</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9543,11 +9539,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9559,7 +9550,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9577,54 +9568,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203023</v>
+        <v>128203199</v>
       </c>
       <c r="B80" t="n">
-        <v>57686</v>
+        <v>98576</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>219799</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736365</v>
+        <v>736314</v>
       </c>
       <c r="R80" t="n">
-        <v>6411573</v>
+        <v>6411572</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9659,6 +9641,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9670,7 +9657,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9688,48 +9675,57 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203189</v>
+        <v>128203086</v>
       </c>
       <c r="B81" t="n">
-        <v>109444</v>
+        <v>98569</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736335</v>
+        <v>736450</v>
       </c>
       <c r="R81" t="n">
-        <v>6411533</v>
+        <v>6411486</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9790,45 +9786,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203185</v>
+        <v>128203221</v>
       </c>
       <c r="B82" t="n">
-        <v>109444</v>
+        <v>98593</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736331</v>
+        <v>736272</v>
       </c>
       <c r="R82" t="n">
-        <v>6411530</v>
+        <v>6411546</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9863,11 +9868,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,10 +9897,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203099</v>
+        <v>128203023</v>
       </c>
       <c r="B83" t="n">
-        <v>109444</v>
+        <v>57686</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9908,31 +9908,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736361</v>
+        <v>736365</v>
       </c>
       <c r="R83" t="n">
-        <v>6411697</v>
+        <v>6411573</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203165</v>
+        <v>128205915</v>
       </c>
       <c r="B89" t="n">
-        <v>98569</v>
+        <v>57686</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736260</v>
+        <v>736315</v>
       </c>
       <c r="R89" t="n">
-        <v>6411450</v>
+        <v>6411597</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203081</v>
+        <v>128203156</v>
       </c>
       <c r="B90" t="n">
-        <v>98569</v>
+        <v>98509</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10695,26 +10695,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736347</v>
+        <v>736221</v>
       </c>
       <c r="R90" t="n">
-        <v>6411466</v>
+        <v>6411593</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,10 +10795,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203225</v>
+        <v>128203165</v>
       </c>
       <c r="B91" t="n">
-        <v>98593</v>
+        <v>98569</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,26 +10806,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10839,13 +10839,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736263</v>
+        <v>736260</v>
       </c>
       <c r="R91" t="n">
-        <v>6411533</v>
+        <v>6411450</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203197</v>
+        <v>128203081</v>
       </c>
       <c r="B92" t="n">
-        <v>98593</v>
+        <v>98569</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10917,37 +10917,46 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736314</v>
+        <v>736347</v>
       </c>
       <c r="R92" t="n">
-        <v>6411572</v>
+        <v>6411466</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10979,11 +10988,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10995,7 +10999,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11013,48 +11017,57 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203180</v>
+        <v>128203225</v>
       </c>
       <c r="B93" t="n">
-        <v>105549</v>
+        <v>98593</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736300</v>
+        <v>736263</v>
       </c>
       <c r="R93" t="n">
-        <v>6411481</v>
+        <v>6411533</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11086,11 +11099,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -11102,7 +11110,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11120,32 +11128,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203211</v>
+        <v>128203197</v>
       </c>
       <c r="B94" t="n">
-        <v>99268</v>
+        <v>98593</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11155,13 +11163,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736301</v>
+        <v>736314</v>
       </c>
       <c r="R94" t="n">
-        <v>6411564</v>
+        <v>6411572</v>
       </c>
       <c r="S94" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11191,6 +11199,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11222,54 +11235,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203156</v>
+        <v>128203180</v>
       </c>
       <c r="B95" t="n">
-        <v>98509</v>
+        <v>105549</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>223591</v>
+        <v>221137</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736221</v>
+        <v>736300</v>
       </c>
       <c r="R95" t="n">
-        <v>6411593</v>
+        <v>6411481</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11304,6 +11308,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11315,7 +11324,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11333,10 +11342,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128205915</v>
+        <v>128203211</v>
       </c>
       <c r="B96" t="n">
-        <v>57686</v>
+        <v>99268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11344,46 +11353,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>222322</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736315</v>
+        <v>736301</v>
       </c>
       <c r="R96" t="n">
-        <v>6411597</v>
+        <v>6411564</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11444,32 +11444,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203106</v>
+        <v>128203087</v>
       </c>
       <c r="B97" t="n">
-        <v>98593</v>
+        <v>109444</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736305</v>
+        <v>736474</v>
       </c>
       <c r="R97" t="n">
-        <v>6411739</v>
+        <v>6411506</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11517,11 +11517,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11533,7 +11528,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11551,57 +11546,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203167</v>
+        <v>128203246</v>
       </c>
       <c r="B98" t="n">
-        <v>98569</v>
+        <v>109444</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736275</v>
+        <v>736213</v>
       </c>
       <c r="R98" t="n">
-        <v>6411455</v>
+        <v>6411456</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11631,6 +11617,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11662,7 +11653,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203087</v>
+        <v>128203080</v>
       </c>
       <c r="B99" t="n">
         <v>109444</v>
@@ -11697,10 +11688,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736474</v>
+        <v>736347</v>
       </c>
       <c r="R99" t="n">
-        <v>6411506</v>
+        <v>6411466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11764,32 +11755,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203246</v>
+        <v>128203106</v>
       </c>
       <c r="B100" t="n">
-        <v>109444</v>
+        <v>98593</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11799,13 +11790,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736213</v>
+        <v>736305</v>
       </c>
       <c r="R100" t="n">
-        <v>6411456</v>
+        <v>6411739</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11839,7 +11830,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11853,7 +11844,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11871,45 +11862,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203080</v>
+        <v>128203167</v>
       </c>
       <c r="B101" t="n">
-        <v>109444</v>
+        <v>98569</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736347</v>
+        <v>736275</v>
       </c>
       <c r="R101" t="n">
-        <v>6411466</v>
+        <v>6411455</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13808,57 +13808,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128203101</v>
+        <v>128203159</v>
       </c>
       <c r="B119" t="n">
-        <v>98499</v>
+        <v>109444</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>736358</v>
+        <v>736240</v>
       </c>
       <c r="R119" t="n">
-        <v>6411725</v>
+        <v>6411466</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13890,6 +13881,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13901,7 +13897,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13919,48 +13915,57 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128203159</v>
+        <v>128203101</v>
       </c>
       <c r="B120" t="n">
-        <v>109444</v>
+        <v>98499</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>736240</v>
+        <v>736358</v>
       </c>
       <c r="R120" t="n">
-        <v>6411466</v>
+        <v>6411725</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13992,11 +13997,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203228</v>
+        <v>128203139</v>
       </c>
       <c r="B134" t="n">
-        <v>98576</v>
+        <v>98595</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15438,26 +15438,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219799</v>
+        <v>741</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736263</v>
+        <v>736244</v>
       </c>
       <c r="R134" t="n">
-        <v>6411533</v>
+        <v>6411666</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,57 +15538,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203127</v>
+        <v>128203083</v>
       </c>
       <c r="B135" t="n">
-        <v>98576</v>
+        <v>109444</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736239</v>
+        <v>736442</v>
       </c>
       <c r="R135" t="n">
-        <v>6411738</v>
+        <v>6411479</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15631,7 +15622,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15649,7 +15640,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203083</v>
+        <v>128203164</v>
       </c>
       <c r="B136" t="n">
         <v>109444</v>
@@ -15684,10 +15675,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736442</v>
+        <v>736260</v>
       </c>
       <c r="R136" t="n">
-        <v>6411479</v>
+        <v>6411450</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15751,48 +15742,57 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203164</v>
+        <v>128203228</v>
       </c>
       <c r="B137" t="n">
-        <v>109444</v>
+        <v>98576</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736260</v>
+        <v>736263</v>
       </c>
       <c r="R137" t="n">
-        <v>6411450</v>
+        <v>6411533</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203139</v>
+        <v>128203127</v>
       </c>
       <c r="B138" t="n">
-        <v>98595</v>
+        <v>98576</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15864,26 +15864,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15897,13 +15897,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736244</v>
+        <v>736239</v>
       </c>
       <c r="R138" t="n">
-        <v>6411666</v>
+        <v>6411738</v>
       </c>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6403,7 +6403,7 @@
         <v>128203088</v>
       </c>
       <c r="B51" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>128203259</v>
       </c>
       <c r="B52" t="n">
-        <v>110502</v>
+        <v>110507</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>128203131</v>
       </c>
       <c r="B53" t="n">
-        <v>105549</v>
+        <v>105552</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6729,27 +6729,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203256</v>
+        <v>128203179</v>
       </c>
       <c r="B54" t="n">
-        <v>109444</v>
+        <v>99635</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736176</v>
+        <v>736300</v>
       </c>
       <c r="R54" t="n">
-        <v>6411455</v>
+        <v>6411481</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203241</v>
+        <v>128203256</v>
       </c>
       <c r="B55" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736223</v>
+        <v>736176</v>
       </c>
       <c r="R55" t="n">
-        <v>6411512</v>
+        <v>6411455</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6902,11 +6902,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6938,57 +6933,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203195</v>
+        <v>128203241</v>
       </c>
       <c r="B56" t="n">
-        <v>98499</v>
+        <v>109449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736314</v>
+        <v>736223</v>
       </c>
       <c r="R56" t="n">
-        <v>6411572</v>
+        <v>6411512</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7022,7 +7008,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7036,7 +7022,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7054,10 +7040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203096</v>
+        <v>128203195</v>
       </c>
       <c r="B57" t="n">
-        <v>98569</v>
+        <v>98500</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7065,26 +7051,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7098,13 +7084,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736474</v>
+        <v>736314</v>
       </c>
       <c r="R57" t="n">
-        <v>6411596</v>
+        <v>6411572</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7138,7 +7124,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7152,7 +7138,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7170,10 +7156,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203100</v>
+        <v>128203096</v>
       </c>
       <c r="B58" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7200,7 +7186,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7214,10 +7200,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736361</v>
+        <v>736474</v>
       </c>
       <c r="R58" t="n">
-        <v>6411697</v>
+        <v>6411596</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7250,6 +7236,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7281,10 +7272,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203179</v>
+        <v>128203100</v>
       </c>
       <c r="B59" t="n">
-        <v>99634</v>
+        <v>98570</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7292,34 +7283,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222662</v>
+        <v>219798</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736300</v>
+        <v>736361</v>
       </c>
       <c r="R59" t="n">
-        <v>6411481</v>
+        <v>6411697</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7386,7 +7386,7 @@
         <v>128203220</v>
       </c>
       <c r="B60" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>128203144</v>
       </c>
       <c r="B61" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>128203237</v>
       </c>
       <c r="B62" t="n">
-        <v>110502</v>
+        <v>110507</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>128203233</v>
       </c>
       <c r="B63" t="n">
-        <v>98576</v>
+        <v>98577</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>128203186</v>
       </c>
       <c r="B64" t="n">
-        <v>98613</v>
+        <v>98614</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>128203243</v>
       </c>
       <c r="B66" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>128203089</v>
       </c>
       <c r="B67" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203239</v>
+        <v>128203104</v>
       </c>
       <c r="B68" t="n">
-        <v>109444</v>
+        <v>105552</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8275,16 +8275,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8299,13 +8299,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736283</v>
+        <v>736325</v>
       </c>
       <c r="R68" t="n">
-        <v>6411500</v>
+        <v>6411730</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203095</v>
+        <v>128203239</v>
       </c>
       <c r="B69" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8406,13 +8406,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736474</v>
+        <v>736283</v>
       </c>
       <c r="R69" t="n">
-        <v>6411596</v>
+        <v>6411500</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8478,57 +8478,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203209</v>
+        <v>128203095</v>
       </c>
       <c r="B70" t="n">
-        <v>98593</v>
+        <v>109449</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736295</v>
+        <v>736474</v>
       </c>
       <c r="R70" t="n">
-        <v>6411567</v>
+        <v>6411596</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8560,6 +8551,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8567,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8589,48 +8585,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203104</v>
+        <v>128203209</v>
       </c>
       <c r="B71" t="n">
-        <v>105549</v>
+        <v>98594</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736325</v>
+        <v>736295</v>
       </c>
       <c r="R71" t="n">
-        <v>6411730</v>
+        <v>6411567</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8662,11 +8667,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Spridd. Flera i blom.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8699,7 +8699,7 @@
         <v>128203181</v>
       </c>
       <c r="B72" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>128203166</v>
       </c>
       <c r="B73" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>128203182</v>
       </c>
       <c r="B74" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>128203187</v>
       </c>
       <c r="B75" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>98597</v>
+        <v>98598</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9248,10 +9248,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203189</v>
+        <v>128203023</v>
       </c>
       <c r="B77" t="n">
-        <v>109444</v>
+        <v>57686</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,37 +9259,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736335</v>
+        <v>736365</v>
       </c>
       <c r="R77" t="n">
-        <v>6411533</v>
+        <v>6411573</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9350,10 +9359,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203185</v>
+        <v>128203189</v>
       </c>
       <c r="B78" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9385,10 +9394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736331</v>
+        <v>736335</v>
       </c>
       <c r="R78" t="n">
-        <v>6411530</v>
+        <v>6411533</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9421,11 +9430,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9457,10 +9461,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203099</v>
+        <v>128203185</v>
       </c>
       <c r="B79" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9485,29 +9489,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736361</v>
+        <v>736331</v>
       </c>
       <c r="R79" t="n">
-        <v>6411697</v>
+        <v>6411530</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9537,6 +9532,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9568,48 +9568,57 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203199</v>
+        <v>128203099</v>
       </c>
       <c r="B80" t="n">
-        <v>98576</v>
+        <v>109449</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736314</v>
+        <v>736361</v>
       </c>
       <c r="R80" t="n">
-        <v>6411572</v>
+        <v>6411697</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9641,11 +9650,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9657,7 +9661,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9675,10 +9679,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203086</v>
+        <v>128203199</v>
       </c>
       <c r="B81" t="n">
-        <v>98569</v>
+        <v>98577</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9686,16 +9690,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9703,29 +9707,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736450</v>
+        <v>736314</v>
       </c>
       <c r="R81" t="n">
-        <v>6411486</v>
+        <v>6411572</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9757,6 +9752,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9786,10 +9786,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203221</v>
+        <v>128203086</v>
       </c>
       <c r="B82" t="n">
-        <v>98593</v>
+        <v>98570</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9797,26 +9797,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9830,13 +9830,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736272</v>
+        <v>736450</v>
       </c>
       <c r="R82" t="n">
-        <v>6411546</v>
+        <v>6411486</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,32 +9897,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203023</v>
+        <v>128203221</v>
       </c>
       <c r="B83" t="n">
-        <v>57686</v>
+        <v>98594</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>219811</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9930,9 +9930,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736365</v>
+        <v>736272</v>
       </c>
       <c r="R83" t="n">
-        <v>6411573</v>
+        <v>6411546</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10011,7 +10011,7 @@
         <v>128203192</v>
       </c>
       <c r="B84" t="n">
-        <v>105549</v>
+        <v>105552</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>128203132</v>
       </c>
       <c r="B85" t="n">
-        <v>107500</v>
+        <v>107505</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>128203249</v>
       </c>
       <c r="B86" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>128203162</v>
       </c>
       <c r="B87" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>128203111</v>
       </c>
       <c r="B88" t="n">
-        <v>98522</v>
+        <v>98523</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B89" t="n">
-        <v>57686</v>
+        <v>98570</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R89" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,10 +10684,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203156</v>
+        <v>128203081</v>
       </c>
       <c r="B90" t="n">
-        <v>98509</v>
+        <v>98570</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10695,26 +10695,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736221</v>
+        <v>736347</v>
       </c>
       <c r="R90" t="n">
-        <v>6411593</v>
+        <v>6411466</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,10 +10795,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203165</v>
+        <v>128203225</v>
       </c>
       <c r="B91" t="n">
-        <v>98569</v>
+        <v>98594</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,26 +10806,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10839,13 +10839,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736260</v>
+        <v>736263</v>
       </c>
       <c r="R91" t="n">
-        <v>6411450</v>
+        <v>6411533</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203081</v>
+        <v>128203197</v>
       </c>
       <c r="B92" t="n">
-        <v>98569</v>
+        <v>98594</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10917,46 +10917,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736347</v>
+        <v>736314</v>
       </c>
       <c r="R92" t="n">
-        <v>6411466</v>
+        <v>6411572</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10988,6 +10979,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10999,7 +10995,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11017,57 +11013,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203225</v>
+        <v>128203211</v>
       </c>
       <c r="B93" t="n">
-        <v>98593</v>
+        <v>99269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219811</v>
+        <v>222322</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736263</v>
+        <v>736301</v>
       </c>
       <c r="R93" t="n">
-        <v>6411533</v>
+        <v>6411564</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11110,7 +11097,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11128,10 +11115,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203197</v>
+        <v>128203156</v>
       </c>
       <c r="B94" t="n">
-        <v>98593</v>
+        <v>98510</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11139,37 +11126,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736314</v>
+        <v>736221</v>
       </c>
       <c r="R94" t="n">
-        <v>6411572</v>
+        <v>6411593</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11201,11 +11197,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11217,7 +11208,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11238,7 +11229,7 @@
         <v>128203180</v>
       </c>
       <c r="B95" t="n">
-        <v>105549</v>
+        <v>105552</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11342,10 +11333,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203211</v>
+        <v>128205915</v>
       </c>
       <c r="B96" t="n">
-        <v>99268</v>
+        <v>57686</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11353,37 +11344,46 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736301</v>
+        <v>736315</v>
       </c>
       <c r="R96" t="n">
-        <v>6411564</v>
+        <v>6411597</v>
       </c>
       <c r="S96" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11444,32 +11444,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128203087</v>
+        <v>128203106</v>
       </c>
       <c r="B97" t="n">
-        <v>109444</v>
+        <v>98594</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11479,10 +11479,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>736474</v>
+        <v>736305</v>
       </c>
       <c r="R97" t="n">
-        <v>6411506</v>
+        <v>6411739</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11517,6 +11517,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11528,7 +11533,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11546,48 +11551,57 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128203246</v>
+        <v>128203167</v>
       </c>
       <c r="B98" t="n">
-        <v>109444</v>
+        <v>98570</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>736213</v>
+        <v>736275</v>
       </c>
       <c r="R98" t="n">
-        <v>6411456</v>
+        <v>6411455</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11617,11 +11631,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11653,10 +11662,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203080</v>
+        <v>128203087</v>
       </c>
       <c r="B99" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11688,10 +11697,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736347</v>
+        <v>736474</v>
       </c>
       <c r="R99" t="n">
-        <v>6411466</v>
+        <v>6411506</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11755,32 +11764,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203106</v>
+        <v>128203246</v>
       </c>
       <c r="B100" t="n">
-        <v>98593</v>
+        <v>109449</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11790,13 +11799,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736305</v>
+        <v>736213</v>
       </c>
       <c r="R100" t="n">
-        <v>6411739</v>
+        <v>6411456</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11830,7 +11839,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11844,7 +11853,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11862,54 +11871,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203167</v>
+        <v>128203080</v>
       </c>
       <c r="B101" t="n">
-        <v>98569</v>
+        <v>109449</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736275</v>
+        <v>736347</v>
       </c>
       <c r="R101" t="n">
-        <v>6411455</v>
+        <v>6411466</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11973,54 +11973,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203154</v>
+        <v>128203129</v>
       </c>
       <c r="B102" t="n">
-        <v>98499</v>
+        <v>105552</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219788</v>
+        <v>221137</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R102" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12066,7 +12057,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12084,10 +12075,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203126</v>
+        <v>128203154</v>
       </c>
       <c r="B103" t="n">
-        <v>98593</v>
+        <v>98500</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12095,26 +12086,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219811</v>
+        <v>219788</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12128,13 +12119,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R103" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12177,7 +12168,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12195,35 +12186,44 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203129</v>
+        <v>128203126</v>
       </c>
       <c r="B104" t="n">
-        <v>105549</v>
+        <v>98594</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221137</v>
+        <v>219811</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>128203242</v>
       </c>
       <c r="B105" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>128203255</v>
       </c>
       <c r="B106" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>128203207</v>
       </c>
       <c r="B107" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>128203177</v>
       </c>
       <c r="B108" t="n">
-        <v>98576</v>
+        <v>98577</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>128203234</v>
       </c>
       <c r="B109" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>128203107</v>
       </c>
       <c r="B110" t="n">
-        <v>105549</v>
+        <v>105552</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>128203161</v>
       </c>
       <c r="B111" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>128203236</v>
       </c>
       <c r="B112" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>128203160</v>
       </c>
       <c r="B113" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>128203138</v>
       </c>
       <c r="B114" t="n">
-        <v>98576</v>
+        <v>98577</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>128203094</v>
       </c>
       <c r="B115" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>128203134</v>
       </c>
       <c r="B116" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>128203247</v>
       </c>
       <c r="B117" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>128203215</v>
       </c>
       <c r="B118" t="n">
-        <v>98576</v>
+        <v>98577</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>128203159</v>
       </c>
       <c r="B119" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>128203101</v>
       </c>
       <c r="B120" t="n">
-        <v>98499</v>
+        <v>98500</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14026,57 +14026,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128203213</v>
+        <v>128203230</v>
       </c>
       <c r="B121" t="n">
-        <v>98593</v>
+        <v>109449</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>736301</v>
+        <v>736270</v>
       </c>
       <c r="R121" t="n">
-        <v>6411564</v>
+        <v>6411530</v>
       </c>
       <c r="S121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14108,6 +14099,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14119,7 +14115,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14137,48 +14133,57 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128203230</v>
+        <v>128203213</v>
       </c>
       <c r="B122" t="n">
-        <v>109444</v>
+        <v>98594</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>736270</v>
+        <v>736301</v>
       </c>
       <c r="R122" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14210,11 +14215,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14247,7 +14247,7 @@
         <v>128203151</v>
       </c>
       <c r="B123" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>128203091</v>
       </c>
       <c r="B124" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>128203190</v>
       </c>
       <c r="B125" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>128203216</v>
       </c>
       <c r="B126" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>128203092</v>
       </c>
       <c r="B127" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>128203235</v>
       </c>
       <c r="B128" t="n">
-        <v>110502</v>
+        <v>110507</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203093</v>
+        <v>128203178</v>
       </c>
       <c r="B129" t="n">
-        <v>109444</v>
+        <v>98117</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>221930</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736498</v>
+        <v>736300</v>
       </c>
       <c r="R129" t="n">
-        <v>6411566</v>
+        <v>6411481</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,6 +14966,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14977,7 +14982,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -14995,32 +15000,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203178</v>
+        <v>128203093</v>
       </c>
       <c r="B130" t="n">
-        <v>98116</v>
+        <v>109449</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221930</v>
+        <v>220299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15030,10 +15035,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>736300</v>
+        <v>736498</v>
       </c>
       <c r="R130" t="n">
-        <v>6411481</v>
+        <v>6411566</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15068,11 +15073,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15105,7 +15105,7 @@
         <v>128203112</v>
       </c>
       <c r="B131" t="n">
-        <v>98576</v>
+        <v>98577</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>128203113</v>
       </c>
       <c r="B132" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>128203252</v>
       </c>
       <c r="B133" t="n">
-        <v>98613</v>
+        <v>98614</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>128203139</v>
       </c>
       <c r="B134" t="n">
-        <v>98595</v>
+        <v>98596</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>128203083</v>
       </c>
       <c r="B135" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>128203164</v>
       </c>
       <c r="B136" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>128203228</v>
       </c>
       <c r="B137" t="n">
-        <v>98576</v>
+        <v>98577</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>128203127</v>
       </c>
       <c r="B138" t="n">
-        <v>98576</v>
+        <v>98577</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>128203085</v>
       </c>
       <c r="B139" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>128203240</v>
       </c>
       <c r="B140" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>128203084</v>
       </c>
       <c r="B141" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>128203223</v>
       </c>
       <c r="B142" t="n">
-        <v>98499</v>
+        <v>98500</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>128203231</v>
       </c>
       <c r="B143" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203179</v>
+        <v>128203195</v>
       </c>
       <c r="B54" t="n">
-        <v>99635</v>
+        <v>98500</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,37 +6740,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736300</v>
+        <v>736314</v>
       </c>
       <c r="R54" t="n">
-        <v>6411481</v>
+        <v>6411572</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6802,6 +6811,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6813,7 +6827,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6831,45 +6845,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203256</v>
+        <v>128203096</v>
       </c>
       <c r="B55" t="n">
-        <v>109449</v>
+        <v>98570</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R55" t="n">
-        <v>6411455</v>
+        <v>6411596</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6902,6 +6925,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6933,45 +6961,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203241</v>
+        <v>128203100</v>
       </c>
       <c r="B56" t="n">
-        <v>109449</v>
+        <v>98570</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736223</v>
+        <v>736361</v>
       </c>
       <c r="R56" t="n">
-        <v>6411512</v>
+        <v>6411697</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7004,11 +7041,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7040,57 +7072,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203195</v>
+        <v>128203256</v>
       </c>
       <c r="B57" t="n">
-        <v>98500</v>
+        <v>109449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736314</v>
+        <v>736176</v>
       </c>
       <c r="R57" t="n">
-        <v>6411572</v>
+        <v>6411455</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7122,11 +7145,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7138,7 +7156,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7156,54 +7174,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203096</v>
+        <v>128203241</v>
       </c>
       <c r="B58" t="n">
-        <v>98570</v>
+        <v>109449</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736474</v>
+        <v>736223</v>
       </c>
       <c r="R58" t="n">
-        <v>6411596</v>
+        <v>6411512</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7240,7 +7249,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7272,10 +7281,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203100</v>
+        <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>98570</v>
+        <v>99635</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7283,43 +7292,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219798</v>
+        <v>222662</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736361</v>
+        <v>736300</v>
       </c>
       <c r="R59" t="n">
-        <v>6411697</v>
+        <v>6411481</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203220</v>
+        <v>128203021</v>
       </c>
       <c r="B60" t="n">
-        <v>109449</v>
+        <v>57686</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,31 +7394,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7427,10 +7423,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736295</v>
+        <v>736197</v>
       </c>
       <c r="R60" t="n">
-        <v>6411551</v>
+        <v>6411554</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7463,11 +7459,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7499,7 +7490,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203144</v>
+        <v>128203220</v>
       </c>
       <c r="B61" t="n">
         <v>109449</v>
@@ -7529,7 +7520,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7543,13 +7534,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736246</v>
+        <v>736295</v>
       </c>
       <c r="R61" t="n">
-        <v>6411634</v>
+        <v>6411551</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7583,7 +7574,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7615,27 +7606,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203237</v>
+        <v>128203144</v>
       </c>
       <c r="B62" t="n">
-        <v>110507</v>
+        <v>109449</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7643,17 +7634,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736283</v>
+        <v>736246</v>
       </c>
       <c r="R62" t="n">
-        <v>6411500</v>
+        <v>6411634</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Överallt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7722,10 +7722,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203233</v>
+        <v>128203237</v>
       </c>
       <c r="B63" t="n">
-        <v>98577</v>
+        <v>110507</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7733,46 +7733,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219799</v>
+        <v>219677</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736276</v>
+        <v>736283</v>
       </c>
       <c r="R63" t="n">
-        <v>6411531</v>
+        <v>6411500</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7804,6 +7795,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7815,7 +7811,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7833,10 +7829,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203186</v>
+        <v>128203233</v>
       </c>
       <c r="B64" t="n">
-        <v>98614</v>
+        <v>98577</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7844,26 +7840,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219862</v>
+        <v>219799</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7877,10 +7873,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736331</v>
+        <v>736276</v>
       </c>
       <c r="R64" t="n">
-        <v>6411530</v>
+        <v>6411531</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7926,7 +7922,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7944,38 +7940,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203021</v>
+        <v>128203186</v>
       </c>
       <c r="B65" t="n">
-        <v>57686</v>
+        <v>98614</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736197</v>
+        <v>736331</v>
       </c>
       <c r="R65" t="n">
-        <v>6411554</v>
+        <v>6411530</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203104</v>
+        <v>128203239</v>
       </c>
       <c r="B68" t="n">
-        <v>105552</v>
+        <v>109449</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8275,16 +8275,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8299,13 +8299,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736325</v>
+        <v>736283</v>
       </c>
       <c r="R68" t="n">
-        <v>6411730</v>
+        <v>6411500</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Spridd. Flera i blom.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8371,7 +8371,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203239</v>
+        <v>128203095</v>
       </c>
       <c r="B69" t="n">
         <v>109449</v>
@@ -8406,13 +8406,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736283</v>
+        <v>736474</v>
       </c>
       <c r="R69" t="n">
-        <v>6411500</v>
+        <v>6411596</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8478,48 +8478,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203095</v>
+        <v>128203209</v>
       </c>
       <c r="B70" t="n">
-        <v>109449</v>
+        <v>98594</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736474</v>
+        <v>736295</v>
       </c>
       <c r="R70" t="n">
-        <v>6411596</v>
+        <v>6411567</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8551,11 +8560,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8567,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8585,57 +8589,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203209</v>
+        <v>128203104</v>
       </c>
       <c r="B71" t="n">
-        <v>98594</v>
+        <v>105552</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736295</v>
+        <v>736325</v>
       </c>
       <c r="R71" t="n">
-        <v>6411567</v>
+        <v>6411730</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8667,6 +8662,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Spridd. Flera i blom.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203165</v>
+        <v>128205915</v>
       </c>
       <c r="B89" t="n">
-        <v>98570</v>
+        <v>57686</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736260</v>
+        <v>736315</v>
       </c>
       <c r="R89" t="n">
-        <v>6411450</v>
+        <v>6411597</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,57 +10684,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203081</v>
+        <v>128203211</v>
       </c>
       <c r="B90" t="n">
-        <v>98570</v>
+        <v>99269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736347</v>
+        <v>736301</v>
       </c>
       <c r="R90" t="n">
-        <v>6411466</v>
+        <v>6411564</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10777,7 +10768,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,10 +10786,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203225</v>
+        <v>128203165</v>
       </c>
       <c r="B91" t="n">
-        <v>98594</v>
+        <v>98570</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,26 +10797,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10839,13 +10830,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736263</v>
+        <v>736260</v>
       </c>
       <c r="R91" t="n">
-        <v>6411533</v>
+        <v>6411450</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10888,7 +10879,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,10 +10897,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203197</v>
+        <v>128203081</v>
       </c>
       <c r="B92" t="n">
-        <v>98594</v>
+        <v>98570</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10917,37 +10908,46 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736314</v>
+        <v>736347</v>
       </c>
       <c r="R92" t="n">
-        <v>6411572</v>
+        <v>6411466</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10979,11 +10979,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10995,7 +10990,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11013,48 +11008,57 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203211</v>
+        <v>128203225</v>
       </c>
       <c r="B93" t="n">
-        <v>99269</v>
+        <v>98594</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222322</v>
+        <v>219811</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736301</v>
+        <v>736263</v>
       </c>
       <c r="R93" t="n">
-        <v>6411564</v>
+        <v>6411533</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11097,7 +11101,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11115,10 +11119,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203156</v>
+        <v>128203197</v>
       </c>
       <c r="B94" t="n">
-        <v>98510</v>
+        <v>98594</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11126,46 +11130,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736221</v>
+        <v>736314</v>
       </c>
       <c r="R94" t="n">
-        <v>6411593</v>
+        <v>6411572</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11197,6 +11192,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11226,45 +11226,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203180</v>
+        <v>128203156</v>
       </c>
       <c r="B95" t="n">
-        <v>105552</v>
+        <v>98510</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221137</v>
+        <v>223591</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736300</v>
+        <v>736221</v>
       </c>
       <c r="R95" t="n">
-        <v>6411481</v>
+        <v>6411593</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11299,11 +11308,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11315,7 +11319,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11333,10 +11337,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128205915</v>
+        <v>128203180</v>
       </c>
       <c r="B96" t="n">
-        <v>57686</v>
+        <v>105552</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11344,46 +11348,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>221137</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736315</v>
+        <v>736300</v>
       </c>
       <c r="R96" t="n">
-        <v>6411597</v>
+        <v>6411481</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11415,6 +11410,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203178</v>
+        <v>128203093</v>
       </c>
       <c r="B129" t="n">
-        <v>98117</v>
+        <v>109449</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221930</v>
+        <v>220299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736300</v>
+        <v>736498</v>
       </c>
       <c r="R129" t="n">
-        <v>6411481</v>
+        <v>6411566</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,11 +14966,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Rätt rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14982,7 +14977,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15000,32 +14995,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203093</v>
+        <v>128203112</v>
       </c>
       <c r="B130" t="n">
-        <v>109449</v>
+        <v>98577</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15035,10 +15030,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>736498</v>
+        <v>736184</v>
       </c>
       <c r="R130" t="n">
-        <v>6411566</v>
+        <v>6411805</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15073,6 +15068,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15102,10 +15102,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203112</v>
+        <v>128203113</v>
       </c>
       <c r="B131" t="n">
-        <v>98577</v>
+        <v>98594</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15113,21 +15113,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15209,10 +15209,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203113</v>
+        <v>128203252</v>
       </c>
       <c r="B132" t="n">
-        <v>98594</v>
+        <v>98614</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15220,37 +15220,46 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219811</v>
+        <v>219862</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736184</v>
+        <v>736193</v>
       </c>
       <c r="R132" t="n">
-        <v>6411805</v>
+        <v>6411456</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15282,11 +15291,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
@@ -15298,7 +15302,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15316,10 +15320,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128203252</v>
+        <v>128203178</v>
       </c>
       <c r="B133" t="n">
-        <v>98614</v>
+        <v>98117</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15327,46 +15331,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219862</v>
+        <v>221930</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Wahlenb.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>736193</v>
+        <v>736300</v>
       </c>
       <c r="R133" t="n">
-        <v>6411456</v>
+        <v>6411481</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15398,6 +15393,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15427,57 +15427,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203139</v>
+        <v>128203083</v>
       </c>
       <c r="B134" t="n">
-        <v>98596</v>
+        <v>109449</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>741</v>
+        <v>220299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736244</v>
+        <v>736442</v>
       </c>
       <c r="R134" t="n">
-        <v>6411666</v>
+        <v>6411479</v>
       </c>
       <c r="S134" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,7 +15529,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203083</v>
+        <v>128203164</v>
       </c>
       <c r="B135" t="n">
         <v>109449</v>
@@ -15573,10 +15564,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736442</v>
+        <v>736260</v>
       </c>
       <c r="R135" t="n">
-        <v>6411479</v>
+        <v>6411450</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15640,48 +15631,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203164</v>
+        <v>128203228</v>
       </c>
       <c r="B136" t="n">
-        <v>109449</v>
+        <v>98577</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736260</v>
+        <v>736263</v>
       </c>
       <c r="R136" t="n">
-        <v>6411450</v>
+        <v>6411533</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15742,7 +15742,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203228</v>
+        <v>128203127</v>
       </c>
       <c r="B137" t="n">
         <v>98577</v>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15786,10 +15786,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736263</v>
+        <v>736239</v>
       </c>
       <c r="R137" t="n">
-        <v>6411533</v>
+        <v>6411738</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203127</v>
+        <v>128203139</v>
       </c>
       <c r="B138" t="n">
-        <v>98577</v>
+        <v>98596</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15864,26 +15864,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>219799</v>
+        <v>741</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Wahlenb.) K. Richt.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15897,13 +15897,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736239</v>
+        <v>736244</v>
       </c>
       <c r="R138" t="n">
-        <v>6411738</v>
+        <v>6411666</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,10 +6400,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203088</v>
+        <v>128203259</v>
       </c>
       <c r="B51" t="n">
-        <v>98570</v>
+        <v>110535</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,43 +6411,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736474</v>
+        <v>736176</v>
       </c>
       <c r="R51" t="n">
-        <v>6411506</v>
+        <v>6411455</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6480,6 +6471,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6511,10 +6507,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203259</v>
+        <v>128203088</v>
       </c>
       <c r="B52" t="n">
-        <v>110507</v>
+        <v>98597</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6522,34 +6518,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R52" t="n">
-        <v>6411455</v>
+        <v>6411506</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6582,11 +6587,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6621,7 +6621,7 @@
         <v>128203131</v>
       </c>
       <c r="B53" t="n">
-        <v>105552</v>
+        <v>105580</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>128203195</v>
       </c>
       <c r="B54" t="n">
-        <v>98500</v>
+        <v>98527</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>128203096</v>
       </c>
       <c r="B55" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>128203100</v>
       </c>
       <c r="B56" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>128203256</v>
       </c>
       <c r="B57" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>128203241</v>
       </c>
       <c r="B58" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>128203179</v>
       </c>
       <c r="B59" t="n">
-        <v>99635</v>
+        <v>99662</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7383,53 +7383,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203021</v>
+        <v>128203237</v>
       </c>
       <c r="B60" t="n">
-        <v>57686</v>
+        <v>110535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736197</v>
+        <v>736283</v>
       </c>
       <c r="R60" t="n">
-        <v>6411554</v>
+        <v>6411500</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7459,6 +7454,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7490,10 +7490,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203220</v>
+        <v>128203021</v>
       </c>
       <c r="B61" t="n">
-        <v>109449</v>
+        <v>57713</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7501,31 +7501,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7534,10 +7530,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736295</v>
+        <v>736197</v>
       </c>
       <c r="R61" t="n">
-        <v>6411551</v>
+        <v>6411554</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7570,11 +7566,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7606,42 +7597,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203144</v>
+        <v>128203233</v>
       </c>
       <c r="B62" t="n">
-        <v>109449</v>
+        <v>98604</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7650,13 +7641,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736246</v>
+        <v>736276</v>
       </c>
       <c r="R62" t="n">
-        <v>6411634</v>
+        <v>6411531</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7688,11 +7679,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7704,7 +7690,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7722,10 +7708,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203237</v>
+        <v>128203186</v>
       </c>
       <c r="B63" t="n">
-        <v>110507</v>
+        <v>98641</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7733,37 +7719,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219677</v>
+        <v>219862</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736283</v>
+        <v>736331</v>
       </c>
       <c r="R63" t="n">
-        <v>6411500</v>
+        <v>6411530</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7793,11 +7788,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7829,42 +7819,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128203233</v>
+        <v>128203220</v>
       </c>
       <c r="B64" t="n">
-        <v>98577</v>
+        <v>109477</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7873,10 +7863,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>736276</v>
+        <v>736295</v>
       </c>
       <c r="R64" t="n">
-        <v>6411531</v>
+        <v>6411551</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7911,6 +7901,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7922,7 +7917,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7940,42 +7935,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128203186</v>
+        <v>128203144</v>
       </c>
       <c r="B65" t="n">
-        <v>98614</v>
+        <v>109477</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7984,13 +7979,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>736331</v>
+        <v>736246</v>
       </c>
       <c r="R65" t="n">
-        <v>6411530</v>
+        <v>6411634</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8020,6 +8015,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8051,45 +8051,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128203243</v>
+        <v>128203089</v>
       </c>
       <c r="B66" t="n">
-        <v>109449</v>
+        <v>98597</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>736237</v>
+        <v>736488</v>
       </c>
       <c r="R66" t="n">
-        <v>6411472</v>
+        <v>6411510</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8135,7 +8144,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8153,54 +8162,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128203089</v>
+        <v>128203243</v>
       </c>
       <c r="B67" t="n">
-        <v>98570</v>
+        <v>109477</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>736488</v>
+        <v>736237</v>
       </c>
       <c r="R67" t="n">
-        <v>6411510</v>
+        <v>6411472</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203239</v>
+        <v>128203095</v>
       </c>
       <c r="B68" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8299,13 +8299,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736283</v>
+        <v>736474</v>
       </c>
       <c r="R68" t="n">
-        <v>6411500</v>
+        <v>6411596</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt samt spridd.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8371,48 +8371,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203095</v>
+        <v>128203209</v>
       </c>
       <c r="B69" t="n">
-        <v>109449</v>
+        <v>98621</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736474</v>
+        <v>736295</v>
       </c>
       <c r="R69" t="n">
-        <v>6411596</v>
+        <v>6411567</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8444,11 +8453,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8460,7 +8464,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8478,57 +8482,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203209</v>
+        <v>128203104</v>
       </c>
       <c r="B70" t="n">
-        <v>98594</v>
+        <v>105580</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736295</v>
+        <v>736325</v>
       </c>
       <c r="R70" t="n">
-        <v>6411567</v>
+        <v>6411730</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8560,6 +8555,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Spridd. Flera i blom.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203104</v>
+        <v>128203239</v>
       </c>
       <c r="B71" t="n">
-        <v>105552</v>
+        <v>109477</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8600,16 +8600,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8624,13 +8624,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736325</v>
+        <v>736283</v>
       </c>
       <c r="R71" t="n">
-        <v>6411730</v>
+        <v>6411500</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Spridd. Flera i blom.</t>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8696,35 +8696,44 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128203181</v>
+        <v>128203182</v>
       </c>
       <c r="B72" t="n">
-        <v>109449</v>
+        <v>98597</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8771,7 +8780,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8803,48 +8812,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128203166</v>
+        <v>128203187</v>
       </c>
       <c r="B73" t="n">
-        <v>109449</v>
+        <v>98597</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>736275</v>
+        <v>736331</v>
       </c>
       <c r="R73" t="n">
-        <v>6411455</v>
+        <v>6411530</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8905,44 +8923,35 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203182</v>
+        <v>128203181</v>
       </c>
       <c r="B74" t="n">
-        <v>98570</v>
+        <v>109477</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -8989,7 +8998,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Stig över våtmark; avsnitslat.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9021,57 +9030,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128203187</v>
+        <v>128203166</v>
       </c>
       <c r="B75" t="n">
-        <v>98570</v>
+        <v>109477</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736331</v>
+        <v>736275</v>
       </c>
       <c r="R75" t="n">
-        <v>6411530</v>
+        <v>6411455</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203114</v>
+        <v>128203189</v>
       </c>
       <c r="B76" t="n">
-        <v>98598</v>
+        <v>109477</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,43 +9143,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>742</v>
+        <v>220299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736184</v>
+        <v>736335</v>
       </c>
       <c r="R76" t="n">
-        <v>6411805</v>
+        <v>6411533</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9214,11 +9205,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9230,7 +9216,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9248,10 +9234,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203023</v>
+        <v>128203185</v>
       </c>
       <c r="B77" t="n">
-        <v>57686</v>
+        <v>109477</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,46 +9245,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736365</v>
+        <v>736331</v>
       </c>
       <c r="R77" t="n">
-        <v>6411573</v>
+        <v>6411530</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9328,6 +9305,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9359,10 +9341,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203189</v>
+        <v>128203099</v>
       </c>
       <c r="B78" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9387,20 +9369,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736335</v>
+        <v>736361</v>
       </c>
       <c r="R78" t="n">
-        <v>6411533</v>
+        <v>6411697</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9461,32 +9452,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203185</v>
+        <v>128203199</v>
       </c>
       <c r="B79" t="n">
-        <v>109449</v>
+        <v>98604</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9496,13 +9487,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736331</v>
+        <v>736314</v>
       </c>
       <c r="R79" t="n">
-        <v>6411530</v>
+        <v>6411572</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9536,7 +9527,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9550,7 +9541,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9568,42 +9559,42 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203099</v>
+        <v>128203086</v>
       </c>
       <c r="B80" t="n">
-        <v>109449</v>
+        <v>98597</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9612,10 +9603,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736361</v>
+        <v>736450</v>
       </c>
       <c r="R80" t="n">
-        <v>6411697</v>
+        <v>6411486</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9679,10 +9670,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203199</v>
+        <v>128203221</v>
       </c>
       <c r="B81" t="n">
-        <v>98577</v>
+        <v>98621</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9690,37 +9681,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736314</v>
+        <v>736272</v>
       </c>
       <c r="R81" t="n">
-        <v>6411572</v>
+        <v>6411546</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9752,11 +9752,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9768,7 +9763,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9786,37 +9781,37 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203086</v>
+        <v>128203114</v>
       </c>
       <c r="B82" t="n">
-        <v>98570</v>
+        <v>98625</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219798</v>
+        <v>742</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9830,13 +9825,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736450</v>
+        <v>736184</v>
       </c>
       <c r="R82" t="n">
-        <v>6411486</v>
+        <v>6411805</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9868,6 +9863,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,32 +9897,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203221</v>
+        <v>128203023</v>
       </c>
       <c r="B83" t="n">
-        <v>98594</v>
+        <v>57713</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219811</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -9930,9 +9930,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736272</v>
+        <v>736365</v>
       </c>
       <c r="R83" t="n">
-        <v>6411546</v>
+        <v>6411573</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10008,10 +10008,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203192</v>
+        <v>128203132</v>
       </c>
       <c r="B84" t="n">
-        <v>105552</v>
+        <v>107533</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10019,26 +10019,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221137</v>
+        <v>220079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736339</v>
+        <v>736242</v>
       </c>
       <c r="R84" t="n">
-        <v>6411571</v>
+        <v>6411713</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10090,11 +10090,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10106,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10124,32 +10119,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203132</v>
+        <v>128203249</v>
       </c>
       <c r="B85" t="n">
-        <v>107505</v>
+        <v>98597</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10168,10 +10163,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736242</v>
+        <v>736192</v>
       </c>
       <c r="R85" t="n">
-        <v>6411713</v>
+        <v>6411467</v>
       </c>
       <c r="S85" t="n">
         <v>3</v>
@@ -10217,7 +10212,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10235,10 +10230,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203249</v>
+        <v>128203162</v>
       </c>
       <c r="B86" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10265,7 +10260,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10279,13 +10274,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736192</v>
+        <v>736250</v>
       </c>
       <c r="R86" t="n">
-        <v>6411467</v>
+        <v>6411464</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10346,10 +10341,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203162</v>
+        <v>128203111</v>
       </c>
       <c r="B87" t="n">
-        <v>98570</v>
+        <v>98550</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10357,26 +10352,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219798</v>
+        <v>219794</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10390,10 +10385,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736250</v>
+        <v>736184</v>
       </c>
       <c r="R87" t="n">
-        <v>6411464</v>
+        <v>6411805</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10428,6 +10423,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10457,32 +10457,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128203111</v>
+        <v>128203192</v>
       </c>
       <c r="B88" t="n">
-        <v>98523</v>
+        <v>105580</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219794</v>
+        <v>221137</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10501,13 +10501,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>736184</v>
+        <v>736339</v>
       </c>
       <c r="R88" t="n">
-        <v>6411805</v>
+        <v>6411571</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10573,42 +10573,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128205915</v>
+        <v>128203165</v>
       </c>
       <c r="B89" t="n">
-        <v>57686</v>
+        <v>98597</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10617,13 +10617,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736315</v>
+        <v>736260</v>
       </c>
       <c r="R89" t="n">
-        <v>6411597</v>
+        <v>6411450</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10684,48 +10684,57 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203211</v>
+        <v>128203081</v>
       </c>
       <c r="B90" t="n">
-        <v>99269</v>
+        <v>98597</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736301</v>
+        <v>736347</v>
       </c>
       <c r="R90" t="n">
-        <v>6411564</v>
+        <v>6411466</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10768,7 +10777,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10786,10 +10795,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203165</v>
+        <v>128203225</v>
       </c>
       <c r="B91" t="n">
-        <v>98570</v>
+        <v>98621</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10797,26 +10806,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10830,13 +10839,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736260</v>
+        <v>736263</v>
       </c>
       <c r="R91" t="n">
-        <v>6411450</v>
+        <v>6411533</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10879,7 +10888,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10897,10 +10906,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203081</v>
+        <v>128203197</v>
       </c>
       <c r="B92" t="n">
-        <v>98570</v>
+        <v>98621</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10908,46 +10917,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736347</v>
+        <v>736314</v>
       </c>
       <c r="R92" t="n">
-        <v>6411466</v>
+        <v>6411572</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10979,6 +10979,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10990,7 +10995,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11008,57 +11013,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203225</v>
+        <v>128203180</v>
       </c>
       <c r="B93" t="n">
-        <v>98594</v>
+        <v>105580</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736263</v>
+        <v>736300</v>
       </c>
       <c r="R93" t="n">
-        <v>6411533</v>
+        <v>6411481</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11090,6 +11086,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -11101,7 +11102,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11119,10 +11120,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203197</v>
+        <v>128203156</v>
       </c>
       <c r="B94" t="n">
-        <v>98594</v>
+        <v>98537</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11130,37 +11131,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736314</v>
+        <v>736221</v>
       </c>
       <c r="R94" t="n">
-        <v>6411572</v>
+        <v>6411593</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11192,11 +11202,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11208,7 +11213,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11226,42 +11231,42 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128203156</v>
+        <v>128205915</v>
       </c>
       <c r="B95" t="n">
-        <v>98510</v>
+        <v>57713</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11270,13 +11275,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736221</v>
+        <v>736315</v>
       </c>
       <c r="R95" t="n">
-        <v>6411593</v>
+        <v>6411597</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11319,7 +11324,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11337,10 +11342,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203180</v>
+        <v>128203211</v>
       </c>
       <c r="B96" t="n">
-        <v>105552</v>
+        <v>99296</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11348,21 +11353,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221137</v>
+        <v>222322</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11372,13 +11377,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736300</v>
+        <v>736301</v>
       </c>
       <c r="R96" t="n">
-        <v>6411481</v>
+        <v>6411564</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11410,11 +11415,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11447,7 +11447,7 @@
         <v>128203106</v>
       </c>
       <c r="B97" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>128203167</v>
       </c>
       <c r="B98" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>128203087</v>
       </c>
       <c r="B99" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>128203246</v>
       </c>
       <c r="B100" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>128203080</v>
       </c>
       <c r="B101" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11973,45 +11973,54 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128203129</v>
+        <v>128203154</v>
       </c>
       <c r="B102" t="n">
-        <v>105552</v>
+        <v>98527</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221137</v>
+        <v>219788</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>736239</v>
+        <v>736240</v>
       </c>
       <c r="R102" t="n">
-        <v>6411738</v>
+        <v>6411594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12057,7 +12066,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Våtmark med ag.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12075,10 +12084,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128203154</v>
+        <v>128203126</v>
       </c>
       <c r="B103" t="n">
-        <v>98500</v>
+        <v>98621</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12086,26 +12095,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219788</v>
+        <v>219811</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12119,13 +12128,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>736240</v>
+        <v>736239</v>
       </c>
       <c r="R103" t="n">
-        <v>6411594</v>
+        <v>6411738</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12168,7 +12177,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Våtmark med ag.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12186,44 +12195,35 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128203126</v>
+        <v>128203129</v>
       </c>
       <c r="B104" t="n">
-        <v>98594</v>
+        <v>105580</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>219811</v>
+        <v>221137</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
@@ -12236,7 +12236,7 @@
         <v>6411738</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12297,48 +12297,57 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128203242</v>
+        <v>128203207</v>
       </c>
       <c r="B105" t="n">
-        <v>109449</v>
+        <v>98621</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>736237</v>
+        <v>736300</v>
       </c>
       <c r="R105" t="n">
-        <v>6411484</v>
+        <v>6411576</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12370,11 +12379,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12386,7 +12390,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12404,32 +12408,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128203255</v>
+        <v>128203177</v>
       </c>
       <c r="B106" t="n">
-        <v>109449</v>
+        <v>98604</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12439,10 +12443,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>736200</v>
+        <v>736300</v>
       </c>
       <c r="R106" t="n">
-        <v>6411456</v>
+        <v>6411481</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12477,6 +12481,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12488,7 +12497,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12506,10 +12515,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128203207</v>
+        <v>128203234</v>
       </c>
       <c r="B107" t="n">
-        <v>98594</v>
+        <v>98597</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12517,26 +12526,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12550,10 +12559,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>736300</v>
+        <v>736279</v>
       </c>
       <c r="R107" t="n">
-        <v>6411576</v>
+        <v>6411517</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12599,7 +12608,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12617,32 +12626,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128203177</v>
+        <v>128203107</v>
       </c>
       <c r="B108" t="n">
-        <v>98577</v>
+        <v>105580</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219799</v>
+        <v>221137</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12652,10 +12661,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>736300</v>
+        <v>736305</v>
       </c>
       <c r="R108" t="n">
-        <v>6411481</v>
+        <v>6411739</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12692,7 +12701,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12706,7 +12715,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12724,57 +12733,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128203234</v>
+        <v>128203242</v>
       </c>
       <c r="B109" t="n">
-        <v>98570</v>
+        <v>109477</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>736279</v>
+        <v>736237</v>
       </c>
       <c r="R109" t="n">
-        <v>6411517</v>
+        <v>6411484</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12804,6 +12804,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12835,10 +12840,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128203107</v>
+        <v>128203255</v>
       </c>
       <c r="B110" t="n">
-        <v>105552</v>
+        <v>109477</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12846,16 +12851,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12870,10 +12875,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>736305</v>
+        <v>736200</v>
       </c>
       <c r="R110" t="n">
-        <v>6411739</v>
+        <v>6411456</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12908,11 +12913,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12945,7 +12945,7 @@
         <v>128203161</v>
       </c>
       <c r="B111" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>128203236</v>
       </c>
       <c r="B112" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>128203160</v>
       </c>
       <c r="B113" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>128203138</v>
       </c>
       <c r="B114" t="n">
-        <v>98577</v>
+        <v>98604</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>128203094</v>
       </c>
       <c r="B115" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13484,42 +13484,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128203134</v>
+        <v>128203215</v>
       </c>
       <c r="B116" t="n">
-        <v>109449</v>
+        <v>98604</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13528,13 +13528,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>736242</v>
+        <v>736301</v>
       </c>
       <c r="R116" t="n">
-        <v>6411713</v>
+        <v>6411564</v>
       </c>
       <c r="S116" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13595,10 +13595,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128203247</v>
+        <v>128203134</v>
       </c>
       <c r="B117" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13623,17 +13623,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>736192</v>
+        <v>736242</v>
       </c>
       <c r="R117" t="n">
-        <v>6411467</v>
+        <v>6411713</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -13679,7 +13688,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13697,57 +13706,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128203215</v>
+        <v>128203247</v>
       </c>
       <c r="B118" t="n">
-        <v>98577</v>
+        <v>109477</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>736301</v>
+        <v>736192</v>
       </c>
       <c r="R118" t="n">
-        <v>6411564</v>
+        <v>6411467</v>
       </c>
       <c r="S118" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13808,48 +13808,57 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128203159</v>
+        <v>128203101</v>
       </c>
       <c r="B119" t="n">
-        <v>109449</v>
+        <v>98527</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>736240</v>
+        <v>736358</v>
       </c>
       <c r="R119" t="n">
-        <v>6411466</v>
+        <v>6411725</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13881,11 +13890,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13897,7 +13901,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13915,57 +13919,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128203101</v>
+        <v>128203159</v>
       </c>
       <c r="B120" t="n">
-        <v>98500</v>
+        <v>109477</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>736358</v>
+        <v>736240</v>
       </c>
       <c r="R120" t="n">
-        <v>6411725</v>
+        <v>6411466</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13997,6 +13992,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14026,48 +14026,57 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128203230</v>
+        <v>128203213</v>
       </c>
       <c r="B121" t="n">
-        <v>109449</v>
+        <v>98621</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>736270</v>
+        <v>736301</v>
       </c>
       <c r="R121" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14099,11 +14108,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14115,7 +14119,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14133,57 +14137,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128203213</v>
+        <v>128203230</v>
       </c>
       <c r="B122" t="n">
-        <v>98594</v>
+        <v>109477</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>736301</v>
+        <v>736270</v>
       </c>
       <c r="R122" t="n">
-        <v>6411564</v>
+        <v>6411530</v>
       </c>
       <c r="S122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14215,6 +14210,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14247,7 +14247,7 @@
         <v>128203151</v>
       </c>
       <c r="B123" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>128203091</v>
       </c>
       <c r="B124" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14453,10 +14453,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203190</v>
+        <v>128203216</v>
       </c>
       <c r="B125" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14497,10 +14497,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736335</v>
+        <v>736297</v>
       </c>
       <c r="R125" t="n">
-        <v>6411533</v>
+        <v>6411559</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14533,6 +14533,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14564,10 +14569,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203216</v>
+        <v>128203092</v>
       </c>
       <c r="B126" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14594,7 +14599,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -14608,13 +14613,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736297</v>
+        <v>736520</v>
       </c>
       <c r="R126" t="n">
-        <v>6411559</v>
+        <v>6411544</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14644,11 +14649,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14680,10 +14680,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203092</v>
+        <v>128203235</v>
       </c>
       <c r="B127" t="n">
-        <v>98570</v>
+        <v>110535</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14691,46 +14691,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736520</v>
+        <v>736279</v>
       </c>
       <c r="R127" t="n">
-        <v>6411544</v>
+        <v>6411517</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14791,10 +14782,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203235</v>
+        <v>128203190</v>
       </c>
       <c r="B128" t="n">
-        <v>110507</v>
+        <v>98597</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14802,34 +14793,43 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736279</v>
+        <v>736335</v>
       </c>
       <c r="R128" t="n">
-        <v>6411517</v>
+        <v>6411533</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14893,32 +14893,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128203093</v>
+        <v>128203112</v>
       </c>
       <c r="B129" t="n">
-        <v>109449</v>
+        <v>98604</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14928,10 +14928,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>736498</v>
+        <v>736184</v>
       </c>
       <c r="R129" t="n">
-        <v>6411566</v>
+        <v>6411805</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14966,6 +14966,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -14977,7 +14982,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -14995,10 +15000,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128203112</v>
+        <v>128203113</v>
       </c>
       <c r="B130" t="n">
-        <v>98577</v>
+        <v>98621</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15006,21 +15011,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15102,10 +15107,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128203113</v>
+        <v>128203252</v>
       </c>
       <c r="B131" t="n">
-        <v>98594</v>
+        <v>98641</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15113,37 +15118,46 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219811</v>
+        <v>219862</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>736184</v>
+        <v>736193</v>
       </c>
       <c r="R131" t="n">
-        <v>6411805</v>
+        <v>6411456</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15175,11 +15189,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15191,7 +15200,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15209,57 +15218,48 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128203252</v>
+        <v>128203093</v>
       </c>
       <c r="B132" t="n">
-        <v>98614</v>
+        <v>109477</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>736193</v>
+        <v>736498</v>
       </c>
       <c r="R132" t="n">
-        <v>6411456</v>
+        <v>6411566</v>
       </c>
       <c r="S132" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>128203178</v>
       </c>
       <c r="B133" t="n">
-        <v>98117</v>
+        <v>98144</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15427,48 +15427,57 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203083</v>
+        <v>128203228</v>
       </c>
       <c r="B134" t="n">
-        <v>109449</v>
+        <v>98604</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736442</v>
+        <v>736263</v>
       </c>
       <c r="R134" t="n">
-        <v>6411479</v>
+        <v>6411533</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15529,48 +15538,57 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203164</v>
+        <v>128203127</v>
       </c>
       <c r="B135" t="n">
-        <v>109449</v>
+        <v>98604</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736260</v>
+        <v>736239</v>
       </c>
       <c r="R135" t="n">
-        <v>6411450</v>
+        <v>6411738</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15613,7 +15631,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15631,57 +15649,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203228</v>
+        <v>128203083</v>
       </c>
       <c r="B136" t="n">
-        <v>98577</v>
+        <v>109477</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736263</v>
+        <v>736442</v>
       </c>
       <c r="R136" t="n">
-        <v>6411533</v>
+        <v>6411479</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15724,7 +15733,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15742,57 +15751,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203127</v>
+        <v>128203164</v>
       </c>
       <c r="B137" t="n">
-        <v>98577</v>
+        <v>109477</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736239</v>
+        <v>736260</v>
       </c>
       <c r="R137" t="n">
-        <v>6411738</v>
+        <v>6411450</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15856,7 +15856,7 @@
         <v>128203139</v>
       </c>
       <c r="B138" t="n">
-        <v>98596</v>
+        <v>98623</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>128203085</v>
       </c>
       <c r="B139" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>128203240</v>
       </c>
       <c r="B140" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>128203084</v>
       </c>
       <c r="B141" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>128203223</v>
       </c>
       <c r="B142" t="n">
-        <v>98500</v>
+        <v>98527</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>128203231</v>
       </c>
       <c r="B143" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -6400,10 +6400,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203259</v>
+        <v>128203088</v>
       </c>
       <c r="B51" t="n">
-        <v>110535</v>
+        <v>98597</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6411,34 +6411,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219677</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736176</v>
+        <v>736474</v>
       </c>
       <c r="R51" t="n">
-        <v>6411455</v>
+        <v>6411506</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6471,11 +6480,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6507,10 +6511,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203088</v>
+        <v>128203259</v>
       </c>
       <c r="B52" t="n">
-        <v>98597</v>
+        <v>110535</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6518,43 +6522,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736474</v>
+        <v>736176</v>
       </c>
       <c r="R52" t="n">
-        <v>6411506</v>
+        <v>6411455</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6587,6 +6582,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Närmast heltäckande i hela skogen både på marken och klättrande i träden.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6729,10 +6729,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128203195</v>
+        <v>128203096</v>
       </c>
       <c r="B54" t="n">
-        <v>98527</v>
+        <v>98597</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6740,26 +6740,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219788</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6773,13 +6773,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736314</v>
+        <v>736474</v>
       </c>
       <c r="R54" t="n">
-        <v>6411572</v>
+        <v>6411596</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6845,7 +6845,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128203096</v>
+        <v>128203100</v>
       </c>
       <c r="B55" t="n">
         <v>98597</v>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736474</v>
+        <v>736361</v>
       </c>
       <c r="R55" t="n">
-        <v>6411596</v>
+        <v>6411697</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6925,11 +6925,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6961,54 +6956,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128203100</v>
+        <v>128203241</v>
       </c>
       <c r="B56" t="n">
-        <v>98597</v>
+        <v>109477</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736361</v>
+        <v>736223</v>
       </c>
       <c r="R56" t="n">
-        <v>6411697</v>
+        <v>6411512</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7041,6 +7027,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7072,27 +7063,27 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128203256</v>
+        <v>128203179</v>
       </c>
       <c r="B57" t="n">
-        <v>109477</v>
+        <v>99662</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220299</v>
+        <v>222662</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7107,10 +7098,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736176</v>
+        <v>736300</v>
       </c>
       <c r="R57" t="n">
-        <v>6411455</v>
+        <v>6411481</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7156,7 +7147,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7174,7 +7165,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128203241</v>
+        <v>128203256</v>
       </c>
       <c r="B58" t="n">
         <v>109477</v>
@@ -7209,10 +7200,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736223</v>
+        <v>736176</v>
       </c>
       <c r="R58" t="n">
-        <v>6411512</v>
+        <v>6411455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7245,11 +7236,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>T-kors stigar. Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7281,10 +7267,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128203179</v>
+        <v>128203195</v>
       </c>
       <c r="B59" t="n">
-        <v>99662</v>
+        <v>98527</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7292,37 +7278,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222662</v>
+        <v>219788</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736300</v>
+        <v>736314</v>
       </c>
       <c r="R59" t="n">
-        <v>6411481</v>
+        <v>6411572</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7354,6 +7349,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7383,48 +7383,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128203237</v>
+        <v>128203021</v>
       </c>
       <c r="B60" t="n">
-        <v>110535</v>
+        <v>57713</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736283</v>
+        <v>736197</v>
       </c>
       <c r="R60" t="n">
-        <v>6411500</v>
+        <v>6411554</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7454,11 +7459,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7490,38 +7490,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128203021</v>
+        <v>128203233</v>
       </c>
       <c r="B61" t="n">
-        <v>57713</v>
+        <v>98604</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>219799</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7530,10 +7534,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736197</v>
+        <v>736276</v>
       </c>
       <c r="R61" t="n">
-        <v>6411554</v>
+        <v>6411531</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7579,7 +7583,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7597,10 +7601,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128203233</v>
+        <v>128203186</v>
       </c>
       <c r="B62" t="n">
-        <v>98604</v>
+        <v>98641</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7608,26 +7612,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219799</v>
+        <v>219862</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7641,10 +7645,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>736276</v>
+        <v>736331</v>
       </c>
       <c r="R62" t="n">
-        <v>6411531</v>
+        <v>6411530</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7690,7 +7694,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7708,10 +7712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128203186</v>
+        <v>128203237</v>
       </c>
       <c r="B63" t="n">
-        <v>98641</v>
+        <v>110535</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7719,46 +7723,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219862</v>
+        <v>219677</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>736331</v>
+        <v>736283</v>
       </c>
       <c r="R63" t="n">
-        <v>6411530</v>
+        <v>6411500</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7788,6 +7783,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Överallt!</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8051,54 +8051,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128203089</v>
+        <v>128203243</v>
       </c>
       <c r="B66" t="n">
-        <v>98597</v>
+        <v>109477</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>736488</v>
+        <v>736237</v>
       </c>
       <c r="R66" t="n">
-        <v>6411510</v>
+        <v>6411472</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8144,7 +8135,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8162,45 +8153,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128203243</v>
+        <v>128203089</v>
       </c>
       <c r="B67" t="n">
-        <v>109477</v>
+        <v>98597</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>736237</v>
+        <v>736488</v>
       </c>
       <c r="R67" t="n">
-        <v>6411472</v>
+        <v>6411510</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, fuktig svacka mked blodriskor mm.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128203095</v>
+        <v>128203104</v>
       </c>
       <c r="B68" t="n">
-        <v>109477</v>
+        <v>105580</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8275,16 +8275,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>221137</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8299,13 +8299,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>736474</v>
+        <v>736325</v>
       </c>
       <c r="R68" t="n">
-        <v>6411596</v>
+        <v>6411730</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+          <t>Spridd. Flera i blom.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8371,57 +8371,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128203209</v>
+        <v>128203239</v>
       </c>
       <c r="B69" t="n">
-        <v>98621</v>
+        <v>109477</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>736295</v>
+        <v>736283</v>
       </c>
       <c r="R69" t="n">
-        <v>6411567</v>
+        <v>6411500</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8453,6 +8444,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8464,7 +8460,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8482,10 +8478,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128203104</v>
+        <v>128203095</v>
       </c>
       <c r="B70" t="n">
-        <v>105580</v>
+        <v>109477</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8493,16 +8489,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8517,13 +8513,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>736325</v>
+        <v>736474</v>
       </c>
       <c r="R70" t="n">
-        <v>6411730</v>
+        <v>6411596</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8557,7 +8553,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Spridd. Flera i blom.</t>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8571,7 +8567,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8589,48 +8585,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128203239</v>
+        <v>128203209</v>
       </c>
       <c r="B71" t="n">
-        <v>109477</v>
+        <v>98621</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>736283</v>
+        <v>736295</v>
       </c>
       <c r="R71" t="n">
-        <v>6411500</v>
+        <v>6411567</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8662,11 +8667,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8923,7 +8923,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128203181</v>
+        <v>128203166</v>
       </c>
       <c r="B74" t="n">
         <v>109477</v>
@@ -8958,13 +8958,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>736350</v>
+        <v>736275</v>
       </c>
       <c r="R74" t="n">
-        <v>6411491</v>
+        <v>6411455</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8994,11 +8994,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9030,7 +9025,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128203166</v>
+        <v>128203181</v>
       </c>
       <c r="B75" t="n">
         <v>109477</v>
@@ -9065,13 +9060,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>736275</v>
+        <v>736350</v>
       </c>
       <c r="R75" t="n">
-        <v>6411455</v>
+        <v>6411491</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9101,6 +9096,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9132,10 +9132,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128203189</v>
+        <v>128203114</v>
       </c>
       <c r="B76" t="n">
-        <v>109477</v>
+        <v>98625</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,34 +9143,43 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220299</v>
+        <v>742</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Luktsporre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia odoratissima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>736335</v>
+        <v>736184</v>
       </c>
       <c r="R76" t="n">
-        <v>6411533</v>
+        <v>6411805</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9205,6 +9214,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9216,7 +9230,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9234,10 +9248,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128203185</v>
+        <v>128203023</v>
       </c>
       <c r="B77" t="n">
-        <v>109477</v>
+        <v>57713</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9245,37 +9259,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>736331</v>
+        <v>736365</v>
       </c>
       <c r="R77" t="n">
-        <v>6411530</v>
+        <v>6411573</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9305,11 +9328,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9341,57 +9359,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128203099</v>
+        <v>128203199</v>
       </c>
       <c r="B78" t="n">
-        <v>109477</v>
+        <v>98604</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>736361</v>
+        <v>736314</v>
       </c>
       <c r="R78" t="n">
-        <v>6411697</v>
+        <v>6411572</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9423,6 +9432,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9434,7 +9448,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9452,10 +9466,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128203199</v>
+        <v>128203086</v>
       </c>
       <c r="B79" t="n">
-        <v>98604</v>
+        <v>98597</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9463,16 +9477,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9480,20 +9494,29 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>736314</v>
+        <v>736450</v>
       </c>
       <c r="R79" t="n">
-        <v>6411572</v>
+        <v>6411486</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9525,11 +9548,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9541,7 +9559,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9559,10 +9577,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128203086</v>
+        <v>128203221</v>
       </c>
       <c r="B80" t="n">
-        <v>98597</v>
+        <v>98621</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9570,26 +9588,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9603,13 +9621,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>736450</v>
+        <v>736272</v>
       </c>
       <c r="R80" t="n">
-        <v>6411486</v>
+        <v>6411546</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9652,7 +9670,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9670,54 +9688,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128203221</v>
+        <v>128203189</v>
       </c>
       <c r="B81" t="n">
-        <v>98621</v>
+        <v>109477</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219811</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>736272</v>
+        <v>736335</v>
       </c>
       <c r="R81" t="n">
-        <v>6411546</v>
+        <v>6411533</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9763,7 +9772,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9781,10 +9790,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128203114</v>
+        <v>128203185</v>
       </c>
       <c r="B82" t="n">
-        <v>98625</v>
+        <v>109477</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,43 +9801,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>742</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luktsporre</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gymnadenia odoratissima</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>736184</v>
+        <v>736331</v>
       </c>
       <c r="R82" t="n">
-        <v>6411805</v>
+        <v>6411530</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt. Flera andra spridda kan vara denna art också, men helt överblommade.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9897,10 +9897,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128203023</v>
+        <v>128203099</v>
       </c>
       <c r="B83" t="n">
-        <v>57713</v>
+        <v>109477</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9908,31 +9908,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>736365</v>
+        <v>736361</v>
       </c>
       <c r="R83" t="n">
-        <v>6411573</v>
+        <v>6411697</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10008,32 +10008,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128203132</v>
+        <v>128203249</v>
       </c>
       <c r="B84" t="n">
-        <v>107533</v>
+        <v>98597</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -10052,10 +10052,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>736242</v>
+        <v>736192</v>
       </c>
       <c r="R84" t="n">
-        <v>6411713</v>
+        <v>6411467</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128203249</v>
+        <v>128203162</v>
       </c>
       <c r="B85" t="n">
         <v>98597</v>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10163,13 +10163,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>736192</v>
+        <v>736250</v>
       </c>
       <c r="R85" t="n">
-        <v>6411467</v>
+        <v>6411464</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10230,10 +10230,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128203162</v>
+        <v>128203111</v>
       </c>
       <c r="B86" t="n">
-        <v>98597</v>
+        <v>98550</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10241,26 +10241,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219798</v>
+        <v>219794</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sumpnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10274,10 +10274,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>736250</v>
+        <v>736184</v>
       </c>
       <c r="R86" t="n">
-        <v>6411464</v>
+        <v>6411805</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10312,6 +10312,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10323,7 +10328,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10341,37 +10346,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128203111</v>
+        <v>128203132</v>
       </c>
       <c r="B87" t="n">
-        <v>98550</v>
+        <v>107533</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219794</v>
+        <v>220079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sumpnycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. lapponica</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Laest. ex Hartm.) H. Sund.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10385,13 +10390,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>736184</v>
+        <v>736242</v>
       </c>
       <c r="R87" t="n">
-        <v>6411805</v>
+        <v>6411713</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10423,11 +10428,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Stor källmyr under f.d. kraftledningsgata; körspårt.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Källmyr med insipprande vatten fårn strandvall i norr..</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10573,54 +10573,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128203165</v>
+        <v>128203180</v>
       </c>
       <c r="B89" t="n">
-        <v>98597</v>
+        <v>105580</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219798</v>
+        <v>221137</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>736260</v>
+        <v>736300</v>
       </c>
       <c r="R89" t="n">
-        <v>6411450</v>
+        <v>6411481</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10655,6 +10646,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10666,7 +10662,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10684,57 +10680,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128203081</v>
+        <v>128203211</v>
       </c>
       <c r="B90" t="n">
-        <v>98597</v>
+        <v>99296</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>736347</v>
+        <v>736301</v>
       </c>
       <c r="R90" t="n">
-        <v>6411466</v>
+        <v>6411564</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10777,7 +10764,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10795,10 +10782,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128203225</v>
+        <v>128203156</v>
       </c>
       <c r="B91" t="n">
-        <v>98621</v>
+        <v>98537</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10806,26 +10793,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219811</v>
+        <v>223591</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10839,13 +10826,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>736263</v>
+        <v>736221</v>
       </c>
       <c r="R91" t="n">
-        <v>6411533</v>
+        <v>6411593</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10888,7 +10875,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Blåtåtelkärr.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10906,10 +10893,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128203197</v>
+        <v>128203165</v>
       </c>
       <c r="B92" t="n">
-        <v>98621</v>
+        <v>98597</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10917,37 +10904,46 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>736314</v>
+        <v>736260</v>
       </c>
       <c r="R92" t="n">
-        <v>6411572</v>
+        <v>6411450</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10979,11 +10975,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10995,7 +10986,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11013,45 +11004,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128203180</v>
+        <v>128203081</v>
       </c>
       <c r="B93" t="n">
-        <v>105580</v>
+        <v>98597</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>736300</v>
+        <v>736347</v>
       </c>
       <c r="R93" t="n">
-        <v>6411481</v>
+        <v>6411466</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11086,11 +11086,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -11102,7 +11097,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11120,10 +11115,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128203156</v>
+        <v>128203225</v>
       </c>
       <c r="B94" t="n">
-        <v>98537</v>
+        <v>98621</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11131,26 +11126,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223591</v>
+        <v>219811</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11164,13 +11159,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>736221</v>
+        <v>736263</v>
       </c>
       <c r="R94" t="n">
-        <v>6411593</v>
+        <v>6411533</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11213,7 +11208,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Blåtåtelkärr.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11231,54 +11226,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128205915</v>
+        <v>128203197</v>
       </c>
       <c r="B95" t="n">
-        <v>57713</v>
+        <v>98621</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>219811</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>736315</v>
+        <v>736314</v>
       </c>
       <c r="R95" t="n">
-        <v>6411597</v>
+        <v>6411572</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11313,6 +11299,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -11324,7 +11315,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11342,10 +11333,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128203211</v>
+        <v>128205915</v>
       </c>
       <c r="B96" t="n">
-        <v>99296</v>
+        <v>57713</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11353,37 +11344,46 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>736301</v>
+        <v>736315</v>
       </c>
       <c r="R96" t="n">
-        <v>6411564</v>
+        <v>6411597</v>
       </c>
       <c r="S96" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11662,7 +11662,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128203087</v>
+        <v>128203246</v>
       </c>
       <c r="B99" t="n">
         <v>109477</v>
@@ -11697,13 +11697,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>736474</v>
+        <v>736213</v>
       </c>
       <c r="R99" t="n">
-        <v>6411506</v>
+        <v>6411456</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11733,6 +11733,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11764,7 +11769,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128203246</v>
+        <v>128203080</v>
       </c>
       <c r="B100" t="n">
         <v>109477</v>
@@ -11799,13 +11804,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>736213</v>
+        <v>736347</v>
       </c>
       <c r="R100" t="n">
-        <v>6411456</v>
+        <v>6411466</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11835,11 +11840,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Spridd. Nära stig genom skogen från Puttersjaus 1:29 (7).</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11871,7 +11871,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128203080</v>
+        <v>128203087</v>
       </c>
       <c r="B101" t="n">
         <v>109477</v>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>736347</v>
+        <v>736474</v>
       </c>
       <c r="R101" t="n">
-        <v>6411466</v>
+        <v>6411506</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13484,42 +13484,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128203215</v>
+        <v>128203134</v>
       </c>
       <c r="B116" t="n">
-        <v>98604</v>
+        <v>109477</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13528,13 +13528,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>736301</v>
+        <v>736242</v>
       </c>
       <c r="R116" t="n">
-        <v>6411564</v>
+        <v>6411713</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Stig på relikt strandvall, kalkgrus.</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128203134</v>
+        <v>128203247</v>
       </c>
       <c r="B117" t="n">
         <v>109477</v>
@@ -13623,26 +13623,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>736242</v>
+        <v>736192</v>
       </c>
       <c r="R117" t="n">
-        <v>6411713</v>
+        <v>6411467</v>
       </c>
       <c r="S117" t="n">
         <v>3</v>
@@ -13688,7 +13679,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Stig på relikt strandvall, kalkgrus.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13706,48 +13697,57 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128203247</v>
+        <v>128203215</v>
       </c>
       <c r="B118" t="n">
-        <v>109477</v>
+        <v>98604</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>736192</v>
+        <v>736301</v>
       </c>
       <c r="R118" t="n">
-        <v>6411467</v>
+        <v>6411564</v>
       </c>
       <c r="S118" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14244,48 +14244,57 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128203151</v>
+        <v>128203190</v>
       </c>
       <c r="B123" t="n">
-        <v>109477</v>
+        <v>98597</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>736248</v>
+        <v>736335</v>
       </c>
       <c r="R123" t="n">
-        <v>6411616</v>
+        <v>6411533</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14315,11 +14324,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14351,48 +14355,57 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128203091</v>
+        <v>128203216</v>
       </c>
       <c r="B124" t="n">
-        <v>109477</v>
+        <v>98597</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>736520</v>
+        <v>736297</v>
       </c>
       <c r="R124" t="n">
-        <v>6411544</v>
+        <v>6411559</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14422,6 +14435,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14453,7 +14471,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128203216</v>
+        <v>128203092</v>
       </c>
       <c r="B125" t="n">
         <v>98597</v>
@@ -14483,7 +14501,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -14497,13 +14515,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>736297</v>
+        <v>736520</v>
       </c>
       <c r="R125" t="n">
-        <v>6411559</v>
+        <v>6411544</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14533,11 +14551,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14569,54 +14582,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128203092</v>
+        <v>128203151</v>
       </c>
       <c r="B126" t="n">
-        <v>98597</v>
+        <v>109477</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>736520</v>
+        <v>736248</v>
       </c>
       <c r="R126" t="n">
-        <v>6411544</v>
+        <v>6411616</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14649,6 +14653,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14680,27 +14689,27 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128203235</v>
+        <v>128203091</v>
       </c>
       <c r="B127" t="n">
-        <v>110535</v>
+        <v>109477</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>219677</v>
+        <v>220299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -14715,13 +14724,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>736279</v>
+        <v>736520</v>
       </c>
       <c r="R127" t="n">
-        <v>6411517</v>
+        <v>6411544</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14782,10 +14791,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128203190</v>
+        <v>128203235</v>
       </c>
       <c r="B128" t="n">
-        <v>98597</v>
+        <v>110535</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14793,43 +14802,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219798</v>
+        <v>219677</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>736335</v>
+        <v>736279</v>
       </c>
       <c r="R128" t="n">
-        <v>6411533</v>
+        <v>6411517</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15427,57 +15427,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128203228</v>
+        <v>128203083</v>
       </c>
       <c r="B134" t="n">
-        <v>98604</v>
+        <v>109477</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>736263</v>
+        <v>736442</v>
       </c>
       <c r="R134" t="n">
-        <v>6411533</v>
+        <v>6411479</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15538,57 +15529,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128203127</v>
+        <v>128203164</v>
       </c>
       <c r="B135" t="n">
-        <v>98604</v>
+        <v>109477</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>219799</v>
+        <v>220299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>736239</v>
+        <v>736260</v>
       </c>
       <c r="R135" t="n">
-        <v>6411738</v>
+        <v>6411450</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15631,7 +15613,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15649,48 +15631,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128203083</v>
+        <v>128203139</v>
       </c>
       <c r="B136" t="n">
-        <v>109477</v>
+        <v>98623</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220299</v>
+        <v>741</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Praktsporre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea subsp. densiflora</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Wahlenb.) K. Richt.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>736442</v>
+        <v>736244</v>
       </c>
       <c r="R136" t="n">
-        <v>6411479</v>
+        <v>6411666</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15733,7 +15724,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Blåtåtelmyr, tuvigt.</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -15751,48 +15742,57 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128203164</v>
+        <v>128203228</v>
       </c>
       <c r="B137" t="n">
-        <v>109477</v>
+        <v>98604</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220299</v>
+        <v>219799</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>736260</v>
+        <v>736263</v>
       </c>
       <c r="R137" t="n">
-        <v>6411450</v>
+        <v>6411533</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128203139</v>
+        <v>128203127</v>
       </c>
       <c r="B138" t="n">
-        <v>98623</v>
+        <v>98604</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15864,26 +15864,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>741</v>
+        <v>219799</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Praktsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. densiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Wahlenb.) K. Richt.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15897,13 +15897,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>736244</v>
+        <v>736239</v>
       </c>
       <c r="R138" t="n">
-        <v>6411666</v>
+        <v>6411738</v>
       </c>
       <c r="S138" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>Blåtåtelmyr, tuvigt.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -15964,48 +15964,57 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128203085</v>
+        <v>128203223</v>
       </c>
       <c r="B139" t="n">
-        <v>109477</v>
+        <v>98527</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>736450</v>
+        <v>736272</v>
       </c>
       <c r="R139" t="n">
-        <v>6411486</v>
+        <v>6411536</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16048,7 +16057,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Agmrkant.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -16066,48 +16075,57 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128203240</v>
+        <v>128203084</v>
       </c>
       <c r="B140" t="n">
-        <v>109477</v>
+        <v>98597</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>736238</v>
+        <v>736442</v>
       </c>
       <c r="R140" t="n">
-        <v>6411496</v>
+        <v>6411479</v>
       </c>
       <c r="S140" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16137,11 +16155,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16173,7 +16186,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128203084</v>
+        <v>128203231</v>
       </c>
       <c r="B141" t="n">
         <v>98597</v>
@@ -16203,7 +16216,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -16217,13 +16230,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>736442</v>
+        <v>736270</v>
       </c>
       <c r="R141" t="n">
-        <v>6411479</v>
+        <v>6411530</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16284,57 +16297,48 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128203223</v>
+        <v>128203085</v>
       </c>
       <c r="B142" t="n">
-        <v>98527</v>
+        <v>109477</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>219788</v>
+        <v>220299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>736272</v>
+        <v>736450</v>
       </c>
       <c r="R142" t="n">
-        <v>6411536</v>
+        <v>6411486</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16377,7 +16381,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>Agmrkant.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
@@ -16395,57 +16399,48 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128203231</v>
+        <v>128203240</v>
       </c>
       <c r="B143" t="n">
-        <v>98597</v>
+        <v>109477</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>736270</v>
+        <v>736238</v>
       </c>
       <c r="R143" t="n">
-        <v>6411530</v>
+        <v>6411496</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16475,6 +16470,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt samt spridd.</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,39 +675,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104320432</v>
+        <v>104320467</v>
       </c>
       <c r="B2" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3712</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736361.8095210823</v>
+        <v>736340</v>
       </c>
       <c r="R2" t="n">
-        <v>6411458.912763584</v>
+        <v>6411442</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +739,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +775,7 @@
         <v>104320444</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736361.8095210823</v>
+        <v>736362</v>
       </c>
       <c r="R3" t="n">
-        <v>6411458.912763584</v>
+        <v>6411459</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,19 +840,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +873,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104320431</v>
+        <v>104320466</v>
       </c>
       <c r="B4" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736361.8095210823</v>
+        <v>736331</v>
       </c>
       <c r="R4" t="n">
-        <v>6411458.912763584</v>
+        <v>6411434</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,19 +941,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104320433</v>
+        <v>104320432</v>
       </c>
       <c r="B5" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736361.8095210823</v>
+        <v>736362</v>
       </c>
       <c r="R5" t="n">
-        <v>6411458.912763584</v>
+        <v>6411459</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,19 +1042,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,57 +1075,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128203088</v>
+        <v>104320454</v>
       </c>
       <c r="B6" t="n">
-        <v>98597</v>
+        <v>87170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>3712</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736474</v>
+        <v>736340</v>
       </c>
       <c r="R6" t="n">
-        <v>6411506</v>
+        <v>6411442</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,12 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,78 +1156,68 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128203096</v>
+        <v>104320464</v>
       </c>
       <c r="B7" t="n">
-        <v>98597</v>
+        <v>87358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>3727</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Klenodspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius spectabilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736474</v>
+        <v>736339</v>
       </c>
       <c r="R7" t="n">
-        <v>6411596</v>
+        <v>6411426</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,17 +1241,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,31 +1257,30 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128203195</v>
+        <v>104320433</v>
       </c>
       <c r="B8" t="n">
-        <v>98527</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,46 +1288,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219788</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736314</v>
+        <v>736362</v>
       </c>
       <c r="R8" t="n">
-        <v>6411572</v>
+        <v>6411459</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,17 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,31 +1358,30 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkgräsmyr.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128203186</v>
+        <v>128203023</v>
       </c>
       <c r="B9" t="n">
-        <v>98641</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1515,9 +1411,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,13 +1422,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736331</v>
+        <v>736365</v>
       </c>
       <c r="R9" t="n">
-        <v>6411530</v>
+        <v>6411573</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1593,10 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128203089</v>
+        <v>128205915</v>
       </c>
       <c r="B10" t="n">
-        <v>98597</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,31 +1500,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1637,13 +1533,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736488</v>
+        <v>736315</v>
       </c>
       <c r="R10" t="n">
-        <v>6411510</v>
+        <v>6411597</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,48 +1600,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128203095</v>
+        <v>128203101</v>
       </c>
       <c r="B11" t="n">
-        <v>109477</v>
+        <v>99026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>219788</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736474</v>
+        <v>736358</v>
       </c>
       <c r="R11" t="n">
-        <v>6411596</v>
+        <v>6411725</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,11 +1682,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1793,7 +1693,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1811,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128203182</v>
+        <v>128203195</v>
       </c>
       <c r="B12" t="n">
-        <v>98597</v>
+        <v>99026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,26 +1722,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1855,13 +1755,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736350</v>
+        <v>736314</v>
       </c>
       <c r="R12" t="n">
-        <v>6411491</v>
+        <v>6411572</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stig över våtmark; avsnitslat.</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,7 +1809,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1927,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128203187</v>
+        <v>128203081</v>
       </c>
       <c r="B13" t="n">
-        <v>98597</v>
+        <v>99096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1857,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1971,13 +1871,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736331</v>
+        <v>736347</v>
       </c>
       <c r="R13" t="n">
-        <v>6411530</v>
+        <v>6411466</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,48 +1938,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128203181</v>
+        <v>128203084</v>
       </c>
       <c r="B14" t="n">
-        <v>109477</v>
+        <v>99096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736350</v>
+        <v>736442</v>
       </c>
       <c r="R14" t="n">
-        <v>6411491</v>
+        <v>6411479</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2109,11 +2018,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,42 +2049,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128203023</v>
+        <v>128203086</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>99096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2189,13 +2093,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736365</v>
+        <v>736450</v>
       </c>
       <c r="R15" t="n">
-        <v>6411573</v>
+        <v>6411486</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2256,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128203199</v>
+        <v>128203088</v>
       </c>
       <c r="B16" t="n">
-        <v>98604</v>
+        <v>99096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,16 +2171,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2284,20 +2188,29 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736314</v>
+        <v>736474</v>
       </c>
       <c r="R16" t="n">
-        <v>6411572</v>
+        <v>6411506</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,11 +2242,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2345,7 +2253,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2363,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128203086</v>
+        <v>128203089</v>
       </c>
       <c r="B17" t="n">
-        <v>98597</v>
+        <v>99096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2393,7 +2301,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2407,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736450</v>
+        <v>736488</v>
       </c>
       <c r="R17" t="n">
-        <v>6411486</v>
+        <v>6411510</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,48 +2382,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128203189</v>
+        <v>128203092</v>
       </c>
       <c r="B18" t="n">
-        <v>109477</v>
+        <v>99096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736335</v>
+        <v>736520</v>
       </c>
       <c r="R18" t="n">
-        <v>6411533</v>
+        <v>6411544</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2576,48 +2493,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128203185</v>
+        <v>128203094</v>
       </c>
       <c r="B19" t="n">
-        <v>109477</v>
+        <v>99096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736331</v>
+        <v>736498</v>
       </c>
       <c r="R19" t="n">
-        <v>6411530</v>
+        <v>6411566</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2647,11 +2573,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,32 +2604,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128203192</v>
+        <v>128203096</v>
       </c>
       <c r="B20" t="n">
-        <v>105580</v>
+        <v>99096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221137</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2727,13 +2648,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736339</v>
+        <v>736474</v>
       </c>
       <c r="R20" t="n">
-        <v>6411571</v>
+        <v>6411596</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,7 +2688,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,7 +2702,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2799,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128203081</v>
+        <v>128203100</v>
       </c>
       <c r="B21" t="n">
-        <v>98597</v>
+        <v>99096</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,10 +2764,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736347</v>
+        <v>736361</v>
       </c>
       <c r="R21" t="n">
-        <v>6411466</v>
+        <v>6411697</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2910,10 +2831,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128203197</v>
+        <v>128203182</v>
       </c>
       <c r="B22" t="n">
-        <v>98621</v>
+        <v>99096</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,37 +2842,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736314</v>
+        <v>736350</v>
       </c>
       <c r="R22" t="n">
-        <v>6411572</v>
+        <v>6411491</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,7 +2915,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,7 +2929,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3017,42 +2947,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128205915</v>
+        <v>128203187</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>99096</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3061,13 +2991,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736315</v>
+        <v>736331</v>
       </c>
       <c r="R23" t="n">
-        <v>6411597</v>
+        <v>6411530</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3128,48 +3058,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128203080</v>
+        <v>128203190</v>
       </c>
       <c r="B24" t="n">
-        <v>109477</v>
+        <v>99096</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736347</v>
+        <v>736335</v>
       </c>
       <c r="R24" t="n">
-        <v>6411466</v>
+        <v>6411533</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3230,48 +3169,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128203087</v>
+        <v>128203216</v>
       </c>
       <c r="B25" t="n">
-        <v>109477</v>
+        <v>99096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736474</v>
+        <v>736297</v>
       </c>
       <c r="R25" t="n">
-        <v>6411506</v>
+        <v>6411559</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3301,6 +3249,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128203094</v>
+        <v>128203177</v>
       </c>
       <c r="B26" t="n">
-        <v>98597</v>
+        <v>99103</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,16 +3296,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3360,26 +3313,17 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736498</v>
+        <v>736300</v>
       </c>
       <c r="R26" t="n">
-        <v>6411566</v>
+        <v>6411481</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3414,6 +3358,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3425,7 +3374,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3443,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128203190</v>
+        <v>128203199</v>
       </c>
       <c r="B27" t="n">
-        <v>98597</v>
+        <v>99103</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3454,16 +3403,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3471,29 +3420,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736335</v>
+        <v>736314</v>
       </c>
       <c r="R27" t="n">
-        <v>6411533</v>
+        <v>6411572</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,6 +3465,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3536,7 +3481,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3554,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128203092</v>
+        <v>128203215</v>
       </c>
       <c r="B28" t="n">
-        <v>98597</v>
+        <v>99103</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3565,16 +3510,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3584,7 +3529,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3598,13 +3543,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736520</v>
+        <v>736301</v>
       </c>
       <c r="R28" t="n">
-        <v>6411544</v>
+        <v>6411564</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3647,7 +3592,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3665,45 +3610,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128203091</v>
+        <v>128203173</v>
       </c>
       <c r="B29" t="n">
-        <v>109477</v>
+        <v>99120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736520</v>
+        <v>736300</v>
       </c>
       <c r="R29" t="n">
-        <v>6411544</v>
+        <v>6411439</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3749,7 +3703,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3767,32 +3721,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128203093</v>
+        <v>128203197</v>
       </c>
       <c r="B30" t="n">
-        <v>109477</v>
+        <v>99120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3802,13 +3756,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736498</v>
+        <v>736314</v>
       </c>
       <c r="R30" t="n">
-        <v>6411566</v>
+        <v>6411572</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3840,6 +3794,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3851,7 +3810,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3869,48 +3828,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128203083</v>
+        <v>128203207</v>
       </c>
       <c r="B31" t="n">
-        <v>109477</v>
+        <v>99120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736442</v>
+        <v>736300</v>
       </c>
       <c r="R31" t="n">
-        <v>6411479</v>
+        <v>6411576</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3953,7 +3921,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3971,10 +3939,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128203084</v>
+        <v>128203209</v>
       </c>
       <c r="B32" t="n">
-        <v>98597</v>
+        <v>99120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3982,26 +3950,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4015,13 +3983,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736442</v>
+        <v>736295</v>
       </c>
       <c r="R32" t="n">
-        <v>6411479</v>
+        <v>6411567</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4064,7 +4032,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4082,48 +4050,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128203085</v>
+        <v>128203213</v>
       </c>
       <c r="B33" t="n">
-        <v>109477</v>
+        <v>99120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736450</v>
+        <v>736301</v>
       </c>
       <c r="R33" t="n">
-        <v>6411486</v>
+        <v>6411564</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4166,7 +4143,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4181,6 +4158,2424 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128203186</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>736331</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6411530</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128203080</v>
+      </c>
+      <c r="B35" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>736347</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6411466</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128203082</v>
+      </c>
+      <c r="B36" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>736416</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6411452</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stig (avsnitslad) ut ur Stora Valle och in i Alvans 1:13 (2).</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128203083</v>
+      </c>
+      <c r="B37" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>736442</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6411479</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128203085</v>
+      </c>
+      <c r="B38" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>736450</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6411486</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128203087</v>
+      </c>
+      <c r="B39" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>736474</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6411506</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128203091</v>
+      </c>
+      <c r="B40" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>736520</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6411544</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128203093</v>
+      </c>
+      <c r="B41" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>736498</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6411566</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128203095</v>
+      </c>
+      <c r="B42" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>736474</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6411596</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128203099</v>
+      </c>
+      <c r="B43" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>736361</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6411697</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128203181</v>
+      </c>
+      <c r="B44" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>736350</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6411491</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128203185</v>
+      </c>
+      <c r="B45" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>736331</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6411530</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128203189</v>
+      </c>
+      <c r="B46" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>736335</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6411533</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128203220</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>736295</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6411551</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128203180</v>
+      </c>
+      <c r="B48" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>736300</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6411481</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Källmyr.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128203192</v>
+      </c>
+      <c r="B49" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>736339</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6411571</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkgräsmyr.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128203178</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98642</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221930</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kärrlilja</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tofieldia calyculata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Wahlenb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>736300</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6411481</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Källmyr.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128203211</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>736301</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6411564</v>
+      </c>
+      <c r="S51" t="n">
+        <v>7</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkgräsmyr.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128203179</v>
+      </c>
+      <c r="B52" t="n">
+        <v>100171</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222662</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Axag</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Schoenus ferrugineus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>736300</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6411481</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Källmyr.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>104320411</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>736341</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6411703</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>104320452</v>
+      </c>
+      <c r="B54" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>736340</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6411442</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>104320431</v>
+      </c>
+      <c r="B55" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>736362</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6411459</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>104320453</v>
+      </c>
+      <c r="B56" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>736340</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6411442</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320467</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320444</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320466</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320432</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320454</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320464</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320433</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203023</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128205915</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203101</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203195</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203081</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2046,6 +2111,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203084</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2157,6 +2227,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203086</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2268,6 +2343,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203088</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203089</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2490,6 +2575,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203092</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2601,6 +2691,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203094</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2717,6 +2812,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203096</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2828,6 +2928,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203100</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2944,6 +3049,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203182</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3055,6 +3165,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203187</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3166,6 +3281,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203190</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3282,6 +3402,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203216</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3389,6 +3514,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203177</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3496,6 +3626,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203199</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3607,6 +3742,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203215</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3718,6 +3858,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203173</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3825,6 +3970,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203197</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3936,6 +4086,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203207</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4047,6 +4202,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203209</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4158,6 +4318,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203213</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4269,6 +4434,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203186</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4371,6 +4541,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203080</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4478,6 +4653,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203082</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4580,6 +4760,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203083</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4682,6 +4867,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203085</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4784,6 +4974,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203087</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4886,6 +5081,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203091</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4988,6 +5188,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203093</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5095,6 +5300,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203095</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5206,6 +5416,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203099</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5313,6 +5528,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203181</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5420,6 +5640,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203185</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5522,6 +5747,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203189</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5638,6 +5868,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203220</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5745,6 +5980,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203180</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5861,6 +6101,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203192</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5968,6 +6213,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203178</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6070,6 +6320,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203211</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6172,6 +6427,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128203179</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6273,6 +6533,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320411</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6374,6 +6639,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320452</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6475,6 +6745,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320431</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6576,8 +6851,70 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320453</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>